--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -860,19 +860,19 @@
         <v>2.28</v>
       </c>
       <c r="G2" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 00:23:13</t>
+          <t>2026-05-24 02:47:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -890,7 +890,7 @@
         <v>1.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 02:47:27</t>
+          <t>2026-05-24 05:12:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="H2" t="n">
         <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
         <v>1.85</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:12:28</t>
+          <t>2026-05-24 07:37:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
         <v>1.85</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 07:37:32</t>
+          <t>2026-05-24 10:00:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 10:00:27</t>
+          <t>2026-05-24 12:22:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -866,7 +866,7 @@
         <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
@@ -875,16 +875,16 @@
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
         <v>1.97</v>
@@ -893,194 +893,194 @@
         <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 12:22:04</t>
+          <t>2026-05-24 14:40:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,7 +875,7 @@
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -884,13 +884,13 @@
         <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
         <v>1.37</v>
@@ -899,10 +899,10 @@
         <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="U2" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
         <v>1.37</v>
@@ -971,10 +971,10 @@
         <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
         <v>8</v>
@@ -986,7 +986,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
@@ -998,25 +998,25 @@
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
         <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
         <v>3.65</v>
@@ -1028,13 +1028,13 @@
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
         <v>5.5</v>
@@ -1046,13 +1046,13 @@
         <v>17.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
         <v>6.8</v>
@@ -1064,23 +1064,531 @@
         <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>26</v>
       </c>
       <c r="CA2" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 14:40:02</t>
+          <t>2026-05-24 16:55:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>KR Reykjavik</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-05-24 16:55:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-05-24 16:55:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
         <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -887,28 +887,28 @@
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R2" t="n">
         <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X2" t="n">
         <v>19</v>
@@ -917,10 +917,10 @@
         <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB2" t="n">
         <v>13</v>
@@ -932,7 +932,7 @@
         <v>17.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
         <v>19</v>
@@ -944,7 +944,7 @@
         <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
         <v>38</v>
@@ -965,7 +965,7 @@
         <v>42</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
         <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT2" t="n">
         <v>8</v>
@@ -986,7 +986,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
@@ -998,25 +998,25 @@
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BC2" t="n">
         <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH2" t="n">
         <v>3.65</v>
@@ -1028,13 +1028,13 @@
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN2" t="n">
         <v>5.5</v>
@@ -1046,16 +1046,16 @@
         <v>17.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU2" t="n">
         <v>5</v>
@@ -1064,23 +1064,23 @@
         <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
         <v>26</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 16:55:33</t>
+          <t>2026-05-24 19:08:36</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.03</v>
@@ -1144,19 +1144,19 @@
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1276,65 +1276,65 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-24 16:55:33</t>
+          <t>2026-05-24 19:08:36</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.08</v>
@@ -1404,13 +1404,13 @@
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-24 16:55:33</t>
+          <t>2026-05-24 19:08:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="H2" t="n">
         <v>3.1</v>
@@ -902,13 +902,13 @@
         <v>1.69</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V2" t="n">
         <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X2" t="n">
         <v>19</v>
@@ -938,7 +938,7 @@
         <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -950,7 +950,7 @@
         <v>38</v>
       </c>
       <c r="AK2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
         <v>44</v>
@@ -968,55 +968,55 @@
         <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AT2" t="n">
         <v>8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.85</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.9</v>
+        <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.75</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.85</v>
+        <v>26</v>
       </c>
       <c r="BE2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BH2" t="n">
         <v>3.65</v>
@@ -1040,7 +1040,7 @@
         <v>5.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
         <v>17.5</v>
@@ -1052,7 +1052,7 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BT2" t="n">
         <v>7</v>
@@ -1064,7 +1064,7 @@
         <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1076,11 +1076,11 @@
         <v>26</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 19:08:36</t>
+          <t>2026-05-24 21:21:11</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>1.81</v>
       </c>
       <c r="O3" t="n">
         <v>1.03</v>
@@ -1144,7 +1144,7 @@
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-24 19:08:36</t>
+          <t>2026-05-24 21:21:11</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,515 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-24 19:08:36</t>
+          <t>2026-05-24 21:21:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>50</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-05-24 21:21:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LDU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Always Ready</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>400</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-05-24 21:21:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G2" t="n">
         <v>2.54</v>
@@ -866,7 +866,7 @@
         <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
@@ -896,19 +896,19 @@
         <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
         <v>1.69</v>
       </c>
       <c r="U2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
         <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="X2" t="n">
         <v>19</v>
@@ -920,7 +920,7 @@
         <v>30</v>
       </c>
       <c r="AA2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
         <v>13</v>
@@ -938,7 +938,7 @@
         <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -968,31 +968,31 @@
         <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>18</v>
+        <v>3.75</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT2" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
         <v>27</v>
       </c>
       <c r="AX2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
         <v>12.5</v>
@@ -1004,19 +1004,19 @@
         <v>22</v>
       </c>
       <c r="BC2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD2" t="n">
         <v>26</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BH2" t="n">
         <v>3.65</v>
@@ -1040,7 +1040,7 @@
         <v>5.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>17.5</v>
@@ -1052,7 +1052,7 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
         <v>7</v>
@@ -1064,7 +1064,7 @@
         <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>18.5</v>
+        <v>7.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1076,11 +1076,11 @@
         <v>26</v>
       </c>
       <c r="CA2" t="n">
-        <v>18</v>
+        <v>7.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
         <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
         <v>120</v>
@@ -1721,7 +1721,7 @@
         <v>270</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AO5" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>5.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="BP5" t="n">
         <v>19</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>5.2</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.31</v>
@@ -1945,7 +1945,7 @@
         <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
         <v>180</v>
@@ -1957,7 +1957,7 @@
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
         <v>140</v>
@@ -1987,10 +1987,10 @@
         <v>22</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -2002,7 +2002,7 @@
         <v>24</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
         <v>6.6</v>
@@ -2014,25 +2014,25 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
         <v>8.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH6" t="n">
         <v>4.3</v>
@@ -2044,59 +2044,59 @@
         <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN6" t="n">
         <v>4</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BP6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BR6" t="n">
         <v>24</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT6" t="n">
         <v>13.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>13</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-24 21:21:11</t>
+          <t>2026-05-24 23:32:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>2.22</v>
       </c>
       <c r="G2" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
         <v>3.1</v>
@@ -896,7 +896,7 @@
         <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T2" t="n">
         <v>1.69</v>
@@ -908,7 +908,7 @@
         <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="X2" t="n">
         <v>19</v>
@@ -968,46 +968,46 @@
         <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.75</v>
+        <v>17.5</v>
       </c>
       <c r="AS2" t="n">
         <v>4</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>27</v>
+        <v>3.95</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
         <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>3.9</v>
       </c>
       <c r="BC2" t="n">
         <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>26</v>
+        <v>3.95</v>
       </c>
       <c r="BE2" t="n">
         <v>4.1</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-24 23:32:33</t>
+          <t>2026-05-25 01:44:27</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-24 23:32:33</t>
+          <t>2026-05-25 01:44:27</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-24 23:32:33</t>
+          <t>2026-05-25 01:44:27</t>
         </is>
       </c>
     </row>
@@ -1628,22 +1628,22 @@
         <v>5.5</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J5" t="n">
         <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O5" t="n">
         <v>1.47</v>
@@ -1667,7 +1667,7 @@
         <v>1.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
         <v>2.16</v>
@@ -1682,10 +1682,10 @@
         <v>46</v>
       </c>
       <c r="AA5" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC5" t="n">
         <v>8.4</v>
@@ -1724,7 +1724,7 @@
         <v>970</v>
       </c>
       <c r="AO5" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AP5" t="n">
         <v>8.6</v>
@@ -1748,7 +1748,7 @@
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX5" t="n">
         <v>8.199999999999999</v>
@@ -1760,7 +1760,7 @@
         <v>23</v>
       </c>
       <c r="BA5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB5" t="n">
         <v>16.5</v>
@@ -1772,77 +1772,77 @@
         <v>46</v>
       </c>
       <c r="BE5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF5" t="n">
         <v>15</v>
       </c>
       <c r="BG5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>11</v>
       </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BZ5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-24 23:32:33</t>
+          <t>2026-05-25 01:44:27</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>110</v>
       </c>
       <c r="AA6" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="AB6" t="n">
         <v>11.5</v>
@@ -1948,7 +1948,7 @@
         <v>950</v>
       </c>
       <c r="AE6" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF6" t="n">
         <v>9</v>
@@ -1972,13 +1972,13 @@
         <v>42</v>
       </c>
       <c r="AM6" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN6" t="n">
         <v>5.7</v>
       </c>
       <c r="AO6" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP6" t="n">
         <v>16</v>
@@ -1987,7 +1987,7 @@
         <v>22</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>7.2</v>
@@ -2044,59 +2044,1075 @@
         <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BP6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
         <v>24</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BU6" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
         <v>13</v>
       </c>
       <c r="CA6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:44:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cusco FC</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I7" t="n">
+        <v>40</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K7" t="n">
+        <v>15</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX7" t="n">
         <v>6</v>
       </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-05-24 23:32:33</t>
+      <c r="AY7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>7</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:44:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:44:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:44:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>290</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-05-25 01:44:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.84</v>
+        <v>1.19</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>1.19</v>
       </c>
       <c r="T2" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 01:44:27</t>
+          <t>2026-05-25 03:56:28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,136 +1135,136 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
         <v>1.03</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="AQ3" t="n">
         <v>1.03</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1276,72 +1276,72 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 01:44:27</t>
+          <t>2026-05-25 03:56:28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.08</v>
+        <v>1.74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>1.07</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 01:44:27</t>
+          <t>2026-05-25 03:56:28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.76</v>
+        <v>1.81</v>
       </c>
       <c r="O5" t="n">
-        <v>1.47</v>
+        <v>1.03</v>
       </c>
       <c r="P5" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>1.03</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>4.7</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 01:44:27</t>
+          <t>2026-05-25 03:56:28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,244 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
         <v>1.04</v>
       </c>
-      <c r="N6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>380</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.25</v>
-      </c>
       <c r="BJ6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 01:44:27</t>
+          <t>2026-05-25 03:56:28</t>
         </is>
       </c>
     </row>
@@ -2113,244 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cusco FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.12</v>
+        <v>1.78</v>
       </c>
       <c r="G7" t="n">
-        <v>1.15</v>
+        <v>1.9</v>
       </c>
       <c r="H7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>21</v>
       </c>
-      <c r="I7" t="n">
-        <v>40</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="AK7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW7" t="n">
         <v>11</v>
       </c>
-      <c r="K7" t="n">
+      <c r="AX7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF7" t="n">
         <v>15</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="BG7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK7" t="n">
         <v>6.4</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="X7" t="n">
-        <v>46</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>95</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AG7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="BU7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="CA7" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 01:44:27</t>
+          <t>2026-05-25 03:56:28</t>
         </is>
       </c>
     </row>
@@ -2367,244 +2367,244 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="G8" t="n">
-        <v>1.89</v>
+        <v>1.42</v>
       </c>
       <c r="H8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J8" t="n">
         <v>5.2</v>
       </c>
-      <c r="I8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.45</v>
-      </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>2.98</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>1.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="S8" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="X8" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>380</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG8" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AH8" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP8" t="n">
         <v>16</v>
       </c>
-      <c r="Z8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AQ8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY8" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AZ8" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD8" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG8" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH8" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="BJ8" t="n">
         <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
         <v>10</v>
       </c>
-      <c r="BN8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>9</v>
-      </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA8" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 01:44:27</t>
+          <t>2026-05-25 03:56:28</t>
         </is>
       </c>
     </row>
@@ -2626,239 +2626,239 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cusco FC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.04</v>
+        <v>1.13</v>
       </c>
       <c r="G9" t="n">
-        <v>2.24</v>
+        <v>1.16</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="I9" t="n">
+        <v>34</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CA9" t="n">
         <v>4.9</v>
       </c>
-      <c r="J9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>11.5</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 01:44:27</t>
+          <t>2026-05-25 03:56:28</t>
         </is>
       </c>
     </row>
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="H10" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="I10" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.65</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.49</v>
@@ -2919,200 +2919,708 @@
         <v>1.43</v>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
         <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="X10" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
-        <v>310</v>
+        <v>160</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE10" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI10" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AJ10" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
         <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="AN10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>8</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-05-25 03:56:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>12</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-05-25 03:56:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF12" t="n">
         <v>970</v>
       </c>
-      <c r="AO10" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP10" t="n">
+      <c r="AG12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP12" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AQ12" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT10" t="n">
+      <c r="AR12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX12" t="n">
         <v>4.9</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY12" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ10" t="n">
+      <c r="AZ12" t="n">
         <v>20</v>
       </c>
-      <c r="BA10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB10" t="n">
+      <c r="BA12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB12" t="n">
         <v>12</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BC12" t="n">
         <v>15</v>
       </c>
-      <c r="BD10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF10" t="n">
+      <c r="BD12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BF12" t="n">
         <v>10</v>
       </c>
-      <c r="BG10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH10" t="n">
+      <c r="BG12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BH12" t="n">
         <v>3.05</v>
       </c>
-      <c r="BI10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK10" t="n">
+      <c r="BI12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
         <v>6.8</v>
       </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
         <v>14</v>
       </c>
-      <c r="BN10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
         <v>10.5</v>
       </c>
-      <c r="BT10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-05-25 01:44:27</t>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-05-25 03:56:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -899,16 +899,16 @@
         <v>1.19</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1022,65 +1022,65 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 03:56:28</t>
+          <t>2026-05-25 06:08:15</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1144,7 +1144,7 @@
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
@@ -1153,16 +1153,16 @@
         <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1276,65 +1276,65 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 03:56:28</t>
+          <t>2026-05-25 06:08:15</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G4" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
         <v>3.75</v>
@@ -1383,13 +1383,13 @@
         <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
@@ -1398,34 +1398,34 @@
         <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
         <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
         <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="n">
         <v>70</v>
@@ -1437,13 +1437,13 @@
         <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG4" t="n">
         <v>14</v>
@@ -1455,13 +1455,13 @@
         <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK4" t="n">
         <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -1470,22 +1470,22 @@
         <v>22</v>
       </c>
       <c r="AO4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.95</v>
+        <v>40</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
         <v>7.2</v>
@@ -1500,16 +1500,16 @@
         <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BC4" t="n">
         <v>18</v>
@@ -1518,77 +1518,77 @@
         <v>3.85</v>
       </c>
       <c r="BE4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN4" t="n">
         <v>5.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP4" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>8</v>
       </c>
-      <c r="BT4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BZ4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 03:56:28</t>
+          <t>2026-05-25 06:08:15</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 03:56:28</t>
+          <t>2026-05-25 06:08:15</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 03:56:28</t>
+          <t>2026-05-25 06:08:15</t>
         </is>
       </c>
     </row>
@@ -2127,175 +2127,175 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P7" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="R7" t="n">
         <v>1.21</v>
       </c>
       <c r="S7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
         <v>120</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
         <v>60</v>
       </c>
       <c r="AM7" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ7" t="n">
         <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.6</v>
+        <v>32</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU7" t="n">
         <v>7.4</v>
       </c>
       <c r="AV7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>20</v>
       </c>
-      <c r="AW7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>23</v>
-      </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD7" t="n">
         <v>46</v>
       </c>
       <c r="BE7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BG7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK7" t="n">
         <v>6.4</v>
@@ -2307,16 +2307,16 @@
         <v>12.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2325,10 +2325,10 @@
         <v>10</v>
       </c>
       <c r="BT7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2343,14 +2343,14 @@
         <v>11.5</v>
       </c>
       <c r="BZ7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 03:56:28</t>
+          <t>2026-05-25 06:08:15</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
         <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K8" t="n">
         <v>6.2</v>
@@ -2414,7 +2414,7 @@
         <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R8" t="n">
         <v>1.51</v>
@@ -2432,13 +2432,13 @@
         <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="X8" t="n">
         <v>28</v>
       </c>
       <c r="Y8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="n">
         <v>110</v>
@@ -2477,7 +2477,7 @@
         <v>15.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
         <v>170</v>
@@ -2498,7 +2498,7 @@
         <v>7</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2510,7 +2510,7 @@
         <v>24</v>
       </c>
       <c r="AW8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX8" t="n">
         <v>6.6</v>
@@ -2522,7 +2522,7 @@
         <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB8" t="n">
         <v>8.6</v>
@@ -2534,13 +2534,13 @@
         <v>6.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF8" t="n">
         <v>4.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="n">
         <v>4.3</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 03:56:28</t>
+          <t>2026-05-25 06:08:15</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="G9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H9" t="n">
         <v>21</v>
@@ -2650,7 +2650,7 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="L9" t="n">
         <v>1.22</v>
@@ -2659,40 +2659,40 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="Q9" t="n">
         <v>1.37</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="U9" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="V9" t="n">
         <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="X9" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2704,10 +2704,10 @@
         <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AD9" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2719,7 +2719,7 @@
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2743,16 +2743,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT9" t="n">
         <v>8.6</v>
@@ -2761,10 +2761,10 @@
         <v>5.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AX9" t="n">
         <v>6</v>
@@ -2773,10 +2773,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BB9" t="n">
         <v>5.8</v>
@@ -2785,64 +2785,64 @@
         <v>11.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="BG9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH9" t="n">
         <v>5.4</v>
       </c>
-      <c r="BH9" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BI9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BP9" t="n">
         <v>5.6</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
@@ -2851,14 +2851,14 @@
         <v>11</v>
       </c>
       <c r="BZ9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 03:56:28</t>
+          <t>2026-05-25 06:08:15</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="G10" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="H10" t="n">
         <v>5.3</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
         <v>3.45</v>
@@ -2907,7 +2907,7 @@
         <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
@@ -2931,19 +2931,19 @@
         <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U10" t="n">
         <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X10" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="n">
         <v>16</v>
@@ -2976,7 +2976,7 @@
         <v>25</v>
       </c>
       <c r="AI10" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ10" t="n">
         <v>21</v>
@@ -3006,7 +3006,7 @@
         <v>34</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT10" t="n">
         <v>6.2</v>
@@ -3018,7 +3018,7 @@
         <v>19</v>
       </c>
       <c r="AW10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX10" t="n">
         <v>8.6</v>
@@ -3030,25 +3030,25 @@
         <v>21</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
         <v>17.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD10" t="n">
         <v>40</v>
       </c>
       <c r="BE10" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF10" t="n">
         <v>14.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="n">
         <v>3.1</v>
@@ -3060,7 +3060,7 @@
         <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3072,13 +3072,13 @@
         <v>4.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="BP10" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR10" t="n">
         <v>36</v>
@@ -3090,7 +3090,7 @@
         <v>9</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3102,17 +3102,17 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-25 03:56:28</t>
+          <t>2026-05-25 06:08:15</t>
         </is>
       </c>
     </row>
@@ -3143,25 +3143,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="M11" t="n">
         <v>1.12</v>
@@ -3173,7 +3173,7 @@
         <v>1.52</v>
       </c>
       <c r="P11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q11" t="n">
         <v>2.56</v>
@@ -3191,40 +3191,40 @@
         <v>1.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X11" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA11" t="n">
         <v>140</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC11" t="n">
         <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE11" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AF11" t="n">
         <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>30</v>
@@ -3254,16 +3254,16 @@
         <v>8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS11" t="n">
         <v>5.6</v>
       </c>
-      <c r="AS11" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AT11" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU11" t="n">
         <v>7</v>
@@ -3272,37 +3272,37 @@
         <v>15</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA11" t="n">
         <v>5.5</v>
       </c>
-      <c r="BA11" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BB11" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG11" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>6.4</v>
       </c>
       <c r="BH11" t="n">
         <v>2.76</v>
@@ -3314,7 +3314,7 @@
         <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3344,7 +3344,7 @@
         <v>8</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-25 03:56:28</t>
+          <t>2026-05-25 06:08:15</t>
         </is>
       </c>
     </row>
@@ -3406,28 +3406,28 @@
         <v>6.4</v>
       </c>
       <c r="I12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
         <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O12" t="n">
         <v>1.43</v>
       </c>
       <c r="P12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
         <v>2.26</v>
@@ -3442,7 +3442,7 @@
         <v>2.22</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
         <v>1.15</v>
@@ -3469,10 +3469,10 @@
         <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AE12" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF12" t="n">
         <v>970</v>
@@ -3481,7 +3481,7 @@
         <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI12" t="n">
         <v>160</v>
@@ -3502,40 +3502,40 @@
         <v>970</v>
       </c>
       <c r="AO12" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AP12" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>9.6</v>
+        <v>36</v>
       </c>
       <c r="AS12" t="n">
         <v>3.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AU12" t="n">
         <v>7.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AX12" t="n">
         <v>4.9</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA12" t="n">
         <v>10.5</v>
@@ -3544,7 +3544,7 @@
         <v>12</v>
       </c>
       <c r="BC12" t="n">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="BD12" t="n">
         <v>6.4</v>
@@ -3562,65 +3562,65 @@
         <v>3.05</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BN12" t="n">
         <v>3.95</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT12" t="n">
         <v>10.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-25 03:56:28</t>
+          <t>2026-05-25 06:08:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -848,55 +848,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>Alashkert</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>FC Shirak</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.25</v>
-      </c>
       <c r="O2" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -905,10 +905,10 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1073,14 +1073,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 06:08:15</t>
+          <t>2026-05-25 08:21:18</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1138,7 +1138,7 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
         <v>1.24</v>
@@ -1150,7 +1150,7 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 06:08:15</t>
+          <t>2026-05-25 08:21:18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.21</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>3.15</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 06:08:15</t>
+          <t>2026-05-25 08:21:18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>1.81</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>3.15</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 06:08:15</t>
+          <t>2026-05-25 08:21:18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="n">
+      <c r="CA6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>1.04</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 06:08:15</t>
+          <t>2026-05-25 08:21:18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>CS Dock Sud</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1.95</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>1.24</v>
       </c>
       <c r="O7" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>4.9</v>
+        <v>1.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 06:08:15</t>
+          <t>2026-05-25 08:21:18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Argentino de Merlo</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.41</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>4.7</v>
+        <v>1.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
-        <v>1.51</v>
+        <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="T8" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 06:08:15</t>
+          <t>2026-05-25 08:21:18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,78 +2621,78 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cusco FC</t>
+          <t>Arsenal de Sarandi</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.12</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H9" t="n">
-        <v>21</v>
-      </c>
-      <c r="I9" t="n">
-        <v>34</v>
-      </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" t="n">
-        <v>14</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.77</v>
-      </c>
       <c r="S9" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="T9" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2701,171 +2701,171 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 06:08:15</t>
+          <t>2026-05-25 08:21:18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.98</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.43</v>
+        <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>1.08</v>
       </c>
       <c r="R10" t="n">
         <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>1.07</v>
       </c>
       <c r="T10" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-25 06:08:15</t>
+          <t>2026-05-25 08:21:18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,498 +3129,2784 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="O11" t="n">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="P11" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.56</v>
+        <v>1.03</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>5.2</v>
+        <v>1.05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-25 06:08:15</t>
+          <t>2026-05-25 08:21:18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Brown de Adrogue</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Talleres (RE)</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K12" t="n">
+        <v>950</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Deportivo Merlo</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CSD Liniers de Ciudad Evita</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Comunicaciones B Aires</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>UAI Urquiza</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K14" t="n">
+        <v>950</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>38</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>10</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LDU</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Always Ready</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="X16" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>380</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CA Ituzaingo</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Deportivo Laferrere</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>12</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Cusco FC</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H19" t="n">
+        <v>21</v>
+      </c>
+      <c r="I19" t="n">
+        <v>34</v>
+      </c>
+      <c r="J19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" t="n">
+        <v>16</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="X19" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>7</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Estudiantes</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Ind Medellin</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="F21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U21" t="n">
         <v>1.71</v>
       </c>
-      <c r="H12" t="n">
+      <c r="V21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB21" t="n">
         <v>6.4</v>
       </c>
-      <c r="I12" t="n">
+      <c r="AC21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>7.6</v>
       </c>
-      <c r="J12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>310</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AR21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ21" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>270</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW12" t="n">
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AX12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA12" t="n">
+      <c r="BT21" t="n">
         <v>10.5</v>
       </c>
-      <c r="BB12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ12" t="n">
+      <c r="BU21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
         <v>12.5</v>
       </c>
-      <c r="BK12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
         <v>12.5</v>
       </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA12" t="n">
+      <c r="BZ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA21" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>2026-05-25 06:08:15</t>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-05-25 08:21:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Armenian Premier League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,234 +843,234 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>04:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Alashkert</t>
+          <t>Taian Tiankuang</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Shirak</t>
+          <t>Dalian Kewei</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.02</v>
+        <v>1.97</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="H2" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="P2" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.15</v>
+        <v>2.44</v>
       </c>
       <c r="R2" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.16</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG2" t="n">
         <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>Shanghai Port B</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>Lanzhou Longyuan Athletic</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1138,31 +1138,31 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1276,72 +1276,72 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Hangzhou Linping Wuyue</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Hubei Istar</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>2.84</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>2.72</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.21</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S4" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Guizhou Zhucheng Athletic</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.24</v>
+        <v>4.1</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38</v>
+        <v>4.4</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.15</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="W5" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>29</v>
+        <v>13.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AB5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD5" t="n">
         <v>13</v>
       </c>
-      <c r="AC5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>18</v>
-      </c>
       <c r="AE5" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
         <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="AK5" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AL5" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="AM5" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="AO5" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.5</v>
+        <v>3.15</v>
       </c>
       <c r="AR5" t="n">
-        <v>17</v>
+        <v>3.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>3.65</v>
       </c>
       <c r="AW5" t="n">
         <v>4.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH5" t="n">
-        <v>3.65</v>
+        <v>2.96</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BO5" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BU5" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,234 +1859,234 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Camioneros</t>
+          <t>Alashkert</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>FC Shirak</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G6" t="n">
+        <v>990</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I6" t="n">
+        <v>990</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K6" t="n">
+        <v>950</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
         <v>1.04</v>
       </c>
-      <c r="G6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
         <v>1.04</v>
       </c>
-      <c r="I6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CS Dock Sud</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M7" t="n">
         <v>1.04</v>
       </c>
-      <c r="G7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="N7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X7" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI7" t="n">
         <v>1.04</v>
       </c>
-      <c r="I7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Czech 1 Liga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,129 +2367,129 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>Banik Ostrava</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Argentino de Merlo</t>
+          <t>MAS Taborsko</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M8" t="n">
         <v>1.04</v>
       </c>
-      <c r="G8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K8" t="n">
-        <v>950</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R8" t="n">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.03</v>
@@ -2501,10 +2501,10 @@
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AV8" t="n">
         <v>1.03</v>
@@ -2513,10 +2513,10 @@
         <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
         <v>1.03</v>
@@ -2525,10 +2525,10 @@
         <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BD8" t="n">
         <v>1.03</v>
@@ -2537,64 +2537,64 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandi</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M9" t="n">
         <v>1.04</v>
       </c>
-      <c r="G9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="N9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI9" t="n">
         <v>1.04</v>
       </c>
-      <c r="I9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.08</v>
+        <v>1.86</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>1.07</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,244 +3129,244 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Argentino de Merlo</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>70</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="n">
+      <c r="CA11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>1.04</v>
-      </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
@@ -3383,105 +3383,105 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Talleres (RE)</t>
+          <t>Arsenal de Sarandi</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -3502,7 +3502,7 @@
         <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP12" t="n">
         <v>1.01</v>
@@ -3538,19 +3538,19 @@
         <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3559,58 +3559,58 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
@@ -3637,171 +3637,171 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CSD Liniers de Ciudad Evita</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R13" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>1.02</v>
+        <v>2.54</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
         <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
         <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
         <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
         <v>1.03</v>
@@ -3813,10 +3813,10 @@
         <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
@@ -3831,7 +3831,7 @@
         <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
@@ -3891,114 +3891,114 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Comunicaciones B Aires</t>
+          <t>CS Dock Sud</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UAI Urquiza</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>3.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N14" t="n">
-        <v>1.24</v>
+        <v>2.16</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="R14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -4013,52 +4013,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -4070,55 +4070,55 @@
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T15" t="n">
         <v>1.11</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.16</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,244 +4399,244 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI16" t="n">
         <v>1.04</v>
       </c>
-      <c r="N16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="X16" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>380</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3.25</v>
-      </c>
       <c r="BJ16" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
@@ -4653,171 +4653,171 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N17" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
         <v>1.12</v>
       </c>
       <c r="S17" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
         <v>1.03</v>
@@ -4829,10 +4829,10 @@
         <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
@@ -4847,7 +4847,7 @@
         <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO17" t="n">
         <v>1.01</v>
@@ -4865,7 +4865,7 @@
         <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU17" t="n">
         <v>1.01</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="G18" t="n">
-        <v>2.06</v>
+        <v>2.66</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="K18" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="M18" t="n">
         <v>1.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P18" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="S18" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="T18" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W18" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="X18" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF18" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AG18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO18" t="n">
         <v>140</v>
       </c>
-      <c r="AB18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>150</v>
-      </c>
       <c r="AP18" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN18" t="n">
         <v>5.3</v>
       </c>
-      <c r="BE18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BO18" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU18" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,244 +5161,244 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Comunicaciones B Aires</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cusco FC</t>
+          <t>UAI Urquiza</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M19" t="n">
         <v>1.12</v>
       </c>
-      <c r="G19" t="n">
+      <c r="N19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.15</v>
       </c>
-      <c r="H19" t="n">
-        <v>21</v>
-      </c>
-      <c r="I19" t="n">
-        <v>34</v>
-      </c>
-      <c r="J19" t="n">
-        <v>10</v>
-      </c>
-      <c r="K19" t="n">
-        <v>16</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="S19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.23</v>
       </c>
-      <c r="M19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.03</v>
-      </c>
       <c r="W19" t="n">
-        <v>7.4</v>
+        <v>1.65</v>
       </c>
       <c r="X19" t="n">
-        <v>950</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y19" t="n">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB19" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ19" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AK19" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AL19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
@@ -5415,87 +5415,87 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I20" t="n">
         <v>5.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="M20" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="O20" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="P20" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.18</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.06</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="V20" t="n">
         <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA20" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC20" t="n">
         <v>8.4</v>
@@ -5507,152 +5507,152 @@
         <v>110</v>
       </c>
       <c r="AF20" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK20" t="n">
         <v>25</v>
       </c>
-      <c r="AI20" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>23</v>
-      </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM20" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AN20" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AO20" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AP20" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ20" t="n">
         <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS20" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY20" t="n">
         <v>10</v>
       </c>
-      <c r="AX20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ20" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC20" t="n">
         <v>21</v>
       </c>
-      <c r="BA20" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD20" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BE20" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF20" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BG20" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BJ20" t="n">
         <v>12</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BP20" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BR20" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT20" t="n">
         <v>9</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA20" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-25 08:21:18</t>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>
@@ -5669,244 +5669,1514 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="G21" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="H21" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="I21" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>2.98</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.26</v>
+        <v>1.63</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="S21" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="V21" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="W21" t="n">
-        <v>2.46</v>
+        <v>3.4</v>
       </c>
       <c r="X21" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>380</v>
+      </c>
+      <c r="AB21" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y21" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>310</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AC21" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AD21" t="n">
         <v>950</v>
       </c>
       <c r="AE21" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF21" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AG21" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
         <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ21" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AK21" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AM21" t="n">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="AN21" t="n">
-        <v>970</v>
+        <v>5.7</v>
       </c>
       <c r="AO21" t="n">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="AP21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB21" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BB21" t="n">
+      <c r="BC21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ21" t="n">
         <v>12</v>
       </c>
-      <c r="BC21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BK21" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BN21" t="n">
         <v>3.95</v>
       </c>
       <c r="BO21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>13</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:35:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CA Ituzaingo</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Deportivo Laferrere</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:35:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>12</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:35:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Cusco FC</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H24" t="n">
+        <v>21</v>
+      </c>
+      <c r="I24" t="n">
+        <v>34</v>
+      </c>
+      <c r="J24" t="n">
+        <v>10</v>
+      </c>
+      <c r="K24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="X24" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:35:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH25" t="n">
         <v>3.1</v>
       </c>
-      <c r="BP21" t="n">
+      <c r="BI25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ25" t="n">
         <v>12</v>
       </c>
-      <c r="BQ21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS21" t="n">
+      <c r="BK25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:35:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>300</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
         <v>10.5</v>
       </c>
-      <c r="BT21" t="n">
+      <c r="BT26" t="n">
         <v>10.5</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="BU26" t="n">
         <v>6.2</v>
       </c>
-      <c r="BV21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>2026-05-25 08:21:18</t>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>10</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:35:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -869,28 +869,28 @@
         <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K2" t="n">
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M2" t="n">
         <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="O2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.52</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.48</v>
-      </c>
       <c r="Q2" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -899,22 +899,22 @@
         <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
         <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z2" t="n">
         <v>40</v>
@@ -923,7 +923,7 @@
         <v>160</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC2" t="n">
         <v>8.6</v>
@@ -947,7 +947,7 @@
         <v>130</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
         <v>36</v>
@@ -956,121 +956,121 @@
         <v>75</v>
       </c>
       <c r="AM2" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AN2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO2" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BN2" t="n">
         <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
         <v>46</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BT2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BV2" t="n">
         <v>55</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>110</v>
+        <v>880</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1132,25 +1132,25 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="H4" t="n">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.47</v>
@@ -1389,7 +1389,7 @@
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O4" t="n">
         <v>1.48</v>
@@ -1410,25 +1410,25 @@
         <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="X4" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AB4" t="n">
         <v>10.5</v>
@@ -1437,28 +1437,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AG4" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
         <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK4" t="n">
         <v>60</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>48</v>
       </c>
       <c r="AL4" t="n">
         <v>75</v>
@@ -1467,70 +1467,70 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AO4" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AP4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>3.55</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3.5</v>
       </c>
       <c r="AR4" t="n">
         <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="n">
         <v>2.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>4.4</v>
       </c>
       <c r="H5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I5" t="n">
         <v>2.2</v>
@@ -1634,16 +1634,16 @@
         <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
         <v>1.45</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O5" t="n">
         <v>1.46</v>
@@ -1790,49 +1790,49 @@
         <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BN5" t="n">
         <v>8</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BT5" t="n">
         <v>4.7</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV5" t="n">
         <v>17</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -1873,109 +1873,109 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="G6" t="n">
-        <v>990</v>
+        <v>1.34</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>990</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X6" t="n">
         <v>950</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -2035,7 +2035,7 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI6" t="n">
         <v>1.04</v>
@@ -2053,10 +2053,10 @@
         <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -2127,67 +2127,67 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="I7" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="V7" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X7" t="n">
         <v>950</v>
       </c>
       <c r="Y7" t="n">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
         <v>27</v>
@@ -2199,158 +2199,158 @@
         <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AG7" t="n">
-        <v>19</v>
+        <v>950</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN7" t="n">
         <v>55</v>
       </c>
-      <c r="AM7" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>40</v>
-      </c>
       <c r="AO7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.85</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX7" t="n">
         <v>4.5</v>
       </c>
-      <c r="AT7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV7" t="n">
+      <c r="AY7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH7" t="n">
         <v>3.8</v>
       </c>
-      <c r="AW7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BN7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H8" t="n">
         <v>13</v>
@@ -2396,7 +2396,7 @@
         <v>5.9</v>
       </c>
       <c r="K8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L8" t="n">
         <v>1.24</v>
@@ -2420,19 +2420,19 @@
         <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U8" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V8" t="n">
         <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="X8" t="n">
         <v>30</v>
@@ -2492,13 +2492,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
@@ -2507,10 +2507,10 @@
         <v>10.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX8" t="n">
         <v>6</v>
@@ -2519,10 +2519,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB8" t="n">
         <v>7.2</v>
@@ -2531,16 +2531,16 @@
         <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BG8" t="n">
-        <v>85</v>
+        <v>4.4</v>
       </c>
       <c r="BH8" t="n">
         <v>4.5</v>
@@ -2552,13 +2552,13 @@
         <v>13.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
         <v>3.85</v>
@@ -2576,25 +2576,25 @@
         <v>25</v>
       </c>
       <c r="BS8" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
         <v>16.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>4.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I9" t="n">
         <v>2.14</v>
@@ -2668,7 +2668,7 @@
         <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="R9" t="n">
         <v>1.49</v>
@@ -2686,7 +2686,7 @@
         <v>1.87</v>
       </c>
       <c r="W9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
         <v>25</v>
@@ -2695,7 +2695,7 @@
         <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA9" t="n">
         <v>29</v>
@@ -2707,7 +2707,7 @@
         <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
         <v>21</v>
@@ -2743,122 +2743,122 @@
         <v>13</v>
       </c>
       <c r="AP9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX9" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AY9" t="n">
         <v>3.8</v>
       </c>
-      <c r="AR9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="AZ9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC9" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BD9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.2</v>
       </c>
-      <c r="AU9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BG9" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="BH9" t="n">
         <v>4.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BT9" t="n">
         <v>5.3</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.32</v>
@@ -2913,13 +2913,13 @@
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O10" t="n">
         <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
         <v>1.86</v>
@@ -2940,7 +2940,7 @@
         <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X10" t="n">
         <v>18.5</v>
@@ -2949,10 +2949,10 @@
         <v>14.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
         <v>13</v>
@@ -2961,10 +2961,10 @@
         <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
         <v>18.5</v>
@@ -2994,7 +2994,7 @@
         <v>22</v>
       </c>
       <c r="AO10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP10" t="n">
         <v>11</v>
@@ -3006,7 +3006,7 @@
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT10" t="n">
         <v>7.8</v>
@@ -3030,25 +3030,25 @@
         <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.2</v>
+        <v>34</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC10" t="n">
         <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF10" t="n">
         <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH10" t="n">
         <v>3.65</v>
@@ -3060,13 +3060,13 @@
         <v>9.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN10" t="n">
         <v>5.5</v>
@@ -3075,44 +3075,44 @@
         <v>4</v>
       </c>
       <c r="BP10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
         <v>7.6</v>
       </c>
-      <c r="BT10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>26</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="G11" t="n">
         <v>3.6</v>
       </c>
       <c r="H11" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J11" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="K11" t="n">
         <v>3.1</v>
@@ -3164,7 +3164,7 @@
         <v>1.6</v>
       </c>
       <c r="M11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N11" t="n">
         <v>2.06</v>
@@ -3176,13 +3176,13 @@
         <v>1.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T11" t="n">
         <v>2.28</v>
@@ -3191,10 +3191,10 @@
         <v>1.61</v>
       </c>
       <c r="V11" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X11" t="n">
         <v>7.8</v>
@@ -3203,40 +3203,40 @@
         <v>8.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK11" t="n">
         <v>70</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>65</v>
       </c>
       <c r="AL11" t="n">
         <v>120</v>
@@ -3245,64 +3245,64 @@
         <v>320</v>
       </c>
       <c r="AN11" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AO11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH11" t="n">
         <v>2.5</v>
@@ -3314,49 +3314,49 @@
         <v>13</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BN11" t="n">
         <v>6.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BR11" t="n">
         <v>70</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BX11" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>2.62</v>
       </c>
       <c r="J12" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="K12" t="n">
         <v>3.45</v>
@@ -3448,13 +3448,13 @@
         <v>1.61</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
         <v>15</v>
@@ -3463,13 +3463,13 @@
         <v>40</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
         <v>40</v>
@@ -3505,58 +3505,58 @@
         <v>42</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH12" t="n">
         <v>2.78</v>
@@ -3568,7 +3568,7 @@
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.08</v>
+        <v>4.9</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3586,7 +3586,7 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -3660,10 +3660,10 @@
         <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J13" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="K13" t="n">
         <v>3.6</v>
@@ -3684,13 +3684,13 @@
         <v>1.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="R13" t="n">
         <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
         <v>2.18</v>
@@ -3699,16 +3699,16 @@
         <v>1.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="X13" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
         <v>44</v>
@@ -3717,22 +3717,22 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
         <v>120</v>
       </c>
       <c r="AF13" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
         <v>32</v>
@@ -3741,10 +3741,10 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL13" t="n">
         <v>80</v>
@@ -3753,64 +3753,64 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="n">
         <v>2.8</v>
@@ -3822,49 +3822,49 @@
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BN13" t="n">
         <v>4.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -3905,76 +3905,76 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="G14" t="n">
         <v>3.7</v>
       </c>
       <c r="H14" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I14" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="L14" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="M14" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="N14" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="O14" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="P14" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
         <v>1.37</v>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
         <v>19</v>
@@ -3995,10 +3995,10 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -4067,16 +4067,16 @@
         <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.1</v>
       </c>
       <c r="O15" t="n">
         <v>1.03</v>
@@ -4204,7 +4204,7 @@
         <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
         <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
         <v>8.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE17" t="n">
         <v>65</v>
@@ -4748,7 +4748,7 @@
         <v>24</v>
       </c>
       <c r="AG17" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
         <v>34</v>
@@ -4775,58 +4775,58 @@
         <v>95</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH17" t="n">
         <v>2.58</v>
@@ -4838,49 +4838,49 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BN17" t="n">
         <v>6.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT17" t="n">
         <v>6.2</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>2.14</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H18" t="n">
         <v>3.35</v>
@@ -4933,7 +4933,7 @@
         <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
@@ -4945,7 +4945,7 @@
         <v>1.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="O18" t="n">
         <v>1.54</v>
@@ -4954,7 +4954,7 @@
         <v>1.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R18" t="n">
         <v>1.15</v>
@@ -4972,7 +4972,7 @@
         <v>1.26</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X18" t="n">
         <v>9.199999999999999</v>
@@ -5029,58 +5029,58 @@
         <v>140</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH18" t="n">
         <v>2.78</v>
@@ -5092,49 +5092,49 @@
         <v>13</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BN18" t="n">
         <v>5.3</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP18" t="n">
         <v>23</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT18" t="n">
         <v>7.8</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -5175,73 +5175,73 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G19" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="n">
         <v>2.68</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L19" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="N19" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="O19" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="P19" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="R19" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>1.02</v>
+        <v>3.95</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
         <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X19" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA19" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AC19" t="n">
         <v>8.4</v>
@@ -5250,91 +5250,91 @@
         <v>23</v>
       </c>
       <c r="AE19" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI19" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AJ19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK19" t="n">
         <v>40</v>
       </c>
       <c r="AL19" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN19" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G20" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I20" t="n">
         <v>5.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
         <v>3.55</v>
@@ -5459,13 +5459,13 @@
         <v>1.49</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q20" t="n">
         <v>2.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
         <v>4.9</v>
@@ -5480,10 +5480,10 @@
         <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X20" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="n">
         <v>15</v>
@@ -5501,7 +5501,7 @@
         <v>8.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
         <v>110</v>
@@ -5516,10 +5516,10 @@
         <v>28</v>
       </c>
       <c r="AI20" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="n">
         <v>25</v>
@@ -5531,7 +5531,7 @@
         <v>210</v>
       </c>
       <c r="AN20" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AO20" t="n">
         <v>180</v>
@@ -5546,7 +5546,7 @@
         <v>32</v>
       </c>
       <c r="AS20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT20" t="n">
         <v>5.8</v>
@@ -5558,10 +5558,10 @@
         <v>18</v>
       </c>
       <c r="AW20" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY20" t="n">
         <v>10</v>
@@ -5570,7 +5570,7 @@
         <v>23</v>
       </c>
       <c r="BA20" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB20" t="n">
         <v>18</v>
@@ -5582,19 +5582,19 @@
         <v>46</v>
       </c>
       <c r="BE20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF20" t="n">
         <v>17</v>
       </c>
       <c r="BG20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH20" t="n">
         <v>2.88</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="BJ20" t="n">
         <v>12</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -5689,13 +5689,13 @@
         <v>1.4</v>
       </c>
       <c r="H21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I21" t="n">
         <v>11</v>
       </c>
       <c r="J21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
@@ -5707,7 +5707,7 @@
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O21" t="n">
         <v>1.22</v>
@@ -5734,7 +5734,7 @@
         <v>1.1</v>
       </c>
       <c r="W21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="X21" t="n">
         <v>28</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -6194,22 +6194,22 @@
         <v>1.96</v>
       </c>
       <c r="G23" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H23" t="n">
         <v>4.7</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="M23" t="n">
         <v>1.12</v>
@@ -6233,22 +6233,22 @@
         <v>5.2</v>
       </c>
       <c r="T23" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U23" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V23" t="n">
         <v>1.24</v>
       </c>
       <c r="W23" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X23" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z23" t="n">
         <v>36</v>
@@ -6260,7 +6260,7 @@
         <v>6.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD23" t="n">
         <v>970</v>
@@ -6269,7 +6269,7 @@
         <v>90</v>
       </c>
       <c r="AF23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG23" t="n">
         <v>13.5</v>
@@ -6281,19 +6281,19 @@
         <v>110</v>
       </c>
       <c r="AJ23" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
         <v>34</v>
       </c>
       <c r="AL23" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM23" t="n">
         <v>240</v>
       </c>
       <c r="AN23" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO23" t="n">
         <v>150</v>
@@ -6305,10 +6305,10 @@
         <v>11</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT23" t="n">
         <v>5.8</v>
@@ -6320,7 +6320,7 @@
         <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX23" t="n">
         <v>9.4</v>
@@ -6329,28 +6329,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB23" t="n">
         <v>17.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF23" t="n">
         <v>17.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH23" t="n">
         <v>2.76</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="G24" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J24" t="n">
         <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="L24" t="n">
         <v>1.23</v>
@@ -6469,34 +6469,34 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O24" t="n">
         <v>1.14</v>
       </c>
       <c r="P24" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R24" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="S24" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T24" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="X24" t="n">
         <v>950</v>
@@ -6523,7 +6523,7 @@
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG24" t="n">
         <v>970</v>
@@ -6532,10 +6532,10 @@
         <v>950</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AJ24" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AK24" t="n">
         <v>970</v>
@@ -6553,16 +6553,16 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AR24" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT24" t="n">
         <v>8.6</v>
@@ -6571,10 +6571,10 @@
         <v>20</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX24" t="n">
         <v>6</v>
@@ -6583,31 +6583,31 @@
         <v>11.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB24" t="n">
         <v>5.8</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH24" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>5.3</v>
       </c>
       <c r="BI24" t="n">
         <v>4.7</v>
@@ -6616,22 +6616,22 @@
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>3.9</v>
+        <v>13.5</v>
       </c>
       <c r="BN24" t="n">
         <v>3.65</v>
       </c>
       <c r="BO24" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BP24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BQ24" t="n">
         <v>4.7</v>
@@ -6640,25 +6640,25 @@
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>3.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT24" t="n">
         <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.45</v>
+        <v>9.4</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>3.9</v>
+        <v>13.5</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="BZ24" t="n">
         <v>6.8</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G25" t="n">
         <v>1.88</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.9</v>
       </c>
       <c r="H25" t="n">
         <v>5.2</v>
       </c>
       <c r="I25" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
         <v>1.43</v>
@@ -6732,7 +6732,7 @@
         <v>1.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R25" t="n">
         <v>1.24</v>
@@ -6747,10 +6747,10 @@
         <v>1.78</v>
       </c>
       <c r="V25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X25" t="n">
         <v>11</v>
@@ -6813,7 +6813,7 @@
         <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="AS25" t="n">
         <v>10.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G26" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H26" t="n">
         <v>6.8</v>
@@ -6965,13 +6965,13 @@
         <v>7.6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
@@ -6983,7 +6983,7 @@
         <v>1.43</v>
       </c>
       <c r="P26" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q26" t="n">
         <v>2.28</v>
@@ -6998,13 +6998,13 @@
         <v>2.24</v>
       </c>
       <c r="U26" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V26" t="n">
         <v>1.15</v>
       </c>
       <c r="W26" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="X26" t="n">
         <v>11.5</v>
@@ -7061,7 +7061,7 @@
         <v>270</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ26" t="n">
         <v>7.6</v>
@@ -7136,7 +7136,7 @@
         <v>3.9</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BP26" t="n">
         <v>12</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-25 10:35:46</t>
+          <t>2026-05-25 12:48:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>2.32</v>
@@ -869,40 +869,40 @@
         <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="P2" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U2" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="V2" t="n">
         <v>1.21</v>
@@ -911,10 +911,10 @@
         <v>1.75</v>
       </c>
       <c r="X2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
         <v>40</v>
@@ -923,10 +923,10 @@
         <v>160</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
         <v>24</v>
@@ -965,67 +965,67 @@
         <v>180</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV2" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF2" t="n">
         <v>4.9</v>
       </c>
-      <c r="BE2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG2" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK2" t="n">
         <v>5.5</v>
@@ -1034,43 +1034,43 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BN2" t="n">
         <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU2" t="n">
         <v>4.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>880</v>
+        <v>970</v>
       </c>
       <c r="H3" t="n">
         <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>210</v>
+        <v>870</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1135,16 +1135,16 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="G4" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="J4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K4" t="n">
         <v>3.4</v>
@@ -1389,7 +1389,7 @@
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O4" t="n">
         <v>1.48</v>
@@ -1413,22 +1413,22 @@
         <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="W4" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z4" t="n">
         <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB4" t="n">
         <v>10.5</v>
@@ -1440,7 +1440,7 @@
         <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF4" t="n">
         <v>26</v>
@@ -1470,100 +1470,100 @@
         <v>75</v>
       </c>
       <c r="AO4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AQ4" t="n">
         <v>3.55</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BC4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG4" t="n">
         <v>5.1</v>
       </c>
-      <c r="BD4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE4" t="n">
+      <c r="BH4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
       </c>
       <c r="BU4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
         <v>2.96</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="BJ5" t="n">
         <v>11.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="G6" t="n">
         <v>1.34</v>
       </c>
       <c r="H6" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.27</v>
@@ -1897,22 +1897,22 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="R6" t="n">
         <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="T6" t="n">
         <v>2.22</v>
@@ -1924,7 +1924,7 @@
         <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="X6" t="n">
         <v>950</v>
@@ -1933,7 +1933,7 @@
         <v>950</v>
       </c>
       <c r="Z6" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1942,7 +1942,7 @@
         <v>9.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
         <v>950</v>
@@ -1954,7 +1954,7 @@
         <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
         <v>950</v>
@@ -1963,10 +1963,10 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK6" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AL6" t="n">
         <v>60</v>
@@ -1981,76 +1981,76 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH6" t="n">
         <v>4.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BN6" t="n">
         <v>3.75</v>
@@ -2062,31 +2062,31 @@
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -2133,13 +2133,13 @@
         <v>4.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="I7" t="n">
         <v>2.08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
         <v>4.2</v>
@@ -2166,10 +2166,10 @@
         <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="T7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
         <v>2.14</v>
@@ -2178,10 +2178,10 @@
         <v>1.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X7" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
         <v>12</v>
@@ -2190,10 +2190,10 @@
         <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AB7" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
         <v>10.5</v>
@@ -2205,7 +2205,7 @@
         <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG7" t="n">
         <v>950</v>
@@ -2232,7 +2232,7 @@
         <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AP7" t="n">
         <v>13</v>
@@ -2244,7 +2244,7 @@
         <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT7" t="n">
         <v>12.5</v>
@@ -2259,7 +2259,7 @@
         <v>15</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AY7" t="n">
         <v>13</v>
@@ -2268,22 +2268,22 @@
         <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.7</v>
+        <v>36</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BG7" t="n">
         <v>9.4</v>
@@ -2292,7 +2292,7 @@
         <v>3.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.800000000000001</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="G8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H8" t="n">
         <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="J8" t="n">
         <v>5.9</v>
       </c>
       <c r="K8" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.24</v>
@@ -2429,19 +2429,19 @@
         <v>1.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X8" t="n">
         <v>30</v>
       </c>
       <c r="Y8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z8" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -2456,7 +2456,7 @@
         <v>60</v>
       </c>
       <c r="AE8" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AF8" t="n">
         <v>9.6</v>
@@ -2468,7 +2468,7 @@
         <v>42</v>
       </c>
       <c r="AI8" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ8" t="n">
         <v>12</v>
@@ -2486,7 +2486,7 @@
         <v>5.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="AP8" t="n">
         <v>17.5</v>
@@ -2495,10 +2495,10 @@
         <v>4.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
@@ -2507,7 +2507,7 @@
         <v>10.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW8" t="n">
         <v>4.4</v>
@@ -2519,7 +2519,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA8" t="n">
         <v>4.4</v>
@@ -2540,7 +2540,7 @@
         <v>3.65</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH8" t="n">
         <v>4.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -2635,79 +2635,79 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="G9" t="n">
         <v>4.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="I9" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N9" t="n">
         <v>4.4</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.7</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="U9" t="n">
         <v>2.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="W9" t="n">
         <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
         <v>21</v>
@@ -2740,125 +2740,125 @@
         <v>42</v>
       </c>
       <c r="AO9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT9" t="n">
         <v>13</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AU9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH9" t="n">
         <v>3.95</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY9" t="n">
+      <c r="BI9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU9" t="n">
         <v>3.8</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.98</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.32</v>
@@ -2946,7 +2946,7 @@
         <v>18.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
         <v>28</v>
@@ -2955,10 +2955,10 @@
         <v>60</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
         <v>17.5</v>
@@ -2991,10 +2991,10 @@
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO10" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP10" t="n">
         <v>11</v>
@@ -3006,7 +3006,7 @@
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
         <v>7.8</v>
@@ -3018,7 +3018,7 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -3033,22 +3033,22 @@
         <v>34</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BC10" t="n">
         <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF10" t="n">
         <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="n">
         <v>3.65</v>
@@ -3072,7 +3072,7 @@
         <v>5.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP10" t="n">
         <v>18</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.92</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H11" t="n">
         <v>2.76</v>
@@ -3155,7 +3155,7 @@
         <v>3.45</v>
       </c>
       <c r="J11" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="K11" t="n">
         <v>3.1</v>
@@ -3191,7 +3191,7 @@
         <v>1.61</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
         <v>1.4</v>
@@ -3251,7 +3251,7 @@
         <v>90</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>3.25</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
         <v>2.1</v>
@@ -3409,7 +3409,7 @@
         <v>2.62</v>
       </c>
       <c r="J12" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="K12" t="n">
         <v>3.45</v>
@@ -3421,7 +3421,7 @@
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
         <v>1.53</v>
@@ -3448,10 +3448,10 @@
         <v>1.61</v>
       </c>
       <c r="W12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y12" t="n">
         <v>970</v>
@@ -3508,55 +3508,55 @@
         <v>3.3</v>
       </c>
       <c r="AQ12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU12" t="n">
         <v>3.15</v>
       </c>
-      <c r="AR12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AV12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG12" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.7</v>
       </c>
       <c r="BH12" t="n">
         <v>2.78</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="O13" t="n">
         <v>1.53</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
         <v>3.7</v>
@@ -3953,13 +3953,13 @@
         <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W14" t="n">
         <v>1.37</v>
       </c>
       <c r="X14" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
         <v>8.199999999999999</v>
@@ -3971,13 +3971,13 @@
         <v>70</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
         <v>70</v>
@@ -3986,7 +3986,7 @@
         <v>23</v>
       </c>
       <c r="AG14" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
         <v>34</v>
@@ -4013,37 +4013,37 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
         <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
         <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
         <v>1.03</v>
@@ -4076,49 +4076,49 @@
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>9.800000000000001</v>
+        <v>1.66</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>8.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.800000000000001</v>
+        <v>1.59</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.800000000000001</v>
+        <v>1.63</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.800000000000001</v>
+        <v>1.59</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.800000000000001</v>
+        <v>1.66</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O15" t="n">
         <v>1.03</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -4437,22 +4437,22 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P16" t="n">
         <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="R16" t="n">
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>2.14</v>
       </c>
       <c r="G18" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H18" t="n">
         <v>3.35</v>
@@ -4933,7 +4933,7 @@
         <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
@@ -4972,7 +4972,7 @@
         <v>1.26</v>
       </c>
       <c r="W18" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X18" t="n">
         <v>9.199999999999999</v>
@@ -4987,7 +4987,7 @@
         <v>120</v>
       </c>
       <c r="AB18" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC18" t="n">
         <v>8.199999999999999</v>
@@ -5029,58 +5029,58 @@
         <v>140</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT18" t="n">
         <v>3.15</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF18" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BG18" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>5</v>
       </c>
       <c r="BH18" t="n">
         <v>2.78</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>2.04</v>
       </c>
       <c r="G19" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H19" t="n">
         <v>3.9</v>
@@ -5187,7 +5187,7 @@
         <v>5.4</v>
       </c>
       <c r="J19" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="K19" t="n">
         <v>3.35</v>
@@ -5199,7 +5199,7 @@
         <v>1.15</v>
       </c>
       <c r="N19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="O19" t="n">
         <v>1.61</v>
@@ -5226,7 +5226,7 @@
         <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X19" t="n">
         <v>7.6</v>
@@ -5235,7 +5235,7 @@
         <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA19" t="n">
         <v>150</v>
@@ -5244,7 +5244,7 @@
         <v>7</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD19" t="n">
         <v>23</v>
@@ -5253,10 +5253,10 @@
         <v>110</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
         <v>32</v>
@@ -5265,7 +5265,7 @@
         <v>150</v>
       </c>
       <c r="AJ19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK19" t="n">
         <v>40</v>
@@ -5283,58 +5283,58 @@
         <v>200</v>
       </c>
       <c r="AP19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT19" t="n">
         <v>3.35</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AU19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF19" t="n">
         <v>5.6</v>
       </c>
-      <c r="BE19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG19" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="G20" t="n">
         <v>1.89</v>
@@ -5438,7 +5438,7 @@
         <v>5.5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J20" t="n">
         <v>3.45</v>
@@ -5477,10 +5477,10 @@
         <v>1.73</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X20" t="n">
         <v>10</v>
@@ -5498,10 +5498,10 @@
         <v>6.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
         <v>110</v>
@@ -5519,7 +5519,7 @@
         <v>130</v>
       </c>
       <c r="AJ20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK20" t="n">
         <v>25</v>
@@ -5528,7 +5528,7 @@
         <v>60</v>
       </c>
       <c r="AM20" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN20" t="n">
         <v>19.5</v>
@@ -5546,7 +5546,7 @@
         <v>32</v>
       </c>
       <c r="AS20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT20" t="n">
         <v>5.8</v>
@@ -5561,7 +5561,7 @@
         <v>13.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY20" t="n">
         <v>10</v>
@@ -5570,10 +5570,10 @@
         <v>23</v>
       </c>
       <c r="BA20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC20" t="n">
         <v>21</v>
@@ -5582,13 +5582,13 @@
         <v>46</v>
       </c>
       <c r="BE20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF20" t="n">
         <v>17</v>
       </c>
       <c r="BG20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH20" t="n">
         <v>2.88</v>
@@ -5612,7 +5612,7 @@
         <v>4.3</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BP20" t="n">
         <v>14.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G21" t="n">
         <v>1.4</v>
@@ -5692,7 +5692,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J21" t="n">
         <v>5.4</v>
@@ -5731,7 +5731,7 @@
         <v>1.86</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
         <v>3.45</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>2.04</v>
       </c>
       <c r="H23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I23" t="n">
         <v>5.1</v>
@@ -6206,7 +6206,7 @@
         <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.57</v>
@@ -6221,7 +6221,7 @@
         <v>1.54</v>
       </c>
       <c r="P23" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q23" t="n">
         <v>2.58</v>
@@ -6230,7 +6230,7 @@
         <v>1.2</v>
       </c>
       <c r="S23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="T23" t="n">
         <v>2.26</v>
@@ -6239,16 +6239,16 @@
         <v>1.7</v>
       </c>
       <c r="V23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
         <v>1.96</v>
       </c>
       <c r="X23" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z23" t="n">
         <v>36</v>
@@ -6272,7 +6272,7 @@
         <v>10.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
         <v>30</v>
@@ -6281,7 +6281,7 @@
         <v>110</v>
       </c>
       <c r="AJ23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK23" t="n">
         <v>34</v>
@@ -6293,7 +6293,7 @@
         <v>240</v>
       </c>
       <c r="AN23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO23" t="n">
         <v>150</v>
@@ -6305,13 +6305,13 @@
         <v>11</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU23" t="n">
         <v>7.2</v>
@@ -6320,7 +6320,7 @@
         <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX23" t="n">
         <v>9.4</v>
@@ -6338,19 +6338,19 @@
         <v>17.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF23" t="n">
         <v>17.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH23" t="n">
         <v>2.76</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -6451,13 +6451,13 @@
         <v>1.15</v>
       </c>
       <c r="H24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I24" t="n">
         <v>36</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
@@ -6469,25 +6469,25 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="R24" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="S24" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="U24" t="n">
         <v>1.5</v>
@@ -6511,7 +6511,7 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AC24" t="n">
         <v>950</v>
@@ -6526,7 +6526,7 @@
         <v>8</v>
       </c>
       <c r="AG24" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AH24" t="n">
         <v>950</v>
@@ -6535,7 +6535,7 @@
         <v>480</v>
       </c>
       <c r="AJ24" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AK24" t="n">
         <v>970</v>
@@ -6553,28 +6553,28 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.2</v>
+        <v>3.35</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU24" t="n">
         <v>20</v>
       </c>
       <c r="AV24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW24" t="n">
         <v>6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>6.4</v>
       </c>
       <c r="AX24" t="n">
         <v>6</v>
@@ -6583,28 +6583,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.4</v>
+        <v>3.35</v>
       </c>
       <c r="BB24" t="n">
         <v>5.8</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.4</v>
+        <v>3.35</v>
       </c>
       <c r="BF24" t="n">
-        <v>2.32</v>
+        <v>2.58</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="BH24" t="n">
         <v>5.4</v>
@@ -6628,7 +6628,7 @@
         <v>3.65</v>
       </c>
       <c r="BO24" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="BP24" t="n">
         <v>5.4</v>
@@ -6664,11 +6664,11 @@
         <v>6.8</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -6702,28 +6702,28 @@
         <v>1.87</v>
       </c>
       <c r="G25" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="H25" t="n">
         <v>5.2</v>
       </c>
       <c r="I25" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J25" t="n">
         <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L25" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
         <v>1.43</v>
@@ -6744,19 +6744,19 @@
         <v>2.08</v>
       </c>
       <c r="U25" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V25" t="n">
         <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X25" t="n">
         <v>11</v>
       </c>
       <c r="Y25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z25" t="n">
         <v>42</v>
@@ -6765,7 +6765,7 @@
         <v>160</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC25" t="n">
         <v>8.4</v>
@@ -6795,28 +6795,28 @@
         <v>23</v>
       </c>
       <c r="AL25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM25" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN25" t="n">
         <v>17.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ25" t="n">
         <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT25" t="n">
         <v>6.2</v>
@@ -6828,7 +6828,7 @@
         <v>19</v>
       </c>
       <c r="AW25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX25" t="n">
         <v>8.6</v>
@@ -6840,25 +6840,25 @@
         <v>21</v>
       </c>
       <c r="BA25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB25" t="n">
         <v>17.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD25" t="n">
         <v>42</v>
       </c>
       <c r="BE25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF25" t="n">
         <v>14.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH25" t="n">
         <v>3.1</v>
@@ -6882,7 +6882,7 @@
         <v>4.4</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BP25" t="n">
         <v>14.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>
@@ -6953,25 +6953,25 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G26" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="H26" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="I26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J26" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K26" t="n">
         <v>4.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
@@ -6995,31 +6995,31 @@
         <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U26" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V26" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W26" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="X26" t="n">
         <v>11.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Z26" t="n">
         <v>60</v>
       </c>
       <c r="AA26" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC26" t="n">
         <v>970</v>
@@ -7061,16 +7061,16 @@
         <v>270</v>
       </c>
       <c r="AP26" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ26" t="n">
         <v>7.6</v>
       </c>
       <c r="AR26" t="n">
-        <v>36</v>
+        <v>3.25</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.96</v>
+        <v>2.56</v>
       </c>
       <c r="AT26" t="n">
         <v>5.8</v>
@@ -7079,40 +7079,40 @@
         <v>7.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AX26" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AY26" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.55</v>
+        <v>2.54</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.96</v>
+        <v>2.56</v>
       </c>
       <c r="BF26" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.96</v>
+        <v>2.56</v>
       </c>
       <c r="BH26" t="n">
         <v>3.05</v>
@@ -7136,7 +7136,7 @@
         <v>3.9</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BP26" t="n">
         <v>12</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-25 12:48:21</t>
+          <t>2026-05-25 14:59:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G2" t="n">
         <v>2.32</v>
@@ -866,37 +866,37 @@
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="K2" t="n">
         <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N2" t="n">
         <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T2" t="n">
         <v>2.22</v>
@@ -905,7 +905,7 @@
         <v>1.61</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
         <v>1.75</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -1111,49 +1111,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I3" t="n">
         <v>970</v>
       </c>
-      <c r="H3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I3" t="n">
-        <v>870</v>
-      </c>
       <c r="J3" t="n">
-        <v>1.19</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="O3" t="n">
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S3" t="n">
-        <v>1.51</v>
+        <v>2.52</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U3" t="n">
         <v>1.01</v>
@@ -1162,10 +1162,10 @@
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
         <v>1000</v>
@@ -1222,55 +1222,55 @@
         <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G4" t="n">
         <v>3.9</v>
@@ -1374,10 +1374,10 @@
         <v>2.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J4" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="K4" t="n">
         <v>3.4</v>
@@ -1413,7 +1413,7 @@
         <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W4" t="n">
         <v>1.35</v>
@@ -1476,61 +1476,61 @@
         <v>3.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BA4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC4" t="n">
+      <c r="BD4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG4" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>5.1</v>
       </c>
       <c r="BH4" t="n">
         <v>2.92</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -1619,25 +1619,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="H5" t="n">
         <v>2.06</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1667,7 +1667,7 @@
         <v>1.79</v>
       </c>
       <c r="V5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W5" t="n">
         <v>1.3</v>
@@ -1784,7 +1784,7 @@
         <v>2.96</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="BJ5" t="n">
         <v>11.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -1873,28 +1873,28 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="H6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J6" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="K6" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
         <v>4.3</v>
@@ -1903,67 +1903,67 @@
         <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R6" t="n">
         <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
         <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Y6" t="n">
         <v>950</v>
       </c>
       <c r="Z6" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
         <v>950</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ6" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AK6" t="n">
         <v>970</v>
@@ -1972,10 +1972,10 @@
         <v>60</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1984,58 +1984,58 @@
         <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
         <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY6" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
         <v>7.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH6" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4.2</v>
       </c>
       <c r="BI6" t="n">
         <v>2.94</v>
@@ -2044,49 +2044,49 @@
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="BN6" t="n">
         <v>3.75</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -2133,19 +2133,19 @@
         <v>4.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="I7" t="n">
         <v>2.08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
         <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
@@ -2208,7 +2208,7 @@
         <v>34</v>
       </c>
       <c r="AG7" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
@@ -2268,10 +2268,10 @@
         <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC7" t="n">
         <v>36</v>
@@ -2280,7 +2280,7 @@
         <v>5</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF7" t="n">
         <v>4.9</v>
@@ -2292,7 +2292,7 @@
         <v>3.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.800000000000001</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G8" t="n">
         <v>1.31</v>
@@ -2390,13 +2390,13 @@
         <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.24</v>
@@ -2408,13 +2408,13 @@
         <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
         <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R8" t="n">
         <v>1.54</v>
@@ -2429,7 +2429,7 @@
         <v>1.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
         <v>4.2</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="G9" t="n">
         <v>4.4</v>
@@ -2644,16 +2644,16 @@
         <v>1.92</v>
       </c>
       <c r="I9" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
         <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
@@ -2662,31 +2662,31 @@
         <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
         <v>2.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
         <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T9" t="n">
         <v>1.67</v>
       </c>
       <c r="U9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X9" t="n">
         <v>23</v>
@@ -2710,7 +2710,7 @@
         <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF9" t="n">
         <v>38</v>
@@ -2746,16 +2746,16 @@
         <v>13.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>16.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="AU9" t="n">
         <v>6.8</v>
@@ -2767,7 +2767,7 @@
         <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
@@ -2776,28 +2776,28 @@
         <v>12</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC9" t="n">
         <v>5.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE9" t="n">
         <v>6</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI9" t="n">
         <v>3.05</v>
@@ -2830,7 +2830,7 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT9" t="n">
         <v>5</v>
@@ -2848,17 +2848,17 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J10" t="n">
         <v>3.55</v>
@@ -2913,19 +2913,19 @@
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
         <v>3.15</v>
@@ -2934,13 +2934,13 @@
         <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X10" t="n">
         <v>18.5</v>
@@ -2961,40 +2961,40 @@
         <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ10" t="n">
         <v>36</v>
       </c>
       <c r="AK10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL10" t="n">
         <v>38</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AP10" t="n">
         <v>11</v>
@@ -3006,7 +3006,7 @@
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AT10" t="n">
         <v>7.8</v>
@@ -3018,7 +3018,7 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -3033,22 +3033,22 @@
         <v>34</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC10" t="n">
         <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF10" t="n">
         <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="n">
         <v>3.65</v>
@@ -3072,10 +3072,10 @@
         <v>5.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ10" t="n">
         <v>6.6</v>
@@ -3084,7 +3084,7 @@
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT10" t="n">
         <v>6.8</v>
@@ -3093,7 +3093,7 @@
         <v>4.9</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW10" t="n">
         <v>7.6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -3143,220 +3143,220 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="G11" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="I11" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
         <v>1.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="O11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="R11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="X11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB11" t="n">
         <v>7.8</v>
       </c>
-      <c r="Y11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>9</v>
-      </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF11" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AG11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR11" t="n">
         <v>18.5</v>
       </c>
-      <c r="AH11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AS11" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.15</v>
+        <v>5.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>4</v>
+        <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO11" t="n">
         <v>4.1</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE11" t="n">
+      <c r="BP11" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU11" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>36</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>70</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BV11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.92</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.98</v>
+        <v>10</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -3397,70 +3397,70 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="I12" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="J12" t="n">
         <v>2.74</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="M12" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="P12" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="R12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="U12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.64</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.61</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z12" t="n">
         <v>970</v>
       </c>
-      <c r="Z12" t="n">
-        <v>15</v>
-      </c>
       <c r="AA12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AB12" t="n">
         <v>970</v>
@@ -3472,28 +3472,28 @@
         <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AG12" t="n">
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK12" t="n">
         <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -3502,115 +3502,115 @@
         <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.15</v>
+        <v>5.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.38</v>
+        <v>5.8</v>
       </c>
       <c r="BB12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
         <v>2.4</v>
       </c>
-      <c r="BC12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>1.07</v>
-      </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.06</v>
+        <v>2.56</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>2.3</v>
@@ -3660,46 +3660,46 @@
         <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="M13" t="n">
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P13" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="T13" t="n">
         <v>2.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
         <v>1.77</v>
@@ -3711,22 +3711,22 @@
         <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB13" t="n">
         <v>6.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AF13" t="n">
         <v>970</v>
@@ -3735,13 +3735,13 @@
         <v>970</v>
       </c>
       <c r="AH13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>32</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>29</v>
       </c>
       <c r="AK13" t="n">
         <v>34</v>
@@ -3759,112 +3759,112 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO13" t="n">
         <v>3.7</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU13" t="n">
         <v>6</v>
       </c>
-      <c r="AT13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -3905,70 +3905,70 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H14" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J14" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="K14" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="M14" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="N14" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="O14" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="P14" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="U14" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="V14" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB14" t="n">
         <v>970</v>
@@ -3980,10 +3980,10 @@
         <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG14" t="n">
         <v>970</v>
@@ -3995,130 +3995,130 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
         <v>80</v>
       </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.66</v>
+        <v>6.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.63</v>
+        <v>1.05</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.66</v>
+        <v>1.05</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4183,142 +4183,142 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.26</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
         <v>1.03</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="S15" t="n">
-        <v>1.05</v>
+        <v>1.45</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="U15" t="n">
         <v>3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
         <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -4413,112 +4413,112 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>1.26</v>
+        <v>6.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>2.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.09</v>
+        <v>1.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="S16" t="n">
-        <v>1.09</v>
+        <v>2.12</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="U16" t="n">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AP16" t="n">
         <v>1.01</v>
@@ -4539,13 +4539,13 @@
         <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
         <v>1.01</v>
@@ -4554,7 +4554,7 @@
         <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
         <v>1.01</v>
@@ -4572,13 +4572,13 @@
         <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
@@ -4611,10 +4611,10 @@
         <v>1.04</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>2.14</v>
       </c>
       <c r="G18" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="H18" t="n">
         <v>3.35</v>
@@ -4933,7 +4933,7 @@
         <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
@@ -4972,7 +4972,7 @@
         <v>1.26</v>
       </c>
       <c r="W18" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="X18" t="n">
         <v>9.199999999999999</v>
@@ -4987,7 +4987,7 @@
         <v>120</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC18" t="n">
         <v>8.199999999999999</v>
@@ -5029,58 +5029,58 @@
         <v>140</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT18" t="n">
         <v>3.15</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AW18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG18" t="n">
         <v>5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>5.1</v>
       </c>
       <c r="BH18" t="n">
         <v>2.78</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>2.04</v>
       </c>
       <c r="G19" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H19" t="n">
         <v>3.9</v>
@@ -5187,7 +5187,7 @@
         <v>5.4</v>
       </c>
       <c r="J19" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="K19" t="n">
         <v>3.35</v>
@@ -5205,7 +5205,7 @@
         <v>1.61</v>
       </c>
       <c r="P19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q19" t="n">
         <v>2.72</v>
@@ -5226,7 +5226,7 @@
         <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X19" t="n">
         <v>7.6</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -5429,49 +5429,49 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="G20" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="H20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I20" t="n">
         <v>5.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L20" t="n">
         <v>1.52</v>
       </c>
       <c r="M20" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N20" t="n">
         <v>2.76</v>
       </c>
       <c r="O20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P20" t="n">
         <v>1.59</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
         <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U20" t="n">
         <v>1.73</v>
@@ -5480,25 +5480,25 @@
         <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Z20" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA20" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD20" t="n">
         <v>24</v>
@@ -5510,7 +5510,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -5522,16 +5522,16 @@
         <v>20</v>
       </c>
       <c r="AK20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL20" t="n">
         <v>60</v>
       </c>
       <c r="AM20" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="AN20" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AO20" t="n">
         <v>180</v>
@@ -5546,19 +5546,19 @@
         <v>32</v>
       </c>
       <c r="AS20" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU20" t="n">
         <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX20" t="n">
         <v>8.4</v>
@@ -5570,10 +5570,10 @@
         <v>23</v>
       </c>
       <c r="BA20" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC20" t="n">
         <v>21</v>
@@ -5582,31 +5582,31 @@
         <v>46</v>
       </c>
       <c r="BE20" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG20" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH20" t="n">
         <v>2.88</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ20" t="n">
         <v>12</v>
       </c>
       <c r="BK20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN20" t="n">
         <v>4.3</v>
@@ -5618,16 +5618,16 @@
         <v>14.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU20" t="n">
         <v>5.5</v>
@@ -5636,7 +5636,7 @@
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
@@ -5648,11 +5648,11 @@
         <v>38</v>
       </c>
       <c r="CA20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -5686,19 +5686,19 @@
         <v>1.38</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
         <v>10.5</v>
       </c>
       <c r="J21" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.31</v>
@@ -5713,49 +5713,49 @@
         <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R21" t="n">
         <v>1.52</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
         <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W21" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="X21" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y21" t="n">
         <v>950</v>
       </c>
       <c r="Z21" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA21" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="AB21" t="n">
         <v>11.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="AE21" t="n">
         <v>170</v>
@@ -5776,7 +5776,7 @@
         <v>12</v>
       </c>
       <c r="AK21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL21" t="n">
         <v>36</v>
@@ -5785,7 +5785,7 @@
         <v>170</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AO21" t="n">
         <v>210</v>
@@ -5794,55 +5794,55 @@
         <v>16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>22</v>
+        <v>5.9</v>
       </c>
       <c r="AR21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS21" t="n">
         <v>7</v>
       </c>
-      <c r="AS21" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY21" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AV21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AZ21" t="n">
-        <v>19</v>
+        <v>5.9</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BC21" t="n">
         <v>12.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF21" t="n">
         <v>4.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH21" t="n">
         <v>4.2</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -6045,58 +6045,58 @@
         <v>75</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="BH22" t="n">
         <v>2.76</v>
@@ -6108,49 +6108,49 @@
         <v>13</v>
       </c>
       <c r="BK22" t="n">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BN22" t="n">
         <v>6.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="BP22" t="n">
         <v>32</v>
       </c>
       <c r="BQ22" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BR22" t="n">
         <v>60</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BT22" t="n">
         <v>6.4</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="BV22" t="n">
         <v>32</v>
       </c>
       <c r="BW22" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BX22" t="n">
         <v>60</v>
       </c>
       <c r="BY22" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
         <v>2.04</v>
@@ -6200,13 +6200,13 @@
         <v>4.6</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
         <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L23" t="n">
         <v>1.57</v>
@@ -6215,7 +6215,7 @@
         <v>1.12</v>
       </c>
       <c r="N23" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O23" t="n">
         <v>1.54</v>
@@ -6233,7 +6233,7 @@
         <v>5.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U23" t="n">
         <v>1.7</v>
@@ -6251,7 +6251,7 @@
         <v>14.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA23" t="n">
         <v>140</v>
@@ -6272,7 +6272,7 @@
         <v>10.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
         <v>30</v>
@@ -6305,10 +6305,10 @@
         <v>11</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT23" t="n">
         <v>5.7</v>
@@ -6320,7 +6320,7 @@
         <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX23" t="n">
         <v>9.4</v>
@@ -6329,28 +6329,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB23" t="n">
         <v>17.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF23" t="n">
         <v>17.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH23" t="n">
         <v>2.76</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
         <v>1.15</v>
       </c>
       <c r="H24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I24" t="n">
         <v>36</v>
@@ -6460,7 +6460,7 @@
         <v>11</v>
       </c>
       <c r="K24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="L24" t="n">
         <v>1.23</v>
@@ -6469,34 +6469,34 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P24" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
         <v>1.39</v>
       </c>
       <c r="R24" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="T24" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V24" t="n">
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="X24" t="n">
         <v>950</v>
@@ -6505,7 +6505,7 @@
         <v>950</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
@@ -6523,7 +6523,7 @@
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG24" t="n">
         <v>18</v>
@@ -6532,13 +6532,13 @@
         <v>950</v>
       </c>
       <c r="AI24" t="n">
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="AJ24" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK24" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="n">
         <v>75</v>
@@ -6553,58 +6553,58 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.35</v>
+        <v>5.9</v>
       </c>
       <c r="AS24" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU24" t="n">
         <v>20</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AW24" t="n">
         <v>6</v>
       </c>
       <c r="AX24" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AY24" t="n">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.35</v>
+        <v>5.9</v>
       </c>
       <c r="BB24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD24" t="n">
         <v>5.8</v>
       </c>
-      <c r="BC24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE24" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH24" t="n">
         <v>5.4</v>
@@ -6616,13 +6616,13 @@
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN24" t="n">
         <v>3.65</v>
@@ -6631,7 +6631,7 @@
         <v>3.2</v>
       </c>
       <c r="BP24" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BQ24" t="n">
         <v>4.7</v>
@@ -6640,19 +6640,19 @@
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BT24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>1.87</v>
       </c>
       <c r="G25" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H25" t="n">
         <v>5.2</v>
@@ -6717,7 +6717,7 @@
         <v>3.65</v>
       </c>
       <c r="L25" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
@@ -6846,7 +6846,7 @@
         <v>17.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BD25" t="n">
         <v>42</v>
@@ -6882,7 +6882,7 @@
         <v>4.4</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BP25" t="n">
         <v>14.5</v>
@@ -6900,7 +6900,7 @@
         <v>9</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>
@@ -6953,25 +6953,25 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G26" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="H26" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I26" t="n">
         <v>7.4</v>
       </c>
       <c r="J26" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K26" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L26" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
@@ -6983,7 +6983,7 @@
         <v>1.43</v>
       </c>
       <c r="P26" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q26" t="n">
         <v>2.28</v>
@@ -6995,16 +6995,16 @@
         <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V26" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W26" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="X26" t="n">
         <v>11.5</v>
@@ -7061,7 +7061,7 @@
         <v>270</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ26" t="n">
         <v>7.6</v>
@@ -7076,7 +7076,7 @@
         <v>5.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV26" t="n">
         <v>9</v>
@@ -7136,7 +7136,7 @@
         <v>3.9</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BP26" t="n">
         <v>12</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-25 14:59:08</t>
+          <t>2026-05-25 17:08:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,37 +857,37 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>2.32</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M2" t="n">
         <v>1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="O2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q2" t="n">
         <v>2.74</v>
@@ -902,52 +902,52 @@
         <v>2.22</v>
       </c>
       <c r="U2" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
         <v>1.75</v>
       </c>
       <c r="X2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF2" t="n">
         <v>13.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AJ2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK2" t="n">
         <v>36</v>
@@ -962,70 +962,70 @@
         <v>36</v>
       </c>
       <c r="AO2" t="n">
-        <v>180</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.45</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="AS2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY2" t="n">
         <v>5.5</v>
       </c>
-      <c r="AT2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK2" t="n">
         <v>5.5</v>
@@ -1034,43 +1034,43 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="BP2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS2" t="n">
-        <v>2</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>2.02</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="G3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H3" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>970</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.02</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
         <v>2.52</v>
       </c>
       <c r="T3" t="n">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.08</v>
+        <v>5.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.08</v>
+        <v>6</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.08</v>
+        <v>6.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.08</v>
+        <v>3.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.08</v>
+        <v>3.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.08</v>
+        <v>5.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.08</v>
+        <v>6.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.08</v>
+        <v>4.3</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.08</v>
+        <v>5.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.08</v>
+        <v>6.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.08</v>
+        <v>5.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.08</v>
+        <v>5.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.08</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.08</v>
+        <v>6.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.08</v>
+        <v>4.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.08</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
@@ -1351,186 +1351,186 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hangzhou Linping Wuyue</t>
+          <t>Shenzhen 2028</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hubei Istar</t>
+          <t>Wenzhou Professional</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.25</v>
+        <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2.64</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="P4" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>1.02</v>
+        <v>4.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="U4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.83</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>100</v>
       </c>
       <c r="AA4" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AL4" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.7</v>
+        <v>2.28</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.4</v>
+        <v>2.24</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.2</v>
+        <v>2.24</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.3</v>
+        <v>2.24</v>
       </c>
       <c r="AX4" t="n">
-        <v>5</v>
+        <v>2.06</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.6</v>
+        <v>2.08</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.9</v>
+        <v>2.14</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.5</v>
+        <v>2.24</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.5</v>
+        <v>2.16</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.5</v>
+        <v>2.26</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.8</v>
+        <v>2.26</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.3</v>
+        <v>2.22</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1548,7 +1548,7 @@
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
@@ -1563,7 +1563,7 @@
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
         <v>1.01</v>
@@ -1581,14 +1581,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
@@ -1605,234 +1605,234 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng II</t>
+          <t>Hangzhou Linping Wuyue</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Guizhou Zhucheng Athletic</t>
+          <t>Hubei Istar</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="H5" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="I5" t="n">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="W5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>4</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AR5" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
         <v>4.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="AW5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH5" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Armenian Premier League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,234 +1859,234 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Alashkert</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Shirak</t>
+          <t>Guizhou Zhucheng Athletic</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.36</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z6" t="n">
         <v>12.5</v>
       </c>
-      <c r="I6" t="n">
-        <v>16</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="AA6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>450</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>440</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>540</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT6" t="n">
         <v>6.4</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X6" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>190</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>330</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN6" t="n">
+      <c r="AU6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY6" t="n">
         <v>5.8</v>
       </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
         <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO6" t="n">
         <v>4.7</v>
       </c>
-      <c r="BG6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.5</v>
+        <v>2.24</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.6</v>
+        <v>2.26</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.76</v>
+        <v>6.8</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.76</v>
+        <v>2.22</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,55 +2118,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>FC Ararat Yerevan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>BKMA Yerevan</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.9</v>
       </c>
-      <c r="G7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
         <v>1.7</v>
@@ -2175,139 +2175,139 @@
         <v>2.14</v>
       </c>
       <c r="V7" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="Y7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AS7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>12</v>
       </c>
-      <c r="AE7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX7" t="n">
+      <c r="BA7" t="n">
         <v>4.7</v>
       </c>
-      <c r="AY7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA7" t="n">
+      <c r="BB7" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BC7" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="BD7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE7" t="n">
         <v>5</v>
       </c>
-      <c r="BE7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BF7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BI7" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO7" t="n">
         <v>4.6</v>
@@ -2316,48 +2316,48 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Czech 1 Liga</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,234 +2367,234 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Banik Ostrava</t>
+          <t>Alashkert</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MAS Taborsko</t>
+          <t>FC Shirak</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="G8" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="I8" t="n">
         <v>15</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="K8" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O8" t="n">
         <v>1.24</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.21</v>
-      </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.52</v>
+        <v>2.84</v>
       </c>
       <c r="T8" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="V8" t="n">
         <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="X8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="Z8" t="n">
-        <v>160</v>
+        <v>540</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>210</v>
+        <v>460</v>
       </c>
       <c r="AJ8" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>18</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
         <v>240</v>
       </c>
       <c r="AN8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>5.5</v>
       </c>
-      <c r="AO8" t="n">
-        <v>410</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BR8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
@@ -2621,171 +2621,171 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="I9" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
         <v>4.2</v>
       </c>
       <c r="L9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.28</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.29</v>
-      </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
-        <v>28</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG9" t="n">
         <v>970</v>
       </c>
-      <c r="AD9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>20</v>
-      </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>250</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>250</v>
+      </c>
+      <c r="AO9" t="n">
         <v>55</v>
       </c>
-      <c r="AL9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO9" t="n">
+      <c r="AP9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS9" t="n">
         <v>11.5</v>
       </c>
-      <c r="AP9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AT9" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="AU9" t="n">
         <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="AY9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA9" t="n">
         <v>5.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BC9" t="n">
         <v>5.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE9" t="n">
         <v>6</v>
@@ -2794,78 +2794,78 @@
         <v>5.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BI9" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.199999999999999</v>
+        <v>2.34</v>
       </c>
       <c r="BN9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BT9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Czech 1 Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Banik Ostrava</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>MAS Taborsko</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.26</v>
+        <v>1.29</v>
       </c>
       <c r="G10" t="n">
-        <v>2.46</v>
+        <v>1.31</v>
       </c>
       <c r="H10" t="n">
-        <v>3.15</v>
+        <v>12.5</v>
       </c>
       <c r="I10" t="n">
-        <v>3.55</v>
+        <v>14.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>2.52</v>
       </c>
       <c r="T10" t="n">
-        <v>1.74</v>
+        <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>1.68</v>
+        <v>4.2</v>
       </c>
       <c r="X10" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="Z10" t="n">
-        <v>28</v>
+        <v>540</v>
       </c>
       <c r="AA10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AD10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>470</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>380</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG10" t="n">
         <v>15</v>
       </c>
-      <c r="AE10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH10" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="BO10" t="n">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="BP10" t="n">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS10" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Argentino de Merlo</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.38</v>
+        <v>3.9</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5</v>
+        <v>1.92</v>
       </c>
       <c r="I11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG11" t="n">
         <v>4.1</v>
       </c>
-      <c r="J11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="BH11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN11" t="n">
         <v>7.6</v>
       </c>
-      <c r="Y11" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="BO11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="BT11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BV11" t="n">
         <v>13.5</v>
       </c>
-      <c r="AW11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>26</v>
-      </c>
-      <c r="BQ11" t="n">
+      <c r="BW11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BR11" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>0</v>
-      </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,244 +3383,244 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandi</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH12" t="n">
         <v>3.65</v>
       </c>
-      <c r="G12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="BI12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
         <v>8.4</v>
       </c>
-      <c r="Y12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT12" t="n">
+      <c r="BZ12" t="n">
+        <v>26</v>
+      </c>
+      <c r="CA12" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>0</v>
-      </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
@@ -3642,229 +3642,229 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Camioneros</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>Arsenal de Sarandi</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>2.04</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>2.16</v>
       </c>
       <c r="J13" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N13" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="O13" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="P13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="R13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U13" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="V13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.25</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.77</v>
-      </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="n">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA13" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>460</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>240</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>540</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW13" t="n">
         <v>6.8</v>
       </c>
-      <c r="AC13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
+      <c r="AX13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB13" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BC13" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
         <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BT13" t="n">
         <v>4.9</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BU13" t="n">
         <v>3.7</v>
       </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>6</v>
-      </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
@@ -3896,67 +3896,67 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CS Dock Sud</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Argentino de Merlo</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="G14" t="n">
-        <v>3.65</v>
+        <v>600</v>
       </c>
       <c r="H14" t="n">
-        <v>2.72</v>
+        <v>2.06</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2</v>
+        <v>970</v>
       </c>
       <c r="J14" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.22</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.66</v>
+        <v>1.02</v>
       </c>
       <c r="P14" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.92</v>
+        <v>2.36</v>
       </c>
       <c r="R14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="T14" t="n">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
@@ -3965,10 +3965,10 @@
         <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>65</v>
+        <v>420</v>
       </c>
       <c r="AB14" t="n">
         <v>970</v>
@@ -3980,145 +3980,145 @@
         <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>60</v>
+        <v>440</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
         <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AJ14" t="n">
-        <v>75</v>
+        <v>420</v>
       </c>
       <c r="AK14" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AO14" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.2</v>
+        <v>1.65</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.86</v>
+        <v>1.74</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.15</v>
+        <v>1.84</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.7</v>
+        <v>1.69</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.45</v>
+        <v>1.66</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.15</v>
+        <v>1.84</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.8</v>
+        <v>1.76</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.05</v>
+        <v>1.82</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.2</v>
+        <v>1.86</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.25</v>
+        <v>1.86</v>
       </c>
       <c r="BE14" t="n">
-        <v>3.3</v>
+        <v>1.87</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.2</v>
+        <v>1.87</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="G15" t="n">
-        <v>1.82</v>
+        <v>2.42</v>
       </c>
       <c r="H15" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>430</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>460</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU15" t="n">
         <v>6</v>
       </c>
-      <c r="J15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="P15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>CS Dock Sud</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>220</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>300</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>290</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>290</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>390</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>450</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO16" t="n">
         <v>4.9</v>
       </c>
-      <c r="G16" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
         <v>1.03</v>
       </c>
-      <c r="N16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X16" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AX16" t="n">
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
         <v>1.03</v>
       </c>
-      <c r="AY16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,189 +4653,189 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Talleres (RE)</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.86</v>
+        <v>1.6</v>
       </c>
       <c r="G17" t="n">
-        <v>3.9</v>
+        <v>1.72</v>
       </c>
       <c r="H17" t="n">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>2.42</v>
+        <v>5.1</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S17" t="n">
         <v>1.57</v>
       </c>
-      <c r="M17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X17" t="n">
+        <v>250</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>120</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS17" t="n">
         <v>5.6</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="AT17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY17" t="n">
         <v>8</v>
       </c>
-      <c r="Y17" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AR17" t="n">
+      <c r="AZ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF17" t="n">
         <v>3.65</v>
       </c>
-      <c r="AS17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG17" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.58</v>
+        <v>7.8</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.02</v>
+        <v>4.6</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK17" t="n">
         <v>4.9</v>
@@ -4844,60 +4844,60 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.92</v>
+        <v>8.6</v>
       </c>
       <c r="BN17" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR17" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BS17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>24</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ17" t="n">
         <v>7</v>
       </c>
-      <c r="BT17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>0</v>
-      </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,219 +4907,219 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CSD Liniers de Ciudad Evita</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N18" t="n">
+        <v>7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.14</v>
       </c>
-      <c r="G18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="T18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U18" t="n">
         <v>2.64</v>
       </c>
-      <c r="K18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.65</v>
-      </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>2.48</v>
       </c>
       <c r="W18" t="n">
-        <v>1.59</v>
+        <v>1.21</v>
       </c>
       <c r="X18" t="n">
-        <v>9.199999999999999</v>
+        <v>85</v>
       </c>
       <c r="Y18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>220</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW18" t="n">
         <v>12</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AX18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE18" t="n">
         <v>32</v>
       </c>
-      <c r="AA18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS18" t="n">
+      <c r="BF18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BT18" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>23</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>7.8</v>
       </c>
       <c r="BU18" t="n">
         <v>3.85</v>
@@ -5128,23 +5128,23 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
@@ -5166,229 +5166,229 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Comunicaciones B Aires</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UAI Urquiza</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.04</v>
+        <v>2.86</v>
       </c>
       <c r="G19" t="n">
-        <v>2.48</v>
+        <v>3.6</v>
       </c>
       <c r="H19" t="n">
-        <v>3.9</v>
+        <v>2.66</v>
       </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>3.35</v>
       </c>
       <c r="J19" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="K19" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="M19" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="N19" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="P19" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>1.05</v>
       </c>
       <c r="T19" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="X19" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AA19" t="n">
-        <v>150</v>
+        <v>420</v>
       </c>
       <c r="AB19" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AD19" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
-        <v>110</v>
+        <v>290</v>
       </c>
       <c r="AF19" t="n">
-        <v>13.5</v>
+        <v>50</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AI19" t="n">
-        <v>150</v>
+        <v>540</v>
       </c>
       <c r="AJ19" t="n">
-        <v>36</v>
+        <v>420</v>
       </c>
       <c r="AK19" t="n">
-        <v>40</v>
+        <v>440</v>
       </c>
       <c r="AL19" t="n">
-        <v>90</v>
+        <v>540</v>
       </c>
       <c r="AM19" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="AO19" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AR19" t="n">
         <v>5.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AV19" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>6</v>
+        <v>2.66</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="BA19" t="n">
-        <v>6</v>
+        <v>2.12</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="BD19" t="n">
-        <v>6</v>
+        <v>2.78</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.6</v>
+        <v>2.12</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,246 +5420,246 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="G20" t="n">
-        <v>1.93</v>
+        <v>2.48</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="I20" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="K20" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L20" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="M20" t="n">
         <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.76</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="P20" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="R20" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="S20" t="n">
-        <v>5.1</v>
+        <v>1.05</v>
       </c>
       <c r="T20" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="W20" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="X20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AA20" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AC20" t="n">
         <v>7.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AF20" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
       </c>
       <c r="AI20" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="AJ20" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AK20" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AL20" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="AM20" t="n">
         <v>260</v>
       </c>
       <c r="AN20" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="AO20" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BT20" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN20" t="n">
+      <c r="BU20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
         <v>4.3</v>
       </c>
-      <c r="BO20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>12</v>
+        <v>4.3</v>
       </c>
       <c r="BZ20" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,246 +5674,246 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Comunicaciones B Aires</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>UAI Urquiza</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.38</v>
+        <v>2.04</v>
       </c>
       <c r="G21" t="n">
-        <v>1.43</v>
+        <v>2.48</v>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>5.2</v>
+        <v>2.68</v>
       </c>
       <c r="K21" t="n">
-        <v>5.9</v>
+        <v>3.35</v>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>2.14</v>
       </c>
       <c r="O21" t="n">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.64</v>
+        <v>2.54</v>
       </c>
       <c r="R21" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>3.95</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="U21" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>3.35</v>
+        <v>1.68</v>
       </c>
       <c r="X21" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AA21" t="n">
-        <v>390</v>
+        <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AC21" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AE21" t="n">
-        <v>170</v>
+        <v>240</v>
       </c>
       <c r="AF21" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="AI21" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AJ21" t="n">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="AK21" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="AL21" t="n">
-        <v>36</v>
+        <v>460</v>
       </c>
       <c r="AM21" t="n">
-        <v>170</v>
+        <v>330</v>
       </c>
       <c r="AN21" t="n">
-        <v>6.4</v>
+        <v>90</v>
       </c>
       <c r="AO21" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>16</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF21" t="n">
         <v>6.8</v>
       </c>
-      <c r="AS21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG21" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="BH21" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BP21" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT21" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CA21" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,244 +5923,244 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="G22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.5</v>
       </c>
-      <c r="H22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L22" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M22" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N22" t="n">
-        <v>2.24</v>
+        <v>2.74</v>
       </c>
       <c r="O22" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="P22" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="R22" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="S22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="X22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC22" t="n">
         <v>9.4</v>
       </c>
-      <c r="Z22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8</v>
-      </c>
       <c r="AD22" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AE22" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AF22" t="n">
-        <v>22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
         <v>28</v>
       </c>
       <c r="AI22" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AJ22" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="AK22" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AM22" t="n">
-        <v>240</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.25</v>
+        <v>8.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.95</v>
+        <v>20</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.7</v>
+        <v>28</v>
       </c>
       <c r="AX22" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN22" t="n">
         <v>4.3</v>
       </c>
-      <c r="BA22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ22" t="n">
+      <c r="BO22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
         <v>13</v>
       </c>
-      <c r="BK22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>32</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
@@ -6177,251 +6177,251 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="G23" t="n">
-        <v>2.04</v>
+        <v>1.38</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="K23" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="M23" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>2.64</v>
+        <v>4.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>1.56</v>
+        <v>2.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.58</v>
+        <v>1.64</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="S23" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="U23" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>1.96</v>
+        <v>3.6</v>
       </c>
       <c r="X23" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>390</v>
+      </c>
+      <c r="AB23" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AC23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK23" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AL23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK23" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP23" t="n">
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP23" t="n">
         <v>8</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU23" t="n">
+      <c r="BQ23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU23" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK23" t="n">
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="CA23" t="n">
         <v>7</v>
       </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>12</v>
-      </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,244 +6431,244 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cusco FC</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.12</v>
+        <v>2.7</v>
       </c>
       <c r="G24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.15</v>
       </c>
-      <c r="H24" t="n">
+      <c r="S24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF24" t="n">
         <v>21</v>
       </c>
-      <c r="I24" t="n">
-        <v>36</v>
-      </c>
-      <c r="J24" t="n">
-        <v>11</v>
-      </c>
-      <c r="K24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="X24" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>390</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AG24" t="n">
         <v>16</v>
       </c>
-      <c r="AC24" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>18</v>
-      </c>
       <c r="AH24" t="n">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AI24" t="n">
-        <v>440</v>
+        <v>200</v>
       </c>
       <c r="AJ24" t="n">
-        <v>8.800000000000001</v>
+        <v>65</v>
       </c>
       <c r="AK24" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="AL24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN24" t="n">
         <v>75</v>
       </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>3</v>
-      </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.6</v>
+        <v>3.85</v>
       </c>
       <c r="AQ24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW24" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>6</v>
-      </c>
       <c r="AX24" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY24" t="n">
         <v>4.6</v>
       </c>
       <c r="AZ24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC24" t="n">
         <v>5.8</v>
       </c>
-      <c r="BA24" t="n">
+      <c r="BD24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF24" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>2.56</v>
-      </c>
       <c r="BG24" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH24" t="n">
-        <v>5.4</v>
+        <v>2.76</v>
       </c>
       <c r="BI24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK24" t="n">
         <v>4.7</v>
       </c>
-      <c r="BJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="BN24" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BP24" t="n">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="BQ24" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS24" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU24" t="n">
-        <v>9.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW24" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY24" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="BZ24" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
@@ -6690,239 +6690,239 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Universitario de Deportes</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="G25" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="H25" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J25" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
         <v>3.65</v>
       </c>
       <c r="L25" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="O25" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="P25" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="V25" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W25" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="X25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AA25" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AE25" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AF25" t="n">
         <v>10.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AI25" t="n">
         <v>110</v>
       </c>
       <c r="AJ25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AK25" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AL25" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AM25" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="AN25" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AO25" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="AS25" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AU25" t="n">
         <v>7.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AX25" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BA25" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BB25" t="n">
         <v>17.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>42</v>
+        <v>7.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BJ25" t="n">
         <v>12</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BN25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP25" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BT25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BU25" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-25 17:08:48</t>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>
@@ -6944,217 +6944,217 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Cusco FC</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.66</v>
+        <v>1.12</v>
       </c>
       <c r="G26" t="n">
-        <v>1.73</v>
+        <v>1.16</v>
       </c>
       <c r="H26" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="I26" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="J26" t="n">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="K26" t="n">
-        <v>3.95</v>
+        <v>13.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="M26" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>1.67</v>
+        <v>3.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.28</v>
+        <v>1.38</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="S26" t="n">
-        <v>4.4</v>
+        <v>1.99</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="U26" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>2.34</v>
+        <v>7.2</v>
       </c>
       <c r="X26" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="Y26" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Z26" t="n">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="AA26" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="AC26" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AD26" t="n">
         <v>950</v>
       </c>
       <c r="AE26" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AG26" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AH26" t="n">
         <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>160</v>
+        <v>440</v>
       </c>
       <c r="AJ26" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK26" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM26" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>970</v>
+        <v>2.9</v>
       </c>
       <c r="AO26" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BO26" t="n">
         <v>3.25</v>
       </c>
-      <c r="AS26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV26" t="n">
+      <c r="BP26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
         <v>9</v>
       </c>
-      <c r="AW26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BT26" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
@@ -7166,17 +7166,525 @@
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:18:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ27" t="n">
         <v>13</v>
       </c>
-      <c r="BZ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA26" t="n">
+      <c r="AR27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW27" t="n">
         <v>10</v>
       </c>
-      <c r="CB26" t="inlineStr">
-        <is>
-          <t>2026-05-25 17:08:48</t>
+      <c r="AX27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:18:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>10</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-05-25 19:18:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G2" t="n">
         <v>2.32</v>
@@ -869,49 +869,49 @@
         <v>5.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
         <v>1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V2" t="n">
         <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y2" t="n">
         <v>13</v>
@@ -965,67 +965,67 @@
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU2" t="n">
         <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AW2" t="n">
         <v>6.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BD2" t="n">
         <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>150</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG2" t="n">
         <v>6.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK2" t="n">
         <v>5.5</v>
@@ -1034,34 +1034,34 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.199999999999999</v>
+        <v>180</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BP2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS2" t="n">
         <v>7.8</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW2" t="n">
         <v>8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -1114,163 +1114,163 @@
         <v>1.73</v>
       </c>
       <c r="G3" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O3" t="n">
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>2.52</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U3" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X3" t="n">
         <v>14</v>
       </c>
       <c r="Y3" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3" t="n">
         <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
         <v>230</v>
       </c>
       <c r="AJ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK3" t="n">
         <v>22</v>
       </c>
-      <c r="AK3" t="n">
-        <v>23</v>
-      </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF3" t="n">
         <v>5.1</v>
       </c>
-      <c r="AR3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="n">
         <v>3.4</v>
@@ -1282,49 +1282,49 @@
         <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO3" t="n">
         <v>3</v>
       </c>
       <c r="BP3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR3" t="n">
         <v>32</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV3" t="n">
         <v>55</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.36</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -1368,34 +1368,34 @@
         <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.51</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O4" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="P4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q4" t="n">
         <v>2.6</v>
@@ -1404,7 +1404,7 @@
         <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T4" t="n">
         <v>2.16</v>
@@ -1413,16 +1413,16 @@
         <v>1.69</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X4" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>100</v>
@@ -1431,25 +1431,25 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AC4" t="n">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>75</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1473,61 +1473,61 @@
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.28</v>
+        <v>5.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>7</v>
+        <v>2.66</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.24</v>
+        <v>6.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.24</v>
+        <v>4.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.06</v>
+        <v>5.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.08</v>
+        <v>5.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.14</v>
+        <v>2.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.24</v>
+        <v>4.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="BC4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="BF4" t="n">
         <v>2.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI4" t="n">
         <v>2.26</v>
@@ -1536,16 +1536,16 @@
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO4" t="n">
         <v>3.6</v>
@@ -1554,41 +1554,41 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>34</v>
+        <v>1.1</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H5" t="n">
         <v>2.32</v>
       </c>
       <c r="I5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J5" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>1.47</v>
@@ -1643,7 +1643,7 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.47</v>
@@ -1652,31 +1652,31 @@
         <v>1.57</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
         <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
         <v>970</v>
@@ -1694,7 +1694,7 @@
         <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
         <v>26</v>
@@ -1703,136 +1703,136 @@
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU5" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AV5" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AX5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
         <v>5.6</v>
       </c>
-      <c r="AY5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H6" t="n">
         <v>2.04</v>
@@ -1885,19 +1885,19 @@
         <v>2.18</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
         <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
         <v>1.46</v>
@@ -1909,22 +1909,22 @@
         <v>2.34</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
         <v>1.84</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X6" t="n">
         <v>10.5</v>
@@ -1951,10 +1951,10 @@
         <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH6" t="n">
         <v>24</v>
@@ -1975,7 +1975,7 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>130</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
         <v>25</v>
@@ -1984,61 +1984,61 @@
         <v>4.9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR6" t="n">
         <v>5.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6</v>
-      </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC6" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC6" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
@@ -2050,31 +2050,31 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.32</v>
+        <v>10.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.24</v>
+        <v>9</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.26</v>
+        <v>9.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BV6" t="n">
         <v>17</v>
@@ -2086,7 +2086,7 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.22</v>
+        <v>8.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.74</v>
+        <v>2.28</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="H7" t="n">
-        <v>2.44</v>
+        <v>3.05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -2145,46 +2145,46 @@
         <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U7" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="X7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z7" t="n">
         <v>34</v>
@@ -2193,22 +2193,22 @@
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
         <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
         <v>60</v>
@@ -2226,131 +2226,131 @@
         <v>120</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN7" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AP7" t="n">
         <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW7" t="n">
         <v>6</v>
       </c>
-      <c r="AV7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AX7" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
         <v>12</v>
       </c>
       <c r="BA7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU7" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.32</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="H8" t="n">
         <v>11.5</v>
@@ -2393,10 +2393,10 @@
         <v>15</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L8" t="n">
         <v>1.27</v>
@@ -2408,7 +2408,7 @@
         <v>4.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P8" t="n">
         <v>2.12</v>
@@ -2426,13 +2426,13 @@
         <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
         <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X8" t="n">
         <v>26</v>
@@ -2474,7 +2474,7 @@
         <v>10.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2489,10 +2489,10 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
         <v>9</v>
@@ -2507,7 +2507,7 @@
         <v>10</v>
       </c>
       <c r="AV8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AW8" t="n">
         <v>9.199999999999999</v>
@@ -2540,7 +2540,7 @@
         <v>4.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>2.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
         <v>4.2</v>
@@ -2662,7 +2662,7 @@
         <v>3.95</v>
       </c>
       <c r="O9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
         <v>2.02</v>
@@ -2689,7 +2689,7 @@
         <v>1.28</v>
       </c>
       <c r="X9" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="Y9" t="n">
         <v>12</v>
@@ -2776,13 +2776,13 @@
         <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB9" t="n">
         <v>6</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD9" t="n">
         <v>5.8</v>
@@ -2791,7 +2791,7 @@
         <v>6</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BG9" t="n">
         <v>9.4</v>
@@ -2800,13 +2800,13 @@
         <v>3.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I10" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K10" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.24</v>
@@ -2913,40 +2913,40 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q10" t="n">
         <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S10" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
         <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X10" t="n">
         <v>26</v>
       </c>
       <c r="Y10" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="Z10" t="n">
         <v>540</v>
@@ -2955,13 +2955,13 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>15.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AE10" t="n">
         <v>270</v>
@@ -2973,7 +2973,7 @@
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AI10" t="n">
         <v>470</v>
@@ -2982,43 +2982,43 @@
         <v>10.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AM10" t="n">
         <v>230</v>
       </c>
       <c r="AN10" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AO10" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AP10" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
         <v>6.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV10" t="n">
         <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX10" t="n">
         <v>6.8</v>
@@ -3030,7 +3030,7 @@
         <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BB10" t="n">
         <v>8.4</v>
@@ -3042,7 +3042,7 @@
         <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10" t="n">
         <v>4.1</v>
@@ -3060,19 +3060,19 @@
         <v>13.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
         <v>3.85</v>
       </c>
       <c r="BO10" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BP10" t="n">
         <v>7.4</v>
@@ -3084,25 +3084,25 @@
         <v>25</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT10" t="n">
         <v>16.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>2.02</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
         <v>4.2</v>
@@ -3200,7 +3200,7 @@
         <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
         <v>16.5</v>
@@ -3260,10 +3260,10 @@
         <v>7</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="AU11" t="n">
         <v>7.8</v>
@@ -3275,7 +3275,7 @@
         <v>9</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
@@ -3284,13 +3284,13 @@
         <v>9</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>5.6</v>
       </c>
       <c r="BB11" t="n">
         <v>6</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD11" t="n">
         <v>20</v>
@@ -3302,7 +3302,7 @@
         <v>5.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH11" t="n">
         <v>3.9</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN11" t="n">
         <v>7.6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
         <v>1.72</v>
       </c>
       <c r="U12" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
         <v>1.4</v>
@@ -3460,7 +3460,7 @@
         <v>55</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB12" t="n">
         <v>11.5</v>
@@ -3472,16 +3472,16 @@
         <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF12" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AG12" t="n">
         <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AI12" t="n">
         <v>100</v>
@@ -3499,10 +3499,10 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AP12" t="n">
         <v>11</v>
@@ -3526,7 +3526,7 @@
         <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -3538,10 +3538,10 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
         <v>18</v>
@@ -3550,13 +3550,13 @@
         <v>18</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
         <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="BH12" t="n">
         <v>3.65</v>
@@ -3580,13 +3580,13 @@
         <v>5.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP12" t="n">
         <v>18</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -3651,40 +3651,40 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H13" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="I13" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="J13" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M13" t="n">
         <v>1.14</v>
       </c>
       <c r="N13" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="P13" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
         <v>1.15</v>
@@ -3693,19 +3693,19 @@
         <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U13" t="n">
         <v>1.63</v>
       </c>
       <c r="V13" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="n">
         <v>6.8</v>
@@ -3717,7 +3717,7 @@
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AC13" t="n">
         <v>14</v>
@@ -3732,10 +3732,10 @@
         <v>100</v>
       </c>
       <c r="AG13" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AH13" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AI13" t="n">
         <v>460</v>
@@ -3744,7 +3744,7 @@
         <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="AL13" t="n">
         <v>540</v>
@@ -3753,22 +3753,22 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AO13" t="n">
         <v>110</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ13" t="n">
         <v>5.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AT13" t="n">
         <v>8</v>
@@ -3780,43 +3780,43 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX13" t="n">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BA13" t="n">
         <v>7.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="n">
         <v>7.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BG13" t="n">
         <v>7.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
@@ -3828,13 +3828,13 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BN13" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
@@ -3846,19 +3846,19 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -3905,220 +3905,220 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N14" t="n">
         <v>2.1</v>
       </c>
-      <c r="G14" t="n">
-        <v>600</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I14" t="n">
-        <v>970</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>950</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.02</v>
+        <v>1.64</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="Q14" t="n">
         <v>2.36</v>
       </c>
       <c r="R14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S14" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="W14" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>420</v>
+        <v>50</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>440</v>
+        <v>120</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AH14" t="n">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="AI14" t="n">
-        <v>540</v>
+        <v>260</v>
       </c>
       <c r="AJ14" t="n">
-        <v>420</v>
+        <v>250</v>
       </c>
       <c r="AK14" t="n">
-        <v>290</v>
+        <v>160</v>
       </c>
       <c r="AL14" t="n">
         <v>540</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN14" t="n">
         <v>210</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.65</v>
+        <v>4.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.74</v>
+        <v>6.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.84</v>
+        <v>9</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.69</v>
+        <v>4.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.66</v>
+        <v>4.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.73</v>
+        <v>6.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.84</v>
+        <v>9</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.76</v>
+        <v>6.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.82</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.85</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.86</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.85</v>
+        <v>9.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.86</v>
+        <v>10</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.87</v>
+        <v>10.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.85</v>
+        <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.87</v>
+        <v>9.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="n">
         <v>2.42</v>
@@ -4180,13 +4180,13 @@
         <v>1.57</v>
       </c>
       <c r="M15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N15" t="n">
         <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P15" t="n">
         <v>1.46</v>
@@ -4204,10 +4204,10 @@
         <v>2.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
         <v>1.7</v>
@@ -4228,10 +4228,10 @@
         <v>12</v>
       </c>
       <c r="AC15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD15" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="AE15" t="n">
         <v>210</v>
@@ -4243,7 +4243,7 @@
         <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="n">
         <v>430</v>
@@ -4273,22 +4273,22 @@
         <v>6.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.96</v>
+        <v>3.65</v>
       </c>
       <c r="AX15" t="n">
         <v>5.1</v>
@@ -4297,28 +4297,28 @@
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BH15" t="n">
         <v>2.76</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="G16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I16" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="K16" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="L16" t="n">
         <v>1.7</v>
@@ -4437,13 +4437,13 @@
         <v>1.22</v>
       </c>
       <c r="N16" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q16" t="n">
         <v>3.9</v>
@@ -4455,19 +4455,19 @@
         <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="U16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
@@ -4482,7 +4482,7 @@
         <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD16" t="n">
         <v>970</v>
@@ -4497,7 +4497,7 @@
         <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
         <v>300</v>
@@ -4527,10 +4527,10 @@
         <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AT16" t="n">
         <v>5.7</v>
@@ -4539,40 +4539,40 @@
         <v>4.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AX16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY16" t="n">
         <v>6</v>
       </c>
-      <c r="AY16" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.89</v>
+        <v>4.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.89</v>
+        <v>4.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.88</v>
+        <v>4.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.91</v>
+        <v>2.98</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="BH16" t="n">
         <v>2.24</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
@@ -4602,13 +4602,13 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
@@ -4620,13 +4620,13 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G17" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
         <v>5.1</v>
@@ -4700,34 +4700,34 @@
         <v>4.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R17" t="n">
         <v>2.46</v>
       </c>
       <c r="S17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="T17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="U17" t="n">
         <v>3.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X17" t="n">
         <v>250</v>
       </c>
       <c r="Y17" t="n">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AA17" t="n">
         <v>120</v>
@@ -4745,22 +4745,22 @@
         <v>48</v>
       </c>
       <c r="AF17" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AG17" t="n">
         <v>13</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI17" t="n">
         <v>36</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
         <v>17.5</v>
@@ -4772,34 +4772,34 @@
         <v>4.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>38</v>
+        <v>5.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>28</v>
+        <v>5.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT17" t="n">
         <v>19</v>
       </c>
       <c r="AU17" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AV17" t="n">
         <v>18</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.2</v>
+        <v>32</v>
       </c>
       <c r="AX17" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AY17" t="n">
         <v>8</v>
@@ -4814,13 +4814,13 @@
         <v>11.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="BD17" t="n">
         <v>11.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BF17" t="n">
         <v>3.65</v>
@@ -4832,7 +4832,7 @@
         <v>7.8</v>
       </c>
       <c r="BI17" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BJ17" t="n">
         <v>8.6</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -4924,19 +4924,19 @@
         <v>5.1</v>
       </c>
       <c r="G18" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H18" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="I18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L18" t="n">
         <v>1.21</v>
@@ -4954,13 +4954,13 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R18" t="n">
         <v>1.79</v>
       </c>
       <c r="S18" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="T18" t="n">
         <v>1.56</v>
@@ -4969,7 +4969,7 @@
         <v>2.64</v>
       </c>
       <c r="V18" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="W18" t="n">
         <v>1.21</v>
@@ -4978,7 +4978,7 @@
         <v>85</v>
       </c>
       <c r="Y18" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z18" t="n">
         <v>14.5</v>
@@ -4987,16 +4987,16 @@
         <v>44</v>
       </c>
       <c r="AB18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD18" t="n">
         <v>10.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF18" t="n">
         <v>220</v>
@@ -5005,7 +5005,7 @@
         <v>950</v>
       </c>
       <c r="AH18" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AI18" t="n">
         <v>48</v>
@@ -5032,19 +5032,19 @@
         <v>22</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
         <v>14</v>
       </c>
       <c r="AT18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV18" t="n">
         <v>8.6</v>
@@ -5053,7 +5053,7 @@
         <v>12</v>
       </c>
       <c r="AX18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY18" t="n">
         <v>15</v>
@@ -5074,7 +5074,7 @@
         <v>26</v>
       </c>
       <c r="BE18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BF18" t="n">
         <v>24</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="G19" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="H19" t="n">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="I19" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
         <v>2.56</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L19" t="n">
         <v>1.61</v>
@@ -5199,37 +5199,37 @@
         <v>1.18</v>
       </c>
       <c r="N19" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="P19" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.78</v>
+        <v>3.45</v>
       </c>
       <c r="R19" t="n">
         <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>1.05</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y19" t="n">
         <v>16.5</v>
@@ -5253,25 +5253,25 @@
         <v>290</v>
       </c>
       <c r="AF19" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="AG19" t="n">
         <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AI19" t="n">
         <v>540</v>
       </c>
       <c r="AJ19" t="n">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
@@ -5292,7 +5292,7 @@
         <v>5.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="AT19" t="n">
         <v>4.4</v>
@@ -5304,37 +5304,37 @@
         <v>5.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="AX19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY19" t="n">
         <v>6.2</v>
       </c>
-      <c r="AY19" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.12</v>
+        <v>7.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.55</v>
+        <v>2.64</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.78</v>
+        <v>1.75</v>
       </c>
       <c r="BE19" t="n">
         <v>8</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="BH19" t="n">
         <v>2.44</v>
@@ -5376,7 +5376,7 @@
         <v>5.7</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -5429,64 +5429,64 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G20" t="n">
         <v>2.48</v>
       </c>
       <c r="H20" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
         <v>4.6</v>
       </c>
       <c r="J20" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="K20" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L20" t="n">
         <v>1.56</v>
       </c>
       <c r="M20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O20" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="P20" t="n">
         <v>1.43</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
         <v>1.15</v>
       </c>
       <c r="S20" t="n">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
         <v>1.27</v>
       </c>
       <c r="W20" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X20" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
         <v>30</v>
@@ -5495,7 +5495,7 @@
         <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC20" t="n">
         <v>7.8</v>
@@ -5507,10 +5507,10 @@
         <v>170</v>
       </c>
       <c r="AF20" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -5519,10 +5519,10 @@
         <v>260</v>
       </c>
       <c r="AJ20" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AK20" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AL20" t="n">
         <v>170</v>
@@ -5531,118 +5531,118 @@
         <v>260</v>
       </c>
       <c r="AN20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.4</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BJ20" t="n">
         <v>13</v>
       </c>
       <c r="BK20" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="BN20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BO20" t="n">
-        <v>2.54</v>
+        <v>3.8</v>
       </c>
       <c r="BP20" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BT20" t="n">
         <v>7.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -5683,64 +5683,64 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G21" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
         <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="M21" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N21" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="O21" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="P21" t="n">
         <v>1.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="R21" t="n">
         <v>1.13</v>
       </c>
       <c r="S21" t="n">
-        <v>3.95</v>
+        <v>6.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V21" t="n">
         <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="X21" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z21" t="n">
         <v>120</v>
@@ -5749,10 +5749,10 @@
         <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
         <v>38</v>
@@ -5761,10 +5761,10 @@
         <v>240</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH21" t="n">
         <v>110</v>
@@ -5776,127 +5776,127 @@
         <v>130</v>
       </c>
       <c r="AK21" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AL21" t="n">
         <v>460</v>
       </c>
       <c r="AM21" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
         <v>90</v>
       </c>
       <c r="AO21" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR21" t="n">
         <v>14.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.75</v>
+        <v>16.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AX21" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="AY21" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF21" t="n">
         <v>6.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G22" t="n">
         <v>1.91</v>
       </c>
       <c r="H22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L22" t="n">
         <v>1.53</v>
@@ -5970,7 +5970,7 @@
         <v>1.59</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R22" t="n">
         <v>1.21</v>
@@ -5985,7 +5985,7 @@
         <v>1.73</v>
       </c>
       <c r="V22" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W22" t="n">
         <v>2.08</v>
@@ -5997,7 +5997,7 @@
         <v>15</v>
       </c>
       <c r="Z22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA22" t="n">
         <v>170</v>
@@ -6009,7 +6009,7 @@
         <v>9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AE22" t="n">
         <v>110</v>
@@ -6021,10 +6021,10 @@
         <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AI22" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="AJ22" t="n">
         <v>22</v>
@@ -6033,7 +6033,7 @@
         <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
@@ -6048,7 +6048,7 @@
         <v>8.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR22" t="n">
         <v>32</v>
@@ -6069,7 +6069,7 @@
         <v>28</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
@@ -6078,7 +6078,7 @@
         <v>24</v>
       </c>
       <c r="BA22" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB22" t="n">
         <v>18.5</v>
@@ -6102,7 +6102,7 @@
         <v>2.84</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ22" t="n">
         <v>12</v>
@@ -6126,13 +6126,13 @@
         <v>15</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT22" t="n">
         <v>8.6</v>
@@ -6150,17 +6150,17 @@
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ22" t="n">
         <v>38</v>
       </c>
       <c r="CA22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G23" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="H23" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I23" t="n">
         <v>10.5</v>
@@ -6206,7 +6206,7 @@
         <v>5.7</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.31</v>
@@ -6215,13 +6215,13 @@
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q23" t="n">
         <v>1.64</v>
@@ -6230,19 +6230,19 @@
         <v>1.52</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="T23" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W23" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X23" t="n">
         <v>24</v>
@@ -6254,10 +6254,10 @@
         <v>95</v>
       </c>
       <c r="AA23" t="n">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC23" t="n">
         <v>13</v>
@@ -6272,7 +6272,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG23" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
         <v>28</v>
@@ -6281,19 +6281,19 @@
         <v>140</v>
       </c>
       <c r="AJ23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK23" t="n">
         <v>14.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AM23" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO23" t="n">
         <v>200</v>
@@ -6305,25 +6305,25 @@
         <v>27</v>
       </c>
       <c r="AR23" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU23" t="n">
         <v>11</v>
       </c>
       <c r="AV23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AW23" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY23" t="n">
         <v>9.4</v>
@@ -6332,25 +6332,25 @@
         <v>24</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB23" t="n">
         <v>10</v>
       </c>
       <c r="BC23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD23" t="n">
         <v>30</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF23" t="n">
         <v>5.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BH23" t="n">
         <v>4.2</v>
@@ -6374,7 +6374,7 @@
         <v>3.9</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BP23" t="n">
         <v>8</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -6445,55 +6445,55 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="G24" t="n">
         <v>3.4</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="K24" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L24" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="M24" t="n">
         <v>1.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="O24" t="n">
         <v>1.54</v>
       </c>
       <c r="P24" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="Q24" t="n">
         <v>2.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S24" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="T24" t="n">
         <v>2.06</v>
       </c>
       <c r="U24" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="V24" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W24" t="n">
         <v>1.41</v>
@@ -6502,25 +6502,25 @@
         <v>8.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB24" t="n">
         <v>9</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF24" t="n">
         <v>21</v>
@@ -6529,7 +6529,7 @@
         <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
         <v>200</v>
@@ -6541,10 +6541,10 @@
         <v>55</v>
       </c>
       <c r="AL24" t="n">
-        <v>200</v>
+        <v>540</v>
       </c>
       <c r="AM24" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN24" t="n">
         <v>75</v>
@@ -6553,16 +6553,16 @@
         <v>150</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.85</v>
+        <v>6.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR24" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AT24" t="n">
         <v>4.9</v>
@@ -6571,94 +6571,94 @@
         <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.8</v>
+        <v>30</v>
       </c>
       <c r="AX24" t="n">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="AY24" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="BH24" t="n">
         <v>2.76</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BJ24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>7.2</v>
+        <v>2.12</v>
       </c>
       <c r="BN24" t="n">
         <v>6.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="BP24" t="n">
         <v>32</v>
       </c>
       <c r="BQ24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BR24" t="n">
         <v>60</v>
       </c>
       <c r="BS24" t="n">
-        <v>6.6</v>
+        <v>2.06</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="BV24" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BW24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BX24" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY24" t="n">
-        <v>6.6</v>
+        <v>2.06</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H25" t="n">
         <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
         <v>3.3</v>
       </c>
       <c r="K25" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.57</v>
@@ -6747,10 +6747,10 @@
         <v>1.71</v>
       </c>
       <c r="V25" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W25" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X25" t="n">
         <v>10.5</v>
@@ -6813,10 +6813,10 @@
         <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT25" t="n">
         <v>5.7</v>
@@ -6837,28 +6837,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB25" t="n">
         <v>17.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF25" t="n">
         <v>17.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH25" t="n">
         <v>2.76</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -6956,13 +6956,13 @@
         <v>1.12</v>
       </c>
       <c r="G26" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H26" t="n">
         <v>21</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J26" t="n">
         <v>11</v>
@@ -6983,7 +6983,7 @@
         <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q26" t="n">
         <v>1.38</v>
@@ -7004,7 +7004,7 @@
         <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="X26" t="n">
         <v>950</v>
@@ -7031,7 +7031,7 @@
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG26" t="n">
         <v>18</v>
@@ -7055,22 +7055,22 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS26" t="n">
         <v>5.4</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>5</v>
       </c>
       <c r="AT26" t="n">
         <v>11</v>
@@ -7079,7 +7079,7 @@
         <v>20</v>
       </c>
       <c r="AV26" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW26" t="n">
         <v>6</v>
@@ -7088,31 +7088,31 @@
         <v>5.8</v>
       </c>
       <c r="AY26" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB26" t="n">
         <v>5.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BG26" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>5</v>
       </c>
       <c r="BH26" t="n">
         <v>5.4</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -7210,88 +7210,88 @@
         <v>1.88</v>
       </c>
       <c r="G27" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H27" t="n">
         <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J27" t="n">
         <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="O27" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R27" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T27" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U27" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="V27" t="n">
         <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z27" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA27" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE27" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AF27" t="n">
         <v>10.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
         <v>110</v>
@@ -7303,7 +7303,7 @@
         <v>24</v>
       </c>
       <c r="AL27" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM27" t="n">
         <v>180</v>
@@ -7312,7 +7312,7 @@
         <v>17.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AP27" t="n">
         <v>9.199999999999999</v>
@@ -7321,22 +7321,22 @@
         <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS27" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU27" t="n">
         <v>7.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX27" t="n">
         <v>8.6</v>
@@ -7345,10 +7345,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BB27" t="n">
         <v>17.5</v>
@@ -7357,28 +7357,28 @@
         <v>20</v>
       </c>
       <c r="BD27" t="n">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BF27" t="n">
         <v>14.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BJ27" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
@@ -7387,25 +7387,25 @@
         <v>10</v>
       </c>
       <c r="BN27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="BP27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ27" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU27" t="n">
         <v>6.8</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
         <v>9</v>
       </c>
-      <c r="BX27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY27" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>
@@ -7461,40 +7461,40 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G28" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="H28" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L28" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O28" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P28" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
@@ -7503,7 +7503,7 @@
         <v>4.4</v>
       </c>
       <c r="T28" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U28" t="n">
         <v>1.73</v>
@@ -7512,16 +7512,16 @@
         <v>1.16</v>
       </c>
       <c r="W28" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="X28" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA28" t="n">
         <v>280</v>
@@ -7530,7 +7530,7 @@
         <v>6.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD28" t="n">
         <v>950</v>
@@ -7554,7 +7554,7 @@
         <v>970</v>
       </c>
       <c r="AK28" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AL28" t="n">
         <v>55</v>
@@ -7569,16 +7569,16 @@
         <v>270</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>3.05</v>
+        <v>2.48</v>
       </c>
       <c r="AT28" t="n">
         <v>5.8</v>
@@ -7590,101 +7590,101 @@
         <v>8.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY28" t="n">
         <v>5.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BA28" t="n">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="BB28" t="n">
         <v>7</v>
       </c>
       <c r="BC28" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD28" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>3.05</v>
+        <v>2.48</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>3.05</v>
+        <v>2.48</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BN28" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP28" t="n">
         <v>12</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BT28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-25 19:18:11</t>
+          <t>2026-05-25 21:27:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB28"/>
+  <dimension ref="A1:CB29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,67 +857,67 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G2" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H2" t="n">
         <v>4.2</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="O2" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W2" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
@@ -929,16 +929,16 @@
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
         <v>240</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
         <v>29</v>
@@ -950,7 +950,7 @@
         <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL2" t="n">
         <v>75</v>
@@ -959,25 +959,25 @@
         <v>270</v>
       </c>
       <c r="AN2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO2" t="n">
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU2" t="n">
         <v>6.2</v>
@@ -986,7 +986,7 @@
         <v>17</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
@@ -995,37 +995,37 @@
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC2" t="n">
         <v>16</v>
       </c>
-      <c r="BA2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE2" t="n">
         <v>150</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK2" t="n">
         <v>5.5</v>
@@ -1043,34 +1043,34 @@
         <v>3.9</v>
       </c>
       <c r="BP2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G3" t="n">
         <v>1.91</v>
@@ -1120,7 +1120,7 @@
         <v>4.7</v>
       </c>
       <c r="I3" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
@@ -1129,91 +1129,91 @@
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W3" t="n">
         <v>2.06</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.08</v>
-      </c>
       <c r="X3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y3" t="n">
         <v>18</v>
       </c>
       <c r="Z3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
         <v>230</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
         <v>230</v>
       </c>
       <c r="AJ3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK3" t="n">
         <v>21</v>
       </c>
-      <c r="AK3" t="n">
-        <v>22</v>
-      </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
@@ -1222,109 +1222,109 @@
         <v>5.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY3" t="n">
         <v>4.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB3" t="n">
         <v>6.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.2</v>
+        <v>85</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.44</v>
+        <v>110</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP3" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR3" t="n">
         <v>32</v>
       </c>
       <c r="BS3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.36</v>
+        <v>7.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -1365,61 +1365,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="H4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K4" t="n">
         <v>4.1</v>
       </c>
-      <c r="I4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="O4" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="R4" t="n">
         <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1431,16 +1431,16 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="n">
         <v>950</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1455,7 +1455,7 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK4" t="n">
         <v>100</v>
@@ -1473,25 +1473,25 @@
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AQ4" t="n">
         <v>5.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.66</v>
+        <v>4.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AU4" t="n">
         <v>4.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AW4" t="n">
         <v>4.5</v>
@@ -1503,49 +1503,49 @@
         <v>5.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="BA4" t="n">
         <v>4.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.8</v>
+        <v>140</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.85</v>
+        <v>2.76</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.06</v>
+        <v>180</v>
       </c>
       <c r="BN4" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BO4" t="n">
         <v>3.6</v>
@@ -1554,41 +1554,41 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H5" t="n">
         <v>2.32</v>
       </c>
       <c r="I5" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -1643,34 +1643,34 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P5" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
         <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W5" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
@@ -1685,10 +1685,10 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
@@ -1718,7 +1718,7 @@
         <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
         <v>600</v>
@@ -1727,55 +1727,55 @@
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="AU5" t="n">
         <v>4.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
         <v>6.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC5" t="n">
         <v>8</v>
       </c>
-      <c r="BC5" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BD5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.48</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
         <v>22</v>
@@ -1796,13 +1796,13 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1814,7 +1814,7 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BT5" t="n">
         <v>5.3</v>
@@ -1826,13 +1826,13 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="J6" t="n">
         <v>3.25</v>
@@ -1891,37 +1891,37 @@
         <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="O6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R6" t="n">
         <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V6" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="W6" t="n">
         <v>1.26</v>
@@ -1936,7 +1936,7 @@
         <v>12.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB6" t="n">
         <v>13.5</v>
@@ -1948,7 +1948,7 @@
         <v>11.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
         <v>85</v>
@@ -1957,7 +1957,7 @@
         <v>19.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
         <v>450</v>
@@ -1978,10 +1978,10 @@
         <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ6" t="n">
         <v>6.2</v>
@@ -1990,7 +1990,7 @@
         <v>5.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -2002,91 +2002,91 @@
         <v>9.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG6" t="n">
         <v>7</v>
       </c>
-      <c r="AY6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH6" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G7" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H7" t="n">
         <v>3.05</v>
@@ -2292,13 +2292,13 @@
         <v>3.65</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,7 +2310,7 @@
         <v>5.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>1.32</v>
       </c>
       <c r="G8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.27</v>
@@ -2420,25 +2420,25 @@
         <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V8" t="n">
         <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X8" t="n">
         <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="Z8" t="n">
         <v>540</v>
@@ -2459,7 +2459,7 @@
         <v>310</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
@@ -2492,13 +2492,13 @@
         <v>14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AR8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS8" t="n">
         <v>9</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>9.6</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
@@ -2507,10 +2507,10 @@
         <v>10</v>
       </c>
       <c r="AV8" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX8" t="n">
         <v>6.6</v>
@@ -2519,28 +2519,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB8" t="n">
         <v>8.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8" t="n">
         <v>4.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
         <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
         <v>1.4</v>
@@ -2707,7 +2707,7 @@
         <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
         <v>65</v>
@@ -2776,13 +2776,13 @@
         <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB9" t="n">
         <v>6</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD9" t="n">
         <v>5.8</v>
@@ -2791,7 +2791,7 @@
         <v>6</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG9" t="n">
         <v>9.4</v>
@@ -2800,7 +2800,7 @@
         <v>3.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.800000000000001</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
         <v>1.59</v>
@@ -2934,7 +2934,7 @@
         <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V10" t="n">
         <v>1.08</v>
@@ -2946,7 +2946,7 @@
         <v>26</v>
       </c>
       <c r="Y10" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="Z10" t="n">
         <v>540</v>
@@ -2964,7 +2964,7 @@
         <v>120</v>
       </c>
       <c r="AE10" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AF10" t="n">
         <v>9.6</v>
@@ -2994,19 +2994,19 @@
         <v>4.9</v>
       </c>
       <c r="AO10" t="n">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AP10" t="n">
         <v>21</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
         <v>7.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT10" t="n">
         <v>6.8</v>
@@ -3030,7 +3030,7 @@
         <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
         <v>8.4</v>
@@ -3042,7 +3042,7 @@
         <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF10" t="n">
         <v>4.1</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3260,7 @@
         <v>7</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT11" t="n">
         <v>10.5</v>
@@ -3275,7 +3275,7 @@
         <v>9</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
@@ -3284,13 +3284,13 @@
         <v>9</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.6</v>
+        <v>26</v>
       </c>
       <c r="BB11" t="n">
         <v>6</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD11" t="n">
         <v>20</v>
@@ -3299,10 +3299,10 @@
         <v>6</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH11" t="n">
         <v>3.9</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BN11" t="n">
         <v>7.6</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,246 +3388,246 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Fk Velez Mostar</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="G12" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>21</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>1.49</v>
       </c>
       <c r="O12" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>3.15</v>
+        <v>1.37</v>
       </c>
       <c r="T12" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
         <v>85</v>
       </c>
-      <c r="AF12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AO12" t="n">
-        <v>32</v>
+        <v>190</v>
       </c>
       <c r="AP12" t="n">
-        <v>11</v>
+        <v>1.02</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.5</v>
+        <v>1.02</v>
       </c>
       <c r="AR12" t="n">
-        <v>17</v>
+        <v>1.02</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.4</v>
+        <v>1.02</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.4</v>
+        <v>1.02</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>1.02</v>
       </c>
       <c r="AV12" t="n">
-        <v>10.5</v>
+        <v>1.02</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.2</v>
+        <v>1.02</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>1.02</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12.5</v>
+        <v>1.02</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.4</v>
+        <v>1.02</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>1.02</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>1.02</v>
       </c>
       <c r="BD12" t="n">
-        <v>18</v>
+        <v>1.02</v>
       </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>1.02</v>
       </c>
       <c r="BF12" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,244 +3637,244 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandi</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.8</v>
+        <v>2.32</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7</v>
+        <v>2.46</v>
       </c>
       <c r="H13" t="n">
-        <v>2.14</v>
+        <v>3.15</v>
       </c>
       <c r="I13" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>2.28</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>1.87</v>
       </c>
       <c r="R13" t="n">
-        <v>1.15</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="T13" t="n">
-        <v>2.24</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>1.63</v>
+        <v>2.26</v>
       </c>
       <c r="V13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.68</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.28</v>
-      </c>
       <c r="X13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE13" t="n">
         <v>8</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="BF13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG13" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>460</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>330</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>540</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>160</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="BH13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT13" t="n">
         <v>6.8</v>
       </c>
-      <c r="AT13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA13" t="n">
+      <c r="BU13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW13" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BN13" t="n">
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>26</v>
+      </c>
+      <c r="CA13" t="n">
         <v>7.6</v>
       </c>
-      <c r="BO13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>0</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -3896,229 +3896,229 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Argentino de Merlo</t>
+          <t>Arsenal de Sarandi</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="G14" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="H14" t="n">
-        <v>2.58</v>
+        <v>2.16</v>
       </c>
       <c r="I14" t="n">
-        <v>2.92</v>
+        <v>2.48</v>
       </c>
       <c r="J14" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="K14" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.68</v>
       </c>
-      <c r="M14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="W14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y14" t="n">
         <v>6.8</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>7.2</v>
-      </c>
       <c r="Z14" t="n">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="AA14" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="AE14" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AF14" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="AG14" t="n">
-        <v>17</v>
+        <v>950</v>
       </c>
       <c r="AH14" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>260</v>
+        <v>460</v>
       </c>
       <c r="AJ14" t="n">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>160</v>
+        <v>330</v>
       </c>
       <c r="AL14" t="n">
         <v>540</v>
       </c>
       <c r="AM14" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="AO14" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AQ14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
         <v>4.5</v>
       </c>
-      <c r="AR14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>42</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>29</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.99</v>
+        <v>5</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -4150,229 +4150,229 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Camioneros</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>Argentino de Merlo</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="G15" t="n">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="H15" t="n">
-        <v>3.85</v>
+        <v>2.64</v>
       </c>
       <c r="I15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>540</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT15" t="n">
         <v>4.8</v>
       </c>
-      <c r="J15" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AU15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY15" t="n">
         <v>12</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AZ15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BJ15" t="n">
         <v>13</v>
       </c>
-      <c r="AD15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>210</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>430</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>460</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
+      <c r="BK15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP15" t="n">
         <v>38</v>
       </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
       <c r="BQ15" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -4413,61 +4413,61 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G16" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="H16" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="J16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K16" t="n">
         <v>2.56</v>
       </c>
-      <c r="K16" t="n">
-        <v>2.96</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="M16" t="n">
         <v>1.22</v>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="O16" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="P16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.9</v>
+        <v>2.92</v>
       </c>
       <c r="R16" t="n">
         <v>1.1</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>2.92</v>
       </c>
       <c r="T16" t="n">
-        <v>2.58</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
@@ -4476,22 +4476,22 @@
         <v>970</v>
       </c>
       <c r="AA16" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AB16" t="n">
         <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
         <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AG16" t="n">
         <v>970</v>
@@ -4500,19 +4500,19 @@
         <v>950</v>
       </c>
       <c r="AI16" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AK16" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN16" t="n">
         <v>600</v>
@@ -4521,70 +4521,70 @@
         <v>450</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.95</v>
+        <v>1.82</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>1.84</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.2</v>
+        <v>2</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.7</v>
+        <v>1.89</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.2</v>
+        <v>1.89</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.5</v>
+        <v>1.92</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="AY16" t="n">
-        <v>6</v>
+        <v>1.99</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.3</v>
+        <v>2.12</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.3</v>
+        <v>2.12</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.1</v>
+        <v>2.12</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.98</v>
+        <v>2.12</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.1</v>
+        <v>2.12</v>
       </c>
       <c r="BG16" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4596,7 +4596,7 @@
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
@@ -4614,7 +4614,7 @@
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,192 +4653,192 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>1.71</v>
+        <v>2.42</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="I17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>430</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>460</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AX17" t="n">
         <v>5.1</v>
       </c>
-      <c r="J17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>11</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X17" t="n">
-        <v>250</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>21</v>
-      </c>
       <c r="AY17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE17" t="n">
         <v>8</v>
       </c>
-      <c r="AZ17" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>24</v>
-      </c>
       <c r="BF17" t="n">
-        <v>3.65</v>
+        <v>6.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>12.5</v>
+        <v>2.86</v>
       </c>
       <c r="BH17" t="n">
-        <v>7.8</v>
+        <v>2.76</v>
       </c>
       <c r="BI17" t="n">
-        <v>5.9</v>
+        <v>2.24</v>
       </c>
       <c r="BJ17" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4847,50 +4847,50 @@
         <v>8.6</v>
       </c>
       <c r="BN17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>6.2</v>
       </c>
-      <c r="BO17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BR17" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT17" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV17" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
         <v>7.8</v>
       </c>
       <c r="BX17" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BZ17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -4912,246 +4912,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I18" t="n">
         <v>5.1</v>
       </c>
-      <c r="G18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.65</v>
-      </c>
       <c r="J18" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="K18" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="M18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O18" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="R18" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.08</v>
+        <v>1.55</v>
       </c>
       <c r="T18" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="U18" t="n">
-        <v>2.64</v>
+        <v>3.8</v>
       </c>
       <c r="V18" t="n">
-        <v>2.52</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.21</v>
+        <v>2.48</v>
       </c>
       <c r="X18" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="Y18" t="n">
-        <v>15.5</v>
+        <v>250</v>
       </c>
       <c r="Z18" t="n">
-        <v>14.5</v>
+        <v>370</v>
       </c>
       <c r="AA18" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AB18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF18" t="n">
         <v>75</v>
       </c>
-      <c r="AC18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>220</v>
-      </c>
       <c r="AG18" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AK18" t="n">
-        <v>190</v>
+        <v>18.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>150</v>
+        <v>17.5</v>
       </c>
       <c r="AM18" t="n">
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>100</v>
+        <v>4.8</v>
       </c>
       <c r="AO18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>6</v>
       </c>
-      <c r="AP18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ18" t="n">
+      <c r="AR18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>12</v>
       </c>
-      <c r="AR18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV18" t="n">
+      <c r="BA18" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BJ18" t="n">
         <v>8.6</v>
       </c>
-      <c r="AW18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF18" t="n">
+      <c r="BK18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX18" t="n">
         <v>24</v>
       </c>
-      <c r="BG18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY18" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,244 +5161,244 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Talleres (RE)</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="G19" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="H19" t="n">
-        <v>2.42</v>
+        <v>1.58</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="J19" t="n">
-        <v>2.56</v>
+        <v>4.6</v>
       </c>
       <c r="K19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N19" t="n">
+        <v>7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P19" t="n">
         <v>3.05</v>
       </c>
-      <c r="L19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Q19" t="n">
-        <v>3.45</v>
+        <v>1.42</v>
       </c>
       <c r="R19" t="n">
-        <v>1.12</v>
+        <v>1.79</v>
       </c>
       <c r="S19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X19" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>220</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
         <v>8</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X19" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>420</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>290</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>540</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY19" t="n">
+      <c r="BZ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA19" t="n">
         <v>6.2</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>0</v>
-      </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -5420,229 +5420,229 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CSD Liniers de Ciudad Evita</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X20" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>420</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>290</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>540</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>200</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF20" t="n">
         <v>2.12</v>
       </c>
-      <c r="G20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S20" t="n">
-        <v>6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="BG20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ20" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>95</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>170</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE20" t="n">
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
         <v>7.2</v>
       </c>
-      <c r="BF20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS20" t="n">
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -5674,187 +5674,187 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Comunicaciones B Aires</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UAI Urquiza</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="G21" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="K21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="M21" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.67</v>
       </c>
-      <c r="P21" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.76</v>
-      </c>
       <c r="X21" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AA21" t="n">
         <v>900</v>
       </c>
       <c r="AB21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>170</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR21" t="n">
         <v>6.4</v>
       </c>
-      <c r="AC21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>240</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG21" t="n">
+      <c r="AS21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BJ21" t="n">
         <v>13</v>
       </c>
-      <c r="AH21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>540</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>460</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BK21" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
@@ -5863,16 +5863,16 @@
         <v>9.6</v>
       </c>
       <c r="BN21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BP21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
@@ -5881,22 +5881,22 @@
         <v>8.4</v>
       </c>
       <c r="BT21" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,239 +5928,239 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Comunicaciones B Aires</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>UAI Urquiza</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="G22" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>2.72</v>
       </c>
       <c r="K22" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L22" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="M22" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="N22" t="n">
-        <v>2.74</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="P22" t="n">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="V22" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W22" t="n">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="X22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AA22" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>540</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>460</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX22" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>380</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB22" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BD22" t="n">
-        <v>46</v>
+        <v>7.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>36</v>
+        <v>8.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>17.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH22" t="n">
-        <v>2.84</v>
+        <v>2.48</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.42</v>
+        <v>2.04</v>
       </c>
       <c r="BJ22" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BK22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ22" t="n">
         <v>6.8</v>
       </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>15</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BT22" t="n">
         <v>8.6</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BZ22" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="CA22" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -6182,246 +6182,246 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.35</v>
+        <v>1.9</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="H23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>380</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX23" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="X23" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>330</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AY23" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
         <v>24</v>
       </c>
       <c r="BA23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BB23" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BD23" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BE23" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.1</v>
+        <v>17.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="BI23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO23" t="n">
         <v>3.75</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BP23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
         <v>11.5</v>
       </c>
-      <c r="BK23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>8</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BT23" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="BU23" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
         <v>13.5</v>
       </c>
-      <c r="BX23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>13</v>
-      </c>
       <c r="BZ23" t="n">
-        <v>12.5</v>
+        <v>38</v>
       </c>
       <c r="CA23" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,251 +6431,251 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.92</v>
+        <v>1.37</v>
       </c>
       <c r="G24" t="n">
-        <v>3.4</v>
+        <v>1.39</v>
       </c>
       <c r="H24" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>10.5</v>
       </c>
       <c r="J24" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="L24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.52</v>
       </c>
-      <c r="M24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.17</v>
-      </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="V24" t="n">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.41</v>
+        <v>3.6</v>
       </c>
       <c r="X24" t="n">
-        <v>8.6</v>
+        <v>24</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.6</v>
+        <v>950</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.5</v>
+        <v>95</v>
       </c>
       <c r="AA24" t="n">
-        <v>55</v>
+        <v>330</v>
       </c>
       <c r="AB24" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="AD24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK24" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>55</v>
-      </c>
       <c r="AL24" t="n">
-        <v>540</v>
+        <v>36</v>
       </c>
       <c r="AM24" t="n">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="AN24" t="n">
-        <v>75</v>
+        <v>6.8</v>
       </c>
       <c r="AO24" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AP24" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4.3</v>
+        <v>27</v>
       </c>
       <c r="AR24" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AU24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH24" t="n">
         <v>4.2</v>
       </c>
-      <c r="AV24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>2.76</v>
-      </c>
       <c r="BI24" t="n">
-        <v>2.24</v>
+        <v>3.75</v>
       </c>
       <c r="BJ24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>2.12</v>
+        <v>14.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="BP24" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="BQ24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BR24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>2.06</v>
+        <v>9.4</v>
       </c>
       <c r="BT24" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV24" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="CA24" t="n">
         <v>7</v>
       </c>
-      <c r="BX24" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA24" t="n">
-        <v>0</v>
-      </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,244 +6685,244 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>2.92</v>
       </c>
       <c r="G25" t="n">
-        <v>2.06</v>
+        <v>3.4</v>
       </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="M25" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N25" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="O25" t="n">
         <v>1.54</v>
       </c>
       <c r="P25" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="Q25" t="n">
         <v>2.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="S25" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="U25" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V25" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="W25" t="n">
-        <v>1.94</v>
+        <v>1.41</v>
       </c>
       <c r="X25" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="Y25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD25" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z25" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>970</v>
-      </c>
       <c r="AE25" t="n">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AF25" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="AG25" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI25" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="AJ25" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="AK25" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AL25" t="n">
-        <v>65</v>
+        <v>540</v>
       </c>
       <c r="AM25" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN25" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="AO25" t="n">
         <v>150</v>
       </c>
       <c r="AP25" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="AR25" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT25" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="AW25" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>17.5</v>
+        <v>7.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD25" t="n">
         <v>7.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF25" t="n">
-        <v>17.5</v>
+        <v>7.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH25" t="n">
         <v>2.76</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="BJ25" t="n">
         <v>12</v>
       </c>
       <c r="BK25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW25" t="n">
         <v>7</v>
       </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT25" t="n">
+      <c r="BX25" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY25" t="n">
         <v>8</v>
       </c>
-      <c r="BU25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA25" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -6956,19 +6956,19 @@
         <v>1.12</v>
       </c>
       <c r="G26" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="H26" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I26" t="n">
         <v>34</v>
       </c>
       <c r="J26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="K26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="L26" t="n">
         <v>1.23</v>
@@ -6977,25 +6977,25 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P26" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S26" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="T26" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="U26" t="n">
         <v>1.53</v>
@@ -7004,7 +7004,7 @@
         <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="X26" t="n">
         <v>950</v>
@@ -7013,13 +7013,13 @@
         <v>950</v>
       </c>
       <c r="Z26" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AC26" t="n">
         <v>950</v>
@@ -7031,16 +7031,16 @@
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG26" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH26" t="n">
         <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AJ26" t="n">
         <v>8.800000000000001</v>
@@ -7055,64 +7055,64 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU26" t="n">
         <v>20</v>
       </c>
       <c r="AV26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX26" t="n">
         <v>6.8</v>
       </c>
-      <c r="AW26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX26" t="n">
+      <c r="AY26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>5.8</v>
       </c>
-      <c r="AY26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ26" t="n">
+      <c r="BA26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB26" t="n">
         <v>6.6</v>
       </c>
-      <c r="BA26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BC26" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BD26" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH26" t="n">
         <v>5.4</v>
@@ -7124,22 +7124,22 @@
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>2.02</v>
+        <v>2.54</v>
       </c>
       <c r="BN26" t="n">
         <v>3.65</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP26" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BQ26" t="n">
         <v>4.7</v>
@@ -7148,35 +7148,35 @@
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BT26" t="n">
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>13</v>
+        <v>4.7</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="BZ26" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="CA26" t="n">
         <v>5.8</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -7207,25 +7207,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G27" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H27" t="n">
         <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
         <v>3.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
@@ -7234,10 +7234,10 @@
         <v>3.15</v>
       </c>
       <c r="O27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P27" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q27" t="n">
         <v>2.24</v>
@@ -7252,13 +7252,13 @@
         <v>2.04</v>
       </c>
       <c r="U27" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V27" t="n">
         <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X27" t="n">
         <v>11.5</v>
@@ -7270,7 +7270,7 @@
         <v>38</v>
       </c>
       <c r="AA27" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB27" t="n">
         <v>7.6</v>
@@ -7294,7 +7294,7 @@
         <v>23</v>
       </c>
       <c r="AI27" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ27" t="n">
         <v>21</v>
@@ -7306,7 +7306,7 @@
         <v>48</v>
       </c>
       <c r="AM27" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN27" t="n">
         <v>17.5</v>
@@ -7315,31 +7315,31 @@
         <v>120</v>
       </c>
       <c r="AP27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AS27" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT27" t="n">
         <v>6.8</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV27" t="n">
         <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
         <v>9.4</v>
@@ -7348,19 +7348,19 @@
         <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC27" t="n">
         <v>20</v>
       </c>
       <c r="BD27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF27" t="n">
         <v>14.5</v>
@@ -7369,68 +7369,68 @@
         <v>12.5</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ27" t="n">
         <v>11.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BP27" t="n">
         <v>14</v>
       </c>
       <c r="BQ27" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT27" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU27" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>
@@ -7452,223 +7452,223 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Universitario de Deportes</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="H28" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="I28" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>2.64</v>
       </c>
       <c r="O28" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="P28" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="T28" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V28" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="W28" t="n">
-        <v>2.34</v>
+        <v>1.9</v>
       </c>
       <c r="X28" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Z28" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AA28" t="n">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="AB28" t="n">
         <v>6.6</v>
       </c>
       <c r="AC28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD28" t="n">
         <v>970</v>
       </c>
-      <c r="AD28" t="n">
-        <v>950</v>
-      </c>
       <c r="AE28" t="n">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="AF28" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AG28" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH28" t="n">
         <v>950</v>
       </c>
       <c r="AI28" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AJ28" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AK28" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AL28" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM28" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN28" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AO28" t="n">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>3.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.48</v>
+        <v>9.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC28" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AX28" t="n">
+      <c r="BD28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BT28" t="n">
         <v>7.8</v>
       </c>
-      <c r="AY28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>17</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>10</v>
-      </c>
       <c r="BU28" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
@@ -7680,11 +7680,265 @@
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-25 21:27:12</t>
+          <t>2026-05-25 23:36:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>260</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>16</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-05-25 23:36:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -857,178 +857,178 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="G2" t="n">
-        <v>2.26</v>
+        <v>2.58</v>
       </c>
       <c r="H2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I2" t="n">
         <v>4.2</v>
       </c>
-      <c r="I2" t="n">
-        <v>5.2</v>
-      </c>
       <c r="J2" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="M2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="P2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="X2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE2" t="n">
         <v>240</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>540</v>
+        <v>260</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AK2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL2" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AM2" t="n">
         <v>270</v>
       </c>
       <c r="AN2" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AO2" t="n">
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AU2" t="n">
         <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="BE2" t="n">
         <v>150</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2" t="n">
         <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,34 +1037,34 @@
         <v>180</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BR2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BS2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW2" t="n">
         <v>8</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -1111,154 +1111,154 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.4</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.38</v>
-      </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="X3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z3" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK3" t="n">
         <v>22</v>
       </c>
-      <c r="AI3" t="n">
-        <v>230</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>21</v>
-      </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
         <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="AW3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX3" t="n">
         <v>7.6</v>
       </c>
-      <c r="AX3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AY3" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="BD3" t="n">
         <v>7</v>
@@ -1267,22 +1267,22 @@
         <v>85</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.68</v>
+        <v>2.02</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,40 +1291,40 @@
         <v>110</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="BP3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.3</v>
+        <v>3.45</v>
       </c>
       <c r="BR3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BT3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="BX3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="G4" t="n">
         <v>1.93</v>
@@ -1374,22 +1374,22 @@
         <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.52</v>
@@ -1398,28 +1398,28 @@
         <v>1.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
         <v>5.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
         <v>2.06</v>
       </c>
       <c r="X4" t="n">
-        <v>90</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1431,7 +1431,7 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="AC4" t="n">
         <v>42</v>
@@ -1440,22 +1440,22 @@
         <v>950</v>
       </c>
       <c r="AE4" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH4" t="n">
         <v>950</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ4" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
         <v>100</v>
@@ -1467,64 +1467,64 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>27</v>
       </c>
       <c r="AO4" t="n">
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AW4" t="n">
         <v>4.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AY4" t="n">
         <v>5.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BC4" t="n">
         <v>7.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE4" t="n">
         <v>140</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="n">
         <v>2.76</v>
@@ -1533,10 +1533,10 @@
         <v>2.44</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,50 +1545,50 @@
         <v>180</v>
       </c>
       <c r="BN4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>7</v>
       </c>
-      <c r="BO4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -1634,37 +1634,37 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
         <v>1.63</v>
@@ -1673,7 +1673,7 @@
         <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1697,10 +1697,10 @@
         <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH5" t="n">
         <v>950</v>
@@ -1727,10 +1727,10 @@
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AR5" t="n">
         <v>6</v>
@@ -1739,10 +1739,10 @@
         <v>7.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
         <v>5.5</v>
@@ -1757,10 +1757,10 @@
         <v>5.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
         <v>8.199999999999999</v>
@@ -1772,16 +1772,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BF5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>22</v>
+        <v>4.3</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BI5" t="n">
         <v>2.38</v>
@@ -1790,31 +1790,31 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.12</v>
+        <v>1.86</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="BT5" t="n">
         <v>5.3</v>
@@ -1826,13 +1826,13 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.13</v>
+        <v>1.87</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -1879,31 +1879,31 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="I6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J6" t="n">
         <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O6" t="n">
         <v>1.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q6" t="n">
         <v>2.32</v>
@@ -1915,13 +1915,13 @@
         <v>4.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="W6" t="n">
         <v>1.26</v>
@@ -1933,10 +1933,10 @@
         <v>7.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="AB6" t="n">
         <v>13.5</v>
@@ -1981,7 +1981,7 @@
         <v>60</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ6" t="n">
         <v>6.2</v>
@@ -1996,97 +1996,97 @@
         <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD6" t="n">
         <v>9.4</v>
       </c>
-      <c r="AW6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>9</v>
-      </c>
       <c r="BE6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN6" t="n">
         <v>8</v>
       </c>
       <c r="BO6" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT6" t="n">
         <v>4.7</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BV6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -2127,40 +2127,40 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G7" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N7" t="n">
         <v>3.65</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.75</v>
       </c>
       <c r="O7" t="n">
         <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
         <v>1.36</v>
@@ -2169,25 +2169,25 @@
         <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="X7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z7" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
@@ -2196,16 +2196,16 @@
         <v>25</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AE7" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AG7" t="n">
         <v>13.5</v>
@@ -2214,109 +2214,109 @@
         <v>60</v>
       </c>
       <c r="AI7" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>38</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="n">
-        <v>13.5</v>
+        <v>5</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="AZ7" t="n">
         <v>12</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC7" t="n">
         <v>5.4</v>
       </c>
-      <c r="BC7" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD7" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>14.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH7" t="n">
         <v>3.65</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2325,10 +2325,10 @@
         <v>7.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2346,11 +2346,11 @@
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.32</v>
       </c>
       <c r="G8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H8" t="n">
         <v>12</v>
@@ -2393,13 +2393,13 @@
         <v>15.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -2408,10 +2408,10 @@
         <v>4.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
         <v>1.73</v>
@@ -2420,10 +2420,10 @@
         <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
         <v>1.68</v>
@@ -2432,7 +2432,7 @@
         <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X8" t="n">
         <v>26</v>
@@ -2483,22 +2483,22 @@
         <v>240</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>38</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
@@ -2510,7 +2510,7 @@
         <v>18</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AX8" t="n">
         <v>6.6</v>
@@ -2522,22 +2522,22 @@
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BD8" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG8" t="n">
         <v>9</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.78</v>
+        <v>4.3</v>
       </c>
       <c r="BN8" t="n">
         <v>3.75</v>
@@ -2567,10 +2567,10 @@
         <v>3.15</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2588,13 +2588,13 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.76</v>
+        <v>4.2</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.76</v>
+        <v>4.2</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -2638,73 +2638,73 @@
         <v>3.9</v>
       </c>
       <c r="G9" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="U9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W9" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X9" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
         <v>16</v>
@@ -2713,13 +2713,13 @@
         <v>65</v>
       </c>
       <c r="AF9" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AI9" t="n">
         <v>95</v>
@@ -2737,16 +2737,16 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
         <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9" t="n">
         <v>10</v>
@@ -2758,10 +2758,10 @@
         <v>12.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AW9" t="n">
         <v>15</v>
@@ -2776,61 +2776,61 @@
         <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BJ9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BK9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT9" t="n">
         <v>4.9</v>
@@ -2842,23 +2842,23 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>1.32</v>
       </c>
       <c r="H10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I10" t="n">
         <v>13</v>
@@ -2910,31 +2910,31 @@
         <v>1.24</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
         <v>1.08</v>
@@ -2958,58 +2958,58 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD10" t="n">
         <v>120</v>
       </c>
       <c r="AE10" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AI10" t="n">
         <v>470</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
         <v>100</v>
       </c>
       <c r="AM10" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="AP10" t="n">
         <v>21</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AS10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT10" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6.8</v>
       </c>
       <c r="AU10" t="n">
         <v>13</v>
@@ -3018,7 +3018,7 @@
         <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AX10" t="n">
         <v>6.8</v>
@@ -3027,10 +3027,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
         <v>8.4</v>
@@ -3042,7 +3042,7 @@
         <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF10" t="n">
         <v>4.1</v>
@@ -3054,13 +3054,13 @@
         <v>4.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BJ10" t="n">
         <v>13.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3072,7 +3072,7 @@
         <v>3.85</v>
       </c>
       <c r="BO10" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BP10" t="n">
         <v>7.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -3146,70 +3146,70 @@
         <v>3.9</v>
       </c>
       <c r="G11" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="I11" t="n">
         <v>2.02</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O11" t="n">
         <v>1.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V11" t="n">
         <v>1.98</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="AB11" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="AC11" t="n">
         <v>9.199999999999999</v>
@@ -3221,124 +3221,124 @@
         <v>34</v>
       </c>
       <c r="AF11" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AG11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AH11" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK11" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AL11" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AM11" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO11" t="n">
         <v>11.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.6</v>
+        <v>20</v>
       </c>
       <c r="AT11" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU11" t="n">
         <v>7.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BA11" t="n">
         <v>26</v>
       </c>
       <c r="BB11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BN11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT11" t="n">
         <v>5</v>
@@ -3350,23 +3350,23 @@
         <v>13.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
         <v>2.9</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,22 +3421,22 @@
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
         <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="G13" t="n">
         <v>2.46</v>
       </c>
       <c r="H13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J13" t="n">
         <v>3.55</v>
@@ -3669,46 +3669,46 @@
         <v>3.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
         <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="R13" t="n">
         <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X13" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z13" t="n">
         <v>55</v>
@@ -3717,7 +3717,7 @@
         <v>130</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC13" t="n">
         <v>9.800000000000001</v>
@@ -3726,7 +3726,7 @@
         <v>15</v>
       </c>
       <c r="AE13" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF13" t="n">
         <v>30</v>
@@ -3738,22 +3738,22 @@
         <v>17</v>
       </c>
       <c r="AI13" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AJ13" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AK13" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
         <v>85</v>
       </c>
       <c r="AM13" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="AO13" t="n">
         <v>500</v>
@@ -3768,7 +3768,7 @@
         <v>17.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13" t="n">
         <v>9.4</v>
@@ -3780,7 +3780,7 @@
         <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
         <v>11</v>
@@ -3792,10 +3792,10 @@
         <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BC13" t="n">
         <v>20</v>
@@ -3804,22 +3804,22 @@
         <v>18</v>
       </c>
       <c r="BE13" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF13" t="n">
         <v>13</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="BJ13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK13" t="n">
         <v>5.1</v>
@@ -3837,25 +3837,25 @@
         <v>4.1</v>
       </c>
       <c r="BP13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT13" t="n">
         <v>6.8</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV13" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
         <v>7.6</v>
@@ -3867,14 +3867,14 @@
         <v>8.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA13" t="n">
         <v>7.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H14" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="I14" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J14" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="K14" t="n">
         <v>3.35</v>
       </c>
       <c r="L14" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="M14" t="n">
         <v>1.14</v>
       </c>
       <c r="N14" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="O14" t="n">
         <v>1.61</v>
       </c>
       <c r="P14" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="U14" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="V14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W14" t="n">
         <v>1.28</v>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Z14" t="n">
         <v>34</v>
@@ -3986,7 +3986,7 @@
         <v>100</v>
       </c>
       <c r="AG14" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
         <v>950</v>
@@ -4007,25 +4007,25 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AO14" t="n">
         <v>110</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AT14" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="AU14" t="n">
         <v>6.2</v>
@@ -4034,10 +4034,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AY14" t="n">
         <v>10.5</v>
@@ -4046,79 +4046,79 @@
         <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC14" t="n">
         <v>8</v>
       </c>
-      <c r="BC14" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BD14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG14" t="n">
         <v>7.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN14" t="n">
         <v>7.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT14" t="n">
         <v>5.2</v>
       </c>
-      <c r="BT14" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BU14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -4159,31 +4159,31 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="G15" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="H15" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="I15" t="n">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
         <v>2.86</v>
       </c>
       <c r="K15" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
         <v>1.16</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O15" t="n">
         <v>1.69</v>
@@ -4192,7 +4192,7 @@
         <v>1.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R15" t="n">
         <v>1.13</v>
@@ -4201,61 +4201,61 @@
         <v>7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="U15" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V15" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="X15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AF15" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AG15" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI15" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="AJ15" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AK15" t="n">
-        <v>65</v>
+        <v>240</v>
       </c>
       <c r="AL15" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
@@ -4264,70 +4264,70 @@
         <v>500</v>
       </c>
       <c r="AO15" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AP15" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU15" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AV15" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BB15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE15" t="n">
         <v>10</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BF15" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BD15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>10</v>
-      </c>
       <c r="BG15" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH15" t="n">
         <v>2.48</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BJ15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK15" t="n">
         <v>6.4</v>
@@ -4339,16 +4339,16 @@
         <v>12</v>
       </c>
       <c r="BN15" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BP15" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BQ15" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
@@ -4357,22 +4357,22 @@
         <v>10.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BV15" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -4413,46 +4413,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="G16" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="I16" t="n">
-        <v>3.65</v>
+        <v>2.38</v>
       </c>
       <c r="J16" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="K16" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="M16" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="N16" t="n">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="O16" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="S16" t="n">
-        <v>2.92</v>
+        <v>7.2</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4461,13 +4461,13 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.72</v>
       </c>
       <c r="W16" t="n">
         <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
@@ -4521,58 +4521,58 @@
         <v>450</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AR16" t="n">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.89</v>
+        <v>1.34</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.92</v>
+        <v>1.37</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="AX16" t="n">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.99</v>
+        <v>1.46</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.12</v>
+        <v>1.48</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.12</v>
+        <v>1.48</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.12</v>
+        <v>1.48</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.12</v>
+        <v>1.48</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.12</v>
+        <v>1.48</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -4667,58 +4667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="H17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
         <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="O17" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="P17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="R17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V17" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="X17" t="n">
         <v>15.5</v>
@@ -4727,7 +4727,7 @@
         <v>29</v>
       </c>
       <c r="Z17" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA17" t="n">
         <v>900</v>
@@ -4736,25 +4736,25 @@
         <v>12</v>
       </c>
       <c r="AC17" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE17" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AF17" t="n">
         <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH17" t="n">
         <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="AJ17" t="n">
         <v>900</v>
@@ -4766,37 +4766,37 @@
         <v>460</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ17" t="n">
         <v>6.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU17" t="n">
         <v>6</v>
       </c>
       <c r="AV17" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="AX17" t="n">
         <v>5.1</v>
@@ -4805,28 +4805,28 @@
         <v>9</v>
       </c>
       <c r="AZ17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC17" t="n">
         <v>14.5</v>
       </c>
-      <c r="BA17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.86</v>
+        <v>6.4</v>
       </c>
       <c r="BH17" t="n">
         <v>2.76</v>
@@ -4838,49 +4838,49 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>8</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -4921,58 +4921,58 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K18" t="n">
         <v>6.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P18" t="n">
         <v>4.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="R18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W18" t="n">
         <v>2.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.48</v>
       </c>
       <c r="X18" t="n">
         <v>950</v>
@@ -4984,37 +4984,37 @@
         <v>370</v>
       </c>
       <c r="AA18" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AC18" t="n">
         <v>23</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>170</v>
       </c>
       <c r="AF18" t="n">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AJ18" t="n">
         <v>75</v>
       </c>
       <c r="AK18" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AL18" t="n">
         <v>17.5</v>
@@ -5023,22 +5023,22 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AO18" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AT18" t="n">
         <v>19</v>
@@ -5047,19 +5047,19 @@
         <v>15.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW18" t="n">
-        <v>32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY18" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
         <v>23</v>
@@ -5068,7 +5068,7 @@
         <v>11.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BD18" t="n">
         <v>11.5</v>
@@ -5077,74 +5077,74 @@
         <v>14.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BG18" t="n">
         <v>13.5</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BJ18" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BK18" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BN18" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BO18" t="n">
         <v>4.8</v>
       </c>
       <c r="BP18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BR18" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BS18" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BV18" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BX18" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BZ18" t="n">
         <v>7</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -5175,55 +5175,55 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G19" t="n">
         <v>5.8</v>
       </c>
       <c r="H19" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="I19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="J19" t="n">
         <v>4.6</v>
       </c>
       <c r="K19" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M19" t="n">
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P19" t="n">
         <v>3.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="R19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T19" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="U19" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V19" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.21</v>
@@ -5232,25 +5232,25 @@
         <v>85</v>
       </c>
       <c r="Y19" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AA19" t="n">
-        <v>44</v>
+        <v>970</v>
       </c>
       <c r="AB19" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AC19" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD19" t="n">
         <v>10.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF19" t="n">
         <v>220</v>
@@ -5277,7 +5277,7 @@
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO19" t="n">
         <v>6</v>
@@ -5295,7 +5295,7 @@
         <v>14</v>
       </c>
       <c r="AT19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU19" t="n">
         <v>10</v>
@@ -5304,40 +5304,40 @@
         <v>8.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX19" t="n">
         <v>27</v>
       </c>
       <c r="AY19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC19" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD19" t="n">
         <v>27</v>
       </c>
-      <c r="BD19" t="n">
-        <v>26</v>
-      </c>
       <c r="BE19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BF19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG19" t="n">
         <v>5.1</v>
       </c>
       <c r="BH19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI19" t="n">
         <v>4.4</v>
@@ -5346,59 +5346,59 @@
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.34</v>
+        <v>1.82</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.39</v>
+        <v>1.82</v>
       </c>
       <c r="BT19" t="n">
         <v>4.9</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -5429,58 +5429,58 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="G20" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="H20" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="J20" t="n">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="K20" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="M20" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="O20" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="P20" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="X20" t="n">
         <v>14</v>
@@ -5495,7 +5495,7 @@
         <v>420</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>80</v>
       </c>
       <c r="AC20" t="n">
         <v>42</v>
@@ -5507,7 +5507,7 @@
         <v>290</v>
       </c>
       <c r="AF20" t="n">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="AG20" t="n">
         <v>970</v>
@@ -5519,97 +5519,97 @@
         <v>540</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK20" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="AO20" t="n">
         <v>210</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AW20" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.6</v>
+        <v>3.35</v>
       </c>
       <c r="BB20" t="n">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BE20" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BF20" t="n">
         <v>2.12</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH20" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO20" t="n">
         <v>4.9</v>
@@ -5618,19 +5618,19 @@
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.6</v>
+        <v>1.54</v>
       </c>
       <c r="BT20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
@@ -5642,7 +5642,7 @@
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.4</v>
+        <v>3.8</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -5683,46 +5683,46 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G21" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="H21" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I21" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J21" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L21" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="O21" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="P21" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
         <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T21" t="n">
         <v>2.2</v>
@@ -5731,13 +5731,13 @@
         <v>1.64</v>
       </c>
       <c r="V21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="X21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y21" t="n">
         <v>11</v>
@@ -5761,7 +5761,7 @@
         <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG21" t="n">
         <v>13.5</v>
@@ -5773,7 +5773,7 @@
         <v>500</v>
       </c>
       <c r="AJ21" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AK21" t="n">
         <v>95</v>
@@ -5785,91 +5785,91 @@
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AO21" t="n">
         <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AR21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB21" t="n">
         <v>6.4</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BC21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE21" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
         <v>6.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH21" t="n">
         <v>2.64</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ21" t="n">
         <v>13</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ21" t="n">
         <v>6.8</v>
@@ -5878,25 +5878,25 @@
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -5937,64 +5937,64 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="G22" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="H22" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="I22" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K22" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="M22" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O22" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="P22" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
         <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U22" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V22" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W22" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="X22" t="n">
         <v>7</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z22" t="n">
         <v>120</v>
@@ -6003,10 +6003,10 @@
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD22" t="n">
         <v>38</v>
@@ -6015,7 +6015,7 @@
         <v>240</v>
       </c>
       <c r="AF22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG22" t="n">
         <v>14</v>
@@ -6027,76 +6027,76 @@
         <v>540</v>
       </c>
       <c r="AJ22" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AK22" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AL22" t="n">
         <v>460</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AN22" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AO22" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR22" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV22" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AW22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA22" t="n">
         <v>8</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BB22" t="n">
         <v>11.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH22" t="n">
         <v>2.48</v>
@@ -6105,10 +6105,10 @@
         <v>2.04</v>
       </c>
       <c r="BJ22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
@@ -6117,40 +6117,40 @@
         <v>9.6</v>
       </c>
       <c r="BN22" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BP22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT22" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BU22" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -6191,139 +6191,139 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="G23" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="H23" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="I23" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K23" t="n">
         <v>3.4</v>
       </c>
-      <c r="K23" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L23" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="M23" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O23" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P23" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="R23" t="n">
         <v>1.21</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U23" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y23" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA23" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AB23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE23" t="n">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="AF23" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG23" t="n">
         <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="AI23" t="n">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL23" t="n">
-        <v>380</v>
+        <v>130</v>
       </c>
       <c r="AM23" t="n">
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO23" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP23" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS23" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AT23" t="n">
         <v>6</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
@@ -6332,34 +6332,34 @@
         <v>24</v>
       </c>
       <c r="BA23" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD23" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE23" t="n">
         <v>36</v>
       </c>
       <c r="BF23" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG23" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI23" t="n">
         <v>2.42</v>
       </c>
       <c r="BJ23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK23" t="n">
         <v>6.8</v>
@@ -6368,53 +6368,53 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BN23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BP23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT23" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU23" t="n">
         <v>5.6</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ23" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -6457,40 +6457,40 @@
         <v>10.5</v>
       </c>
       <c r="J24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K24" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
         <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R24" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V24" t="n">
         <v>1.1</v>
@@ -6502,7 +6502,7 @@
         <v>24</v>
       </c>
       <c r="Y24" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="Z24" t="n">
         <v>95</v>
@@ -6517,25 +6517,25 @@
         <v>13</v>
       </c>
       <c r="AD24" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AE24" t="n">
         <v>170</v>
       </c>
       <c r="AF24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG24" t="n">
         <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI24" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="AJ24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AK24" t="n">
         <v>14.5</v>
@@ -6544,7 +6544,7 @@
         <v>36</v>
       </c>
       <c r="AM24" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN24" t="n">
         <v>6.8</v>
@@ -6559,10 +6559,10 @@
         <v>27</v>
       </c>
       <c r="AR24" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT24" t="n">
         <v>8.4</v>
@@ -6574,7 +6574,7 @@
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX24" t="n">
         <v>7.8</v>
@@ -6586,25 +6586,25 @@
         <v>24</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB24" t="n">
         <v>10</v>
       </c>
       <c r="BC24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD24" t="n">
         <v>30</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF24" t="n">
         <v>5.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BH24" t="n">
         <v>4.2</v>
@@ -6640,7 +6640,7 @@
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT24" t="n">
         <v>13</v>
@@ -6658,7 +6658,7 @@
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ24" t="n">
         <v>12.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -6699,73 +6699,73 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="K25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="M25" t="n">
         <v>1.13</v>
       </c>
       <c r="N25" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="O25" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="P25" t="n">
         <v>1.49</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="R25" t="n">
         <v>1.17</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U25" t="n">
         <v>1.74</v>
       </c>
       <c r="V25" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W25" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="X25" t="n">
         <v>8.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB25" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AC25" t="n">
         <v>7.4</v>
@@ -6774,10 +6774,10 @@
         <v>14.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG25" t="n">
         <v>16</v>
@@ -6789,7 +6789,7 @@
         <v>200</v>
       </c>
       <c r="AJ25" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AK25" t="n">
         <v>55</v>
@@ -6798,7 +6798,7 @@
         <v>540</v>
       </c>
       <c r="AM25" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN25" t="n">
         <v>75</v>
@@ -6810,16 +6810,16 @@
         <v>6.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AR25" t="n">
         <v>14</v>
       </c>
       <c r="AS25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT25" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>4.9</v>
       </c>
       <c r="AU25" t="n">
         <v>4.2</v>
@@ -6828,40 +6828,40 @@
         <v>11</v>
       </c>
       <c r="AW25" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="AX25" t="n">
         <v>14</v>
       </c>
       <c r="AY25" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC25" t="n">
         <v>7.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG25" t="n">
         <v>9</v>
       </c>
       <c r="BH25" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BI25" t="n">
         <v>2.24</v>
@@ -6870,49 +6870,49 @@
         <v>12</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BN25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ25" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR25" t="n">
         <v>60</v>
       </c>
       <c r="BS25" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT25" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BV25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW25" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX25" t="n">
         <v>55</v>
       </c>
       <c r="BY25" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -6944,239 +6944,239 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cusco FC</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.12</v>
+        <v>1.9</v>
       </c>
       <c r="G26" t="n">
-        <v>1.13</v>
+        <v>1.94</v>
       </c>
       <c r="H26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X26" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK26" t="n">
         <v>24</v>
       </c>
-      <c r="I26" t="n">
-        <v>34</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="AL26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ26" t="n">
         <v>11.5</v>
       </c>
-      <c r="K26" t="n">
-        <v>14</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="BK26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT26" t="n">
         <v>8.6</v>
       </c>
-      <c r="X26" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>350</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>410</v>
-      </c>
-      <c r="AJ26" t="n">
+      <c r="BU26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW26" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AK26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT26" t="n">
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>4</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BX26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>2.52</v>
-      </c>
       <c r="BZ26" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -7198,239 +7198,239 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Universitario de Deportes</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="G27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.9</v>
       </c>
-      <c r="H27" t="n">
-        <v>5</v>
-      </c>
-      <c r="I27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y27" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y27" t="n">
-        <v>15</v>
-      </c>
       <c r="Z27" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA27" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC27" t="n">
         <v>8</v>
       </c>
       <c r="AD27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB27" t="n">
         <v>21</v>
       </c>
-      <c r="AE27" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ27" t="n">
+      <c r="BC27" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF27" t="n">
         <v>21</v>
       </c>
-      <c r="AK27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BG27" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="BJ27" t="n">
         <v>11.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP27" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BT27" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BU27" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -7452,239 +7452,239 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="G28" t="n">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="J28" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K28" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="M28" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="P28" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="V28" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="W28" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="X28" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="Y28" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AA28" t="n">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="AB28" t="n">
         <v>6.6</v>
       </c>
       <c r="AC28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF28" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD28" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF28" t="n">
+      <c r="AG28" t="n">
         <v>11</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>11.5</v>
       </c>
       <c r="AH28" t="n">
         <v>950</v>
       </c>
       <c r="AI28" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AJ28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK28" t="n">
         <v>25</v>
       </c>
-      <c r="AK28" t="n">
-        <v>34</v>
-      </c>
       <c r="AL28" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AN28" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AO28" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="AP28" t="n">
         <v>8</v>
       </c>
       <c r="AQ28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS28" t="n">
         <v>10</v>
       </c>
-      <c r="AR28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AT28" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA28" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB28" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BC28" t="n">
         <v>7.6</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF28" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BG28" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH28" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="BJ28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>14</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA28" t="n">
         <v>11.5</v>
       </c>
-      <c r="BK28" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>15</v>
-      </c>
-      <c r="BZ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA28" t="n">
-        <v>13</v>
-      </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>
@@ -7706,239 +7706,239 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Cusco FC</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="G29" t="n">
-        <v>1.71</v>
+        <v>1.14</v>
       </c>
       <c r="H29" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="J29" t="n">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="K29" t="n">
-        <v>3.95</v>
+        <v>13.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>7.6</v>
       </c>
       <c r="O29" t="n">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="P29" t="n">
-        <v>1.67</v>
+        <v>3.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.32</v>
+        <v>1.42</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="S29" t="n">
-        <v>4.4</v>
+        <v>2.08</v>
       </c>
       <c r="T29" t="n">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="U29" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="V29" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="X29" t="n">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="Y29" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="Z29" t="n">
-        <v>55</v>
+        <v>350</v>
       </c>
       <c r="AA29" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AC29" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AD29" t="n">
         <v>950</v>
       </c>
       <c r="AE29" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AG29" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AH29" t="n">
         <v>950</v>
       </c>
       <c r="AI29" t="n">
-        <v>160</v>
+        <v>420</v>
       </c>
       <c r="AJ29" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM29" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>970</v>
+        <v>3</v>
       </c>
       <c r="AO29" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW29" t="n">
         <v>6</v>
       </c>
-      <c r="AQ29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR29" t="n">
+      <c r="AX29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK29" t="n">
         <v>8.6</v>
       </c>
-      <c r="AS29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT29" t="n">
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="CA29" t="n">
         <v>5.8</v>
       </c>
-      <c r="AU29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ29" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BN29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP29" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BT29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BV29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BX29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY29" t="n">
-        <v>16</v>
-      </c>
-      <c r="BZ29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA29" t="n">
-        <v>11.5</v>
-      </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-25 23:36:26</t>
+          <t>2026-05-26 01:46:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.78</v>
+        <v>1.07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9</v>
+        <v>1.09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.92</v>
+        <v>300</v>
       </c>
       <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>950</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="O2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>110</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S2" t="n">
+        <v>110</v>
+      </c>
+      <c r="T2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV2" t="n">
         <v>5</v>
       </c>
-      <c r="T2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>530</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>12</v>
-      </c>
       <c r="AW2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19</v>
+        <v>5.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
-        <v>24</v>
+        <v>5.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>21</v>
+        <v>5.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.6</v>
+        <v>160</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.89</v>
+        <v>1.06</v>
       </c>
       <c r="I3" t="n">
-        <v>1.95</v>
+        <v>1.14</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>20</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>2.04</v>
+        <v>4.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.5</v>
+        <v>1.26</v>
       </c>
       <c r="AE3" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AR3" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AY3" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18</v>
+        <v>5.9</v>
       </c>
       <c r="BA3" t="n">
-        <v>36</v>
+        <v>5.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BC3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BD3" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="BE3" t="n">
-        <v>90</v>
+        <v>4.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="BG3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.22</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.36</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
         <v>1.69</v>
       </c>
       <c r="X4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF4" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AK4" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BF4" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -1619,94 +1619,94 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="H5" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="R5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="X5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z5" t="n">
         <v>120</v>
       </c>
-      <c r="Z5" t="n">
-        <v>180</v>
-      </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="AE5" t="n">
-        <v>370</v>
+        <v>230</v>
       </c>
       <c r="AF5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG5" t="n">
         <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="AI5" t="n">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="AJ5" t="n">
         <v>10.5</v>
@@ -1715,79 +1715,79 @@
         <v>15.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AM5" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AO5" t="n">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="AP5" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>38</v>
       </c>
       <c r="AR5" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="AS5" t="n">
         <v>10.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>27</v>
       </c>
-      <c r="AW5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA5" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD5" t="n">
         <v>23</v>
       </c>
       <c r="BE5" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK5" t="n">
         <v>10</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN5" t="n">
         <v>3.7</v>
@@ -1808,31 +1808,31 @@
         <v>7.6</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BR5" t="n">
         <v>26</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>16</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -1879,10 +1879,10 @@
         <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
@@ -1909,49 +1909,49 @@
         <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
         <v>1.76</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="W6" t="n">
         <v>1.31</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA6" t="n">
         <v>40</v>
       </c>
       <c r="AB6" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AC6" t="n">
         <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AE6" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AG6" t="n">
         <v>22</v>
@@ -1966,7 +1966,7 @@
         <v>300</v>
       </c>
       <c r="AK6" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
         <v>250</v>
@@ -1978,13 +1978,13 @@
         <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR6" t="n">
         <v>11.5</v>
@@ -1993,7 +1993,7 @@
         <v>16</v>
       </c>
       <c r="AT6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
         <v>6.8</v>
@@ -2017,19 +2017,19 @@
         <v>32</v>
       </c>
       <c r="BB6" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BC6" t="n">
         <v>22</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BF6" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BG6" t="n">
         <v>15</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -2127,139 +2127,139 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="G7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H7" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="I7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
         <v>4.5</v>
       </c>
       <c r="X7" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z7" t="n">
-        <v>310</v>
+        <v>210</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AD7" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AE7" t="n">
-        <v>900</v>
+        <v>590</v>
       </c>
       <c r="AF7" t="n">
         <v>6.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AI7" t="n">
-        <v>560</v>
+        <v>480</v>
       </c>
       <c r="AJ7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK7" t="n">
         <v>16.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AM7" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="AN7" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="AP7" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
         <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AY7" t="n">
         <v>10.5</v>
@@ -2268,52 +2268,52 @@
         <v>38</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC7" t="n">
         <v>14</v>
       </c>
       <c r="BD7" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BE7" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF7" t="n">
         <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH7" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BI7" t="n">
         <v>3.15</v>
       </c>
       <c r="BJ7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BO7" t="n">
         <v>2.88</v>
       </c>
       <c r="BP7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ7" t="n">
         <v>6</v>
@@ -2322,35 +2322,35 @@
         <v>32</v>
       </c>
       <c r="BS7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BT7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BU7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="CA7" t="n">
         <v>6</v>
       </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>5.5</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G8" t="n">
         <v>1.48</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.55</v>
-      </c>
       <c r="H8" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.4</v>
@@ -2405,94 +2405,94 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="X8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA8" t="n">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD8" t="n">
         <v>32</v>
       </c>
       <c r="AE8" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI8" t="n">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AK8" t="n">
         <v>16.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM8" t="n">
         <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO8" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AP8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AR8" t="n">
         <v>50</v>
@@ -2507,25 +2507,25 @@
         <v>10</v>
       </c>
       <c r="AV8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW8" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY8" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA8" t="n">
         <v>70</v>
       </c>
       <c r="BB8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC8" t="n">
         <v>14.5</v>
@@ -2534,77 +2534,77 @@
         <v>32</v>
       </c>
       <c r="BE8" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BF8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG8" t="n">
         <v>15</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
         <v>12.5</v>
       </c>
-      <c r="BK8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BN8" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP8" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BR8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BT8" t="n">
         <v>12</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BZ8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -2635,37 +2635,37 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="H9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I9" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="J9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q9" t="n">
         <v>1.6</v>
@@ -2677,46 +2677,46 @@
         <v>2.52</v>
       </c>
       <c r="T9" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="X9" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="Y9" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="Z9" t="n">
         <v>540</v>
       </c>
       <c r="AA9" t="n">
-        <v>620</v>
+        <v>810</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC9" t="n">
         <v>15.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AE9" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>48</v>
@@ -2725,70 +2725,70 @@
         <v>470</v>
       </c>
       <c r="AJ9" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AK9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL9" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AM9" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AP9" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AW9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AX9" t="n">
         <v>7</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BB9" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="BD9" t="n">
         <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BF9" t="n">
         <v>4.1</v>
@@ -2800,13 +2800,13 @@
         <v>4.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BJ9" t="n">
         <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,31 +2818,31 @@
         <v>3.85</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>3.85</v>
       </c>
       <c r="G10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I10" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J10" t="n">
         <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.35</v>
@@ -2913,91 +2913,91 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O10" t="n">
         <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
         <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y10" t="n">
         <v>11.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA10" t="n">
         <v>40</v>
       </c>
       <c r="AB10" t="n">
-        <v>40</v>
+        <v>17.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AE10" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AF10" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AG10" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AH10" t="n">
         <v>16.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK10" t="n">
         <v>120</v>
       </c>
       <c r="AL10" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="n">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>600</v>
+        <v>38</v>
       </c>
       <c r="AO10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>10</v>
@@ -3009,19 +3009,19 @@
         <v>20</v>
       </c>
       <c r="AT10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AY10" t="n">
         <v>14</v>
@@ -3030,7 +3030,7 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BB10" t="n">
         <v>28</v>
@@ -3039,34 +3039,34 @@
         <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BE10" t="n">
         <v>44</v>
       </c>
       <c r="BF10" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BG10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BN10" t="n">
         <v>7.4</v>
@@ -3075,44 +3075,44 @@
         <v>5.6</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS10" t="n">
         <v>11.5</v>
       </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BT10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX10" t="n">
         <v>25</v>
       </c>
       <c r="BY10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="CA10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="G11" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="I11" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="J11" t="n">
         <v>4.2</v>
@@ -3161,7 +3161,7 @@
         <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
@@ -3176,197 +3176,197 @@
         <v>2.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U11" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V11" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="X11" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Y11" t="n">
         <v>17.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AB11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AC11" t="n">
         <v>13.5</v>
       </c>
       <c r="AD11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>240</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR11" t="n">
         <v>13</v>
       </c>
-      <c r="AE11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AS11" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV11" t="n">
         <v>9</v>
       </c>
       <c r="AW11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU11" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
+      <c r="BV11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
         <v>7.2</v>
       </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BZ11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I12" t="n">
         <v>9</v>
@@ -3415,40 +3415,40 @@
         <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
         <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P12" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R12" t="n">
         <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X12" t="n">
         <v>15</v>
@@ -3457,7 +3457,7 @@
         <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AA12" t="n">
         <v>340</v>
@@ -3469,7 +3469,7 @@
         <v>42</v>
       </c>
       <c r="AD12" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AE12" t="n">
         <v>160</v>
@@ -3496,25 +3496,25 @@
         <v>110</v>
       </c>
       <c r="AM12" t="n">
-        <v>300</v>
+        <v>790</v>
       </c>
       <c r="AN12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>260</v>
+      </c>
+      <c r="AP12" t="n">
         <v>11.5</v>
       </c>
-      <c r="AO12" t="n">
-        <v>280</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AQ12" t="n">
-        <v>9.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT12" t="n">
         <v>6.2</v>
@@ -3526,7 +3526,7 @@
         <v>13.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX12" t="n">
         <v>7.4</v>
@@ -3538,7 +3538,7 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB12" t="n">
         <v>5.7</v>
@@ -3547,37 +3547,37 @@
         <v>14.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12" t="n">
         <v>9</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH12" t="n">
         <v>3.55</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO12" t="n">
         <v>3.05</v>
@@ -3586,41 +3586,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS12" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BT12" t="n">
         <v>11.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -3651,136 +3651,136 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G13" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="P13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.92</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
         <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z13" t="n">
         <v>22</v>
       </c>
       <c r="AA13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
         <v>13.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
         <v>11.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AJ13" t="n">
         <v>36</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM13" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AN13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO13" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AP13" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT13" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX13" t="n">
         <v>14.5</v>
@@ -3789,7 +3789,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA13" t="n">
         <v>36</v>
@@ -3798,83 +3798,83 @@
         <v>30</v>
       </c>
       <c r="BC13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE13" t="n">
         <v>55</v>
       </c>
       <c r="BF13" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BL13" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BN13" t="n">
         <v>5.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP13" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BT13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA13" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -3905,43 +3905,43 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="G14" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="H14" t="n">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="I14" t="n">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="K14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M14" t="n">
         <v>1.14</v>
       </c>
       <c r="N14" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="O14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Q14" t="n">
         <v>2.84</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
         <v>6.2</v>
@@ -3950,43 +3950,43 @@
         <v>2.18</v>
       </c>
       <c r="U14" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="V14" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="W14" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="X14" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC14" t="n">
         <v>8</v>
       </c>
-      <c r="Y14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>14</v>
-      </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AE14" t="n">
         <v>100</v>
       </c>
       <c r="AF14" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="AG14" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AH14" t="n">
         <v>950</v>
@@ -3998,7 +3998,7 @@
         <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="AL14" t="n">
         <v>540</v>
@@ -4013,106 +4013,106 @@
         <v>600</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AS14" t="n">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AX14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB14" t="n">
         <v>7.8</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BC14" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF14" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>7.4</v>
       </c>
       <c r="BG14" t="n">
         <v>7.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW14" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>3.8</v>
       </c>
       <c r="G15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
         <v>2.44</v>
@@ -4174,34 +4174,34 @@
         <v>2.9</v>
       </c>
       <c r="K15" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>1.74</v>
       </c>
       <c r="M15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="P15" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S15" t="n">
         <v>7.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
         <v>1.6</v>
@@ -4225,10 +4225,10 @@
         <v>42</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
         <v>14.5</v>
@@ -4237,7 +4237,7 @@
         <v>48</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>19</v>
@@ -4246,7 +4246,7 @@
         <v>32</v>
       </c>
       <c r="AI15" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AJ15" t="n">
         <v>130</v>
@@ -4258,19 +4258,19 @@
         <v>140</v>
       </c>
       <c r="AM15" t="n">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="AN15" t="n">
         <v>150</v>
       </c>
       <c r="AO15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP15" t="n">
         <v>5.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR15" t="n">
         <v>11.5</v>
@@ -4279,10 +4279,10 @@
         <v>28</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
         <v>12</v>
@@ -4300,22 +4300,22 @@
         <v>27</v>
       </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="BD15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BG15" t="n">
         <v>46</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -4413,46 +4413,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G16" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I16" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="J16" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="L16" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="M16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="P16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="S16" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4461,7 +4461,7 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W16" t="n">
         <v>1.3</v>
@@ -4536,7 +4536,7 @@
         <v>1.82</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="AV16" t="n">
         <v>1.71</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
       <c r="G17" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="H17" t="n">
-        <v>2.84</v>
+        <v>3.75</v>
       </c>
       <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.35</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.55</v>
       </c>
       <c r="L17" t="n">
         <v>1.59</v>
@@ -4691,55 +4691,55 @@
         <v>1.12</v>
       </c>
       <c r="N17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O17" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="X17" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA17" t="n">
         <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>970</v>
+        <v>70</v>
       </c>
       <c r="AE17" t="n">
         <v>500</v>
@@ -4754,13 +4754,13 @@
         <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="AJ17" t="n">
         <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AL17" t="n">
         <v>500</v>
@@ -4775,112 +4775,112 @@
         <v>600</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AT17" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU17" t="n">
         <v>6.2</v>
       </c>
       <c r="AV17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>6.6</v>
       </c>
-      <c r="AW17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="H18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I18" t="n">
         <v>4.4</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4.6</v>
       </c>
       <c r="J18" t="n">
         <v>5.5</v>
       </c>
       <c r="K18" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="L18" t="n">
         <v>1.14</v>
@@ -4957,31 +4957,31 @@
         <v>1.21</v>
       </c>
       <c r="R18" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="S18" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="U18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="X18" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Y18" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="Z18" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AA18" t="n">
         <v>120</v>
@@ -4990,28 +4990,28 @@
         <v>34</v>
       </c>
       <c r="AC18" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AD18" t="n">
         <v>24</v>
       </c>
       <c r="AE18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI18" t="n">
         <v>30</v>
       </c>
       <c r="AJ18" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK18" t="n">
         <v>15.5</v>
@@ -5023,28 +5023,28 @@
         <v>34</v>
       </c>
       <c r="AN18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AO18" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AQ18" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AR18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS18" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AT18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AV18" t="n">
         <v>21</v>
@@ -5053,82 +5053,82 @@
         <v>34</v>
       </c>
       <c r="AX18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA18" t="n">
         <v>29</v>
       </c>
       <c r="BB18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC18" t="n">
         <v>14</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BG18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ18" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BK18" t="n">
         <v>5.3</v>
       </c>
-      <c r="BJ18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BL18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BM18" t="n">
         <v>10.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BP18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT18" t="n">
         <v>10</v>
       </c>
       <c r="BU18" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BV18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX18" t="n">
         <v>22</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -5175,230 +5175,230 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K19" t="n">
         <v>5.6</v>
       </c>
-      <c r="G19" t="n">
-        <v>6</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>5.1</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M19" t="n">
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P19" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="R19" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="S19" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U19" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="V19" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X19" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="Y19" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AC19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD19" t="n">
         <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF19" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AG19" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AH19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ19" t="n">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AK19" t="n">
         <v>700</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>580</v>
+        <v>60</v>
       </c>
       <c r="AN19" t="n">
-        <v>700</v>
+        <v>40</v>
       </c>
       <c r="AO19" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AP19" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR19" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS19" t="n">
         <v>14.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AU19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX19" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AY19" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB19" t="n">
         <v>60</v>
       </c>
       <c r="BC19" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BD19" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BE19" t="n">
         <v>34</v>
       </c>
       <c r="BF19" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BH19" t="n">
         <v>5.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.42</v>
+        <v>12</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.45</v>
+        <v>10.5</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT19" t="n">
         <v>4.9</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BW19" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="CA19" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G20" t="n">
         <v>4.6</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="I20" t="n">
         <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="K20" t="n">
         <v>2.68</v>
@@ -5537,58 +5537,58 @@
         <v>600</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AT20" t="n">
         <v>4.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="BH20" t="n">
         <v>2.48</v>
@@ -5600,13 +5600,13 @@
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN20" t="n">
         <v>6.8</v>
@@ -5618,16 +5618,16 @@
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT20" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU20" t="n">
         <v>4.5</v>
@@ -5636,13 +5636,13 @@
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
         <v>2.44</v>
       </c>
       <c r="H21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
         <v>4.7</v>
@@ -5698,7 +5698,7 @@
         <v>2.78</v>
       </c>
       <c r="K21" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
         <v>1.66</v>
@@ -5710,7 +5710,7 @@
         <v>2.32</v>
       </c>
       <c r="O21" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P21" t="n">
         <v>1.41</v>
@@ -5731,7 +5731,7 @@
         <v>1.64</v>
       </c>
       <c r="V21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
         <v>1.7</v>
@@ -5761,7 +5761,7 @@
         <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG21" t="n">
         <v>13.5</v>
@@ -5812,7 +5812,7 @@
         <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX21" t="n">
         <v>11</v>
@@ -5824,25 +5824,25 @@
         <v>21</v>
       </c>
       <c r="BA21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE21" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
         <v>7.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH21" t="n">
         <v>2.64</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -5937,19 +5937,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="K22" t="n">
         <v>3.05</v>
@@ -5964,7 +5964,7 @@
         <v>2.28</v>
       </c>
       <c r="O22" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="P22" t="n">
         <v>1.39</v>
@@ -5976,25 +5976,25 @@
         <v>1.14</v>
       </c>
       <c r="S22" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="X22" t="n">
         <v>7.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
         <v>80</v>
@@ -6003,22 +6003,22 @@
         <v>500</v>
       </c>
       <c r="AB22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC22" t="n">
         <v>7.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE22" t="n">
         <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH22" t="n">
         <v>950</v>
@@ -6048,13 +6048,13 @@
         <v>6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT22" t="n">
         <v>5.4</v>
@@ -6063,13 +6063,13 @@
         <v>4.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>28</v>
+        <v>9.4</v>
       </c>
       <c r="AX22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
@@ -6078,31 +6078,31 @@
         <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BC22" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF22" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="BG22" t="n">
         <v>7.6</v>
       </c>
       <c r="BH22" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BJ22" t="n">
         <v>13.5</v>
@@ -6117,28 +6117,28 @@
         <v>9</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BP22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT22" t="n">
         <v>8</v>
       </c>
-      <c r="BT22" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BU22" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -6191,25 +6191,25 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G23" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I23" t="n">
         <v>5.6</v>
       </c>
-      <c r="I23" t="n">
-        <v>5.8</v>
-      </c>
       <c r="J23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M23" t="n">
         <v>1.12</v>
@@ -6224,31 +6224,31 @@
         <v>1.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T23" t="n">
         <v>2.22</v>
       </c>
       <c r="U23" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V23" t="n">
         <v>1.21</v>
       </c>
       <c r="W23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X23" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z23" t="n">
         <v>42</v>
@@ -6257,19 +6257,19 @@
         <v>180</v>
       </c>
       <c r="AB23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE23" t="n">
         <v>110</v>
       </c>
       <c r="AF23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG23" t="n">
         <v>11.5</v>
@@ -6290,7 +6290,7 @@
         <v>130</v>
       </c>
       <c r="AM23" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN23" t="n">
         <v>21</v>
@@ -6305,10 +6305,10 @@
         <v>12.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AS23" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT23" t="n">
         <v>6</v>
@@ -6317,13 +6317,13 @@
         <v>7.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW23" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
@@ -6332,7 +6332,7 @@
         <v>24</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="BB23" t="n">
         <v>18</v>
@@ -6350,7 +6350,7 @@
         <v>18.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH23" t="n">
         <v>2.78</v>
@@ -6362,16 +6362,16 @@
         <v>12</v>
       </c>
       <c r="BK23" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BN23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO23" t="n">
         <v>3.85</v>
@@ -6380,13 +6380,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT23" t="n">
         <v>8.6</v>
@@ -6395,26 +6395,26 @@
         <v>7</v>
       </c>
       <c r="BV23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>14.5</v>
+        <v>2.36</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G24" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H24" t="n">
         <v>9.6</v>
@@ -6457,10 +6457,10 @@
         <v>10.5</v>
       </c>
       <c r="J24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K24" t="n">
         <v>5.9</v>
-      </c>
-      <c r="K24" t="n">
-        <v>6.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.31</v>
@@ -6475,52 +6475,52 @@
         <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S24" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T24" t="n">
         <v>1.98</v>
       </c>
       <c r="U24" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V24" t="n">
         <v>1.1</v>
       </c>
       <c r="W24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="X24" t="n">
         <v>24</v>
       </c>
       <c r="Y24" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="Z24" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA24" t="n">
         <v>400</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AC24" t="n">
         <v>13.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE24" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AF24" t="n">
         <v>8.800000000000001</v>
@@ -6532,37 +6532,37 @@
         <v>28</v>
       </c>
       <c r="AI24" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AJ24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AK24" t="n">
         <v>14.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM24" t="n">
         <v>150</v>
       </c>
       <c r="AN24" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AO24" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AP24" t="n">
         <v>21</v>
       </c>
       <c r="AQ24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AR24" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="AS24" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT24" t="n">
         <v>8.4</v>
@@ -6574,10 +6574,10 @@
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY24" t="n">
         <v>9.4</v>
@@ -6586,10 +6586,10 @@
         <v>24</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC24" t="n">
         <v>12</v>
@@ -6598,16 +6598,16 @@
         <v>30</v>
       </c>
       <c r="BE24" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG24" t="n">
         <v>15</v>
       </c>
       <c r="BH24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI24" t="n">
         <v>3.75</v>
@@ -6616,16 +6616,16 @@
         <v>12</v>
       </c>
       <c r="BK24" t="n">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BO24" t="n">
         <v>3.45</v>
@@ -6640,25 +6640,25 @@
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BT24" t="n">
         <v>13</v>
       </c>
       <c r="BU24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
         <v>10</v>
       </c>
-      <c r="BV24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>11</v>
-      </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ24" t="n">
         <v>12.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -6702,19 +6702,19 @@
         <v>3.1</v>
       </c>
       <c r="G25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J25" t="n">
         <v>2.72</v>
       </c>
       <c r="K25" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.64</v>
@@ -6726,7 +6726,7 @@
         <v>2.36</v>
       </c>
       <c r="O25" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P25" t="n">
         <v>1.43</v>
@@ -6750,7 +6750,7 @@
         <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X25" t="n">
         <v>7.8</v>
@@ -6816,7 +6816,7 @@
         <v>13.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="AT25" t="n">
         <v>7</v>
@@ -6828,7 +6828,7 @@
         <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="AX25" t="n">
         <v>15.5</v>
@@ -6849,16 +6849,16 @@
         <v>7.2</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF25" t="n">
         <v>7.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH25" t="n">
         <v>2.66</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -6953,85 +6953,85 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="G26" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="H26" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="I26" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O26" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="Q26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W26" t="n">
         <v>2.26</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.14</v>
-      </c>
       <c r="X26" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AA26" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AB26" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE26" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF26" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG26" t="n">
         <v>10.5</v>
@@ -7040,52 +7040,52 @@
         <v>23</v>
       </c>
       <c r="AI26" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ26" t="n">
         <v>19.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM26" t="n">
         <v>160</v>
       </c>
       <c r="AN26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS26" t="n">
         <v>15.5</v>
       </c>
-      <c r="AO26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>16</v>
-      </c>
       <c r="AT26" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW26" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AX26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY26" t="n">
         <v>9.4</v>
@@ -7094,52 +7094,52 @@
         <v>20</v>
       </c>
       <c r="BA26" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="BB26" t="n">
-        <v>18</v>
+        <v>9.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="BD26" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
         <v>13</v>
       </c>
-      <c r="BE26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>12</v>
-      </c>
       <c r="BN26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO26" t="n">
         <v>3.6</v>
       </c>
       <c r="BP26" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ26" t="n">
         <v>6.6</v>
@@ -7148,35 +7148,35 @@
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT26" t="n">
         <v>9</v>
       </c>
       <c r="BU26" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="G27" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="H27" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="I27" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="J27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K27" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L27" t="n">
         <v>1.59</v>
@@ -7231,10 +7231,10 @@
         <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O27" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P27" t="n">
         <v>1.56</v>
@@ -7246,31 +7246,31 @@
         <v>1.2</v>
       </c>
       <c r="S27" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U27" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V27" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W27" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="X27" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y27" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Z27" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AA27" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AB27" t="n">
         <v>7.2</v>
@@ -7279,55 +7279,55 @@
         <v>7.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG27" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG27" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AH27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
         <v>100</v>
       </c>
       <c r="AJ27" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK27" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL27" t="n">
         <v>65</v>
       </c>
       <c r="AM27" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="AN27" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO27" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP27" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS27" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU27" t="n">
         <v>6.8</v>
@@ -7336,40 +7336,40 @@
         <v>15</v>
       </c>
       <c r="AW27" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX27" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY27" t="n">
         <v>11</v>
       </c>
       <c r="AZ27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA27" t="n">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="BB27" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC27" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BD27" t="n">
         <v>55</v>
       </c>
       <c r="BE27" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BG27" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="BH27" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BI27" t="n">
         <v>2.34</v>
@@ -7378,22 +7378,22 @@
         <v>11.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BN27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO27" t="n">
         <v>4.4</v>
       </c>
       <c r="BP27" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BQ27" t="n">
         <v>9.6</v>
@@ -7402,35 +7402,35 @@
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU27" t="n">
         <v>6</v>
       </c>
       <c r="BV27" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>50</v>
+      </c>
+      <c r="CA27" t="n">
         <v>13</v>
       </c>
-      <c r="BX27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BZ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA27" t="n">
-        <v>13.5</v>
-      </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -7461,100 +7461,100 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="G28" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I28" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J28" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K28" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P28" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U28" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W28" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="X28" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y28" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z28" t="n">
         <v>55</v>
       </c>
       <c r="AA28" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AB28" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF28" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AG28" t="n">
         <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AI28" t="n">
         <v>130</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="n">
         <v>55</v>
@@ -7563,10 +7563,10 @@
         <v>220</v>
       </c>
       <c r="AN28" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO28" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AP28" t="n">
         <v>9.800000000000001</v>
@@ -7575,10 +7575,10 @@
         <v>15</v>
       </c>
       <c r="AR28" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AS28" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AT28" t="n">
         <v>6</v>
@@ -7587,22 +7587,22 @@
         <v>7.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW28" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA28" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB28" t="n">
         <v>15</v>
@@ -7611,22 +7611,22 @@
         <v>19</v>
       </c>
       <c r="BD28" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE28" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BH28" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="BJ28" t="n">
         <v>12</v>
@@ -7638,19 +7638,19 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BN28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ28" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
@@ -7659,16 +7659,16 @@
         <v>12.5</v>
       </c>
       <c r="BT28" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
@@ -7680,11 +7680,11 @@
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -7715,19 +7715,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="G29" t="n">
         <v>1.14</v>
       </c>
       <c r="H29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J29" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="K29" t="n">
         <v>13</v>
@@ -7739,28 +7739,28 @@
         <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O29" t="n">
         <v>1.13</v>
       </c>
       <c r="P29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q29" t="n">
         <v>1.42</v>
       </c>
       <c r="R29" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="S29" t="n">
         <v>2.08</v>
       </c>
       <c r="T29" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="U29" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V29" t="n">
         <v>1.03</v>
@@ -7775,7 +7775,7 @@
         <v>950</v>
       </c>
       <c r="Z29" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
@@ -7793,7 +7793,7 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG29" t="n">
         <v>16</v>
@@ -7802,82 +7802,82 @@
         <v>950</v>
       </c>
       <c r="AI29" t="n">
-        <v>340</v>
+        <v>420</v>
       </c>
       <c r="AJ29" t="n">
         <v>9</v>
       </c>
       <c r="AK29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL29" t="n">
         <v>65</v>
       </c>
       <c r="AM29" t="n">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="AN29" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.7</v>
+        <v>34</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU29" t="n">
         <v>6.2</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AV29" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>6</v>
-      </c>
       <c r="AW29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX29" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX29" t="n">
-        <v>7</v>
-      </c>
       <c r="AY29" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB29" t="n">
         <v>6.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF29" t="n">
         <v>2.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH29" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BI29" t="n">
         <v>4.7</v>
@@ -7886,22 +7886,22 @@
         <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BN29" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP29" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BQ29" t="n">
         <v>4.7</v>
@@ -7910,35 +7910,35 @@
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT29" t="n">
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ29" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CA29" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Cusco FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
         <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>150</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,136 +887,136 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>22</v>
+        <v>1.09</v>
       </c>
       <c r="T2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC2" t="n">
         <v>6.4</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="V2" t="n">
-        <v>130</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>850</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>990</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BD2" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -1102,239 +1102,239 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cusco FC</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="n">
+        <v>200</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>1.14</v>
       </c>
-      <c r="H3" t="n">
-        <v>29</v>
-      </c>
-      <c r="I3" t="n">
-        <v>32</v>
-      </c>
-      <c r="J3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>65</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S3" t="n">
+        <v>130</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>850</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY3" t="n">
         <v>9.4</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="X3" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>130</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>330</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>530</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>360</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>48</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>19.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>40</v>
+        <v>5.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>130</v>
+        <v>6.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.42</v>
+        <v>5.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -1356,239 +1356,239 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Universitario de Deportes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>1.09</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -1610,493 +1610,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Universitario de Deportes</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.2</v>
+        <v>1.05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.22</v>
+        <v>1.07</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>30</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>22</v>
       </c>
       <c r="L5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.98</v>
+        <v>1.16</v>
       </c>
       <c r="O5" t="n">
-        <v>1.48</v>
+        <v>6.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.56</v>
+        <v>100</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8</v>
+        <v>12.5</v>
       </c>
       <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BF5" t="n">
         <v>9.4</v>
       </c>
-      <c r="Y5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>130</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>23</v>
-      </c>
       <c r="BG5" t="n">
-        <v>85</v>
+        <v>1.09</v>
       </c>
       <c r="BH5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Estudiantes</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ind Medellin</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X6" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>90</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>160</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>80</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>970</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>160</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>32</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>17</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
